--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,6 +827,260 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FK Riga</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Rigas Futbola Skola</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-06-15 05:15:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,17 +843,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -869,10 +869,10 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,261 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 05:15:13</t>
+          <t>2026-06-15 07:22:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FK Riga</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Rigas Futbola Skola</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K3" t="n">
+        <v>950</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-15 07:22:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -872,7 +872,7 @@
         <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 07:22:59</t>
+          <t>2026-06-15 09:31:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>Kairat Almaty</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>FK Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,515 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 09:31:21</t>
+          <t>2026-06-15 11:39:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Estonian Premier League</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Paide Linnameeskond</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Harju JK Laagri</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K4" t="n">
+        <v>440</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:39:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FK Riga</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rigas Futbola Skola</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:39:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O2" t="n">
         <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Q2" t="n">
         <v>1.28</v>
@@ -896,7 +896,7 @@
         <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,229 +1102,229 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,234 +1351,234 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="H4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>440</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,261 +1588,2293 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 11:39:29</t>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TPS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:49:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Latvian Virsliga</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FK Jelgava</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ogre United</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:49:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FK Tukums 2000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FK Auda</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:49:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Estonian Premier League</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>13:00:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Nomme Kalju</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Tammeka Tartu</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:49:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Estonian Premier League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Nomme Utd</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FCI Tallinn</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:49:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Estonian Premier League</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Paide Linnameeskond</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Harju JK Laagri</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:49:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>FK Riga</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Rigas Futbola Skola</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="F11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-15 11:39:29</t>
+      <c r="O11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:49:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:49:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:49:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1111,31 +1111,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="H3" t="n">
         <v>2.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.27</v>
@@ -1144,10 +1144,10 @@
         <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
         <v>2.88</v>
@@ -1159,19 +1159,19 @@
         <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
         <v>65</v>
@@ -1183,28 +1183,28 @@
         <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
         <v>24</v>
       </c>
       <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>60</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>55</v>
-      </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1222,13 +1222,13 @@
         <v>2.14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AT3" t="n">
         <v>9.199999999999999</v>
@@ -1240,37 +1240,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.26</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="BH3" t="n">
         <v>3.6</v>
@@ -1279,52 +1279,52 @@
         <v>2.78</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW3" t="n">
         <v>7</v>
       </c>
       <c r="BX3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
         <v>1.41</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.25</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
         <v>1.41</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1619,88 +1619,88 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
         <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
         <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AB5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
@@ -1709,130 +1709,130 @@
         <v>44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AK5" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AL5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
         <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BN5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>4.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV5" t="n">
         <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BX5" t="n">
         <v>27</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q7" t="n">
         <v>1.18</v>
@@ -2169,10 +2169,10 @@
         <v>1.18</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -2880,22 +2880,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -3105,21 +3105,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,22 +3134,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,234 +3383,234 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>1.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.82</v>
+        <v>1.02</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.81</v>
+        <v>1.26</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>
@@ -3642,229 +3642,229 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="G13" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H13" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,261 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 13:49:21</t>
+          <t>2026-06-15 15:58:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:58:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -896,7 +896,7 @@
         <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1144,7 +1144,7 @@
         <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
         <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T4" t="n">
         <v>1.65</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -1637,31 +1637,31 @@
         <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
@@ -1673,7 +1673,7 @@
         <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
         <v>9.199999999999999</v>
@@ -1760,7 +1760,7 @@
         <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB5" t="n">
         <v>4.7</v>
@@ -1775,7 +1775,7 @@
         <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
         <v>7.4</v>
@@ -1790,34 +1790,34 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN5" t="n">
         <v>9.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BP5" t="n">
         <v>55</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU5" t="n">
         <v>3.35</v>
@@ -1826,13 +1826,13 @@
         <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BX5" t="n">
         <v>27</v>
       </c>
       <c r="BY5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
         <v>1.25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
         <v>1.18</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.08</v>
@@ -2928,7 +2928,7 @@
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O11" t="n">
         <v>1.14</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q11" t="n">
         <v>1.13</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q12" t="n">
         <v>1.26</v>
@@ -3436,7 +3436,7 @@
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -3681,10 +3681,10 @@
         <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
@@ -3693,10 +3693,10 @@
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U13" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
         <v>1.46</v>
@@ -3708,7 +3708,7 @@
         <v>19.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
         <v>24</v>
@@ -3717,25 +3717,25 @@
         <v>55</v>
       </c>
       <c r="AB13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
         <v>14</v>
       </c>
-      <c r="AC13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AE13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>46</v>
@@ -3756,19 +3756,19 @@
         <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP13" t="n">
         <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.6</v>
+        <v>36</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -3777,40 +3777,40 @@
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.4</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.5</v>
+        <v>28</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.5</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BH13" t="n">
         <v>3.75</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
         <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3932,22 +3932,22 @@
         <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
         <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U14" t="n">
         <v>2.14</v>
@@ -3974,16 +3974,16 @@
         <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
         <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
         <v>15</v>
@@ -4019,10 +4019,10 @@
         <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
@@ -4034,7 +4034,7 @@
         <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX14" t="n">
         <v>12.5</v>
@@ -4046,10 +4046,10 @@
         <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC14" t="n">
         <v>20</v>
@@ -4058,13 +4058,13 @@
         <v>34</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH14" t="n">
         <v>3.85</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 15:58:37</t>
+          <t>2026-06-15 18:07:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -893,7 +893,7 @@
         <v>1.28</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S2" t="n">
         <v>1.28</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -1111,46 +1111,46 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H3" t="n">
         <v>2.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
         <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
         <v>1.56</v>
@@ -1159,118 +1159,118 @@
         <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
         <v>1.54</v>
       </c>
       <c r="X3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AI3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG3" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.44</v>
       </c>
       <c r="BH3" t="n">
         <v>3.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
         <v>1.84</v>
@@ -1392,7 +1392,7 @@
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
         <v>2.22</v>
@@ -1401,7 +1401,7 @@
         <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
         <v>2.68</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
@@ -1790,7 +1790,7 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>9.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP5" t="n">
         <v>55</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q6" t="n">
         <v>1.25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Q7" t="n">
         <v>1.18</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>2.16</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -2414,13 +2414,13 @@
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q12" t="n">
         <v>1.26</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>2.82</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
         <v>3.5</v>
@@ -3669,7 +3669,7 @@
         <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -3681,7 +3681,7 @@
         <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
         <v>1.81</v>
@@ -3711,7 +3711,7 @@
         <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
         <v>55</v>
@@ -3744,7 +3744,7 @@
         <v>42</v>
       </c>
       <c r="AK13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
         <v>42</v>
@@ -3753,7 +3753,7 @@
         <v>90</v>
       </c>
       <c r="AN13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
         <v>26</v>
@@ -3804,7 +3804,7 @@
         <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF13" t="n">
         <v>16.5</v>
@@ -3819,7 +3819,7 @@
         <v>3.2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK13" t="n">
         <v>5.9</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN13" t="n">
         <v>5.9</v>
@@ -3840,13 +3840,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR13" t="n">
         <v>32</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT13" t="n">
         <v>6.4</v>
@@ -3858,13 +3858,13 @@
         <v>23</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX13" t="n">
         <v>34</v>
       </c>
       <c r="BY13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>
@@ -3932,25 +3932,25 @@
         <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
         <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
         <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
         <v>1.48</v>
@@ -3980,13 +3980,13 @@
         <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
         <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
         <v>17.5</v>
@@ -4001,7 +4001,7 @@
         <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
         <v>120</v>
@@ -4013,7 +4013,7 @@
         <v>38</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
         <v>10.5</v>
@@ -4022,7 +4022,7 @@
         <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
@@ -4034,7 +4034,7 @@
         <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX14" t="n">
         <v>12.5</v>
@@ -4043,13 +4043,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
         <v>36</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BC14" t="n">
         <v>20</v>
@@ -4058,13 +4058,13 @@
         <v>34</v>
       </c>
       <c r="BE14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH14" t="n">
         <v>3.85</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 18:07:21</t>
+          <t>2026-06-15 20:15:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -893,16 +893,16 @@
         <v>1.28</v>
       </c>
       <c r="R2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
         <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
@@ -965,52 +965,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -1022,65 +1022,65 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1138,7 +1138,7 @@
         <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
         <v>1.98</v>
@@ -1153,10 +1153,10 @@
         <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
         <v>1.52</v>
@@ -1228,7 +1228,7 @@
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
         <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB3" t="n">
         <v>7.2</v>
@@ -1261,7 +1261,7 @@
         <v>6.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
         <v>8</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -1386,13 +1386,13 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
         <v>2.22</v>
@@ -1401,7 +1401,7 @@
         <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
         <v>2.68</v>
@@ -1467,118 +1467,118 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AU4" t="n">
         <v>7.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="BF4" t="n">
-        <v>7</v>
+        <v>1.26</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -1673,19 +1673,19 @@
         <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
         <v>18</v>
       </c>
       <c r="AB5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC5" t="n">
         <v>11.5</v>
@@ -1706,7 +1706,7 @@
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
         <v>190</v>
@@ -1724,7 +1724,7 @@
         <v>120</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
         <v>18.5</v>
@@ -1760,22 +1760,22 @@
         <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG5" t="n">
         <v>7.4</v>
@@ -1790,7 +1790,7 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q6" t="n">
         <v>1.25</v>
@@ -1915,10 +1915,10 @@
         <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="Q7" t="n">
         <v>1.18</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2292,55 +2292,55 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
@@ -2405,16 +2405,16 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
@@ -2423,10 +2423,10 @@
         <v>1.51</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2546,65 +2546,65 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2677,10 +2677,10 @@
         <v>1.12</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2800,65 +2800,65 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2931,10 +2931,10 @@
         <v>1.08</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3185,10 +3185,10 @@
         <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
@@ -3251,52 +3251,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3308,55 +3308,55 @@
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3430,7 +3430,7 @@
         <v>1.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
@@ -3505,52 +3505,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3562,55 +3562,55 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -3684,7 +3684,7 @@
         <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
@@ -3693,13 +3693,13 @@
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
         <v>1.59</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 20:15:46</t>
+          <t>2026-06-15 22:23:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -905,7 +905,7 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G3" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H3" t="n">
         <v>2.8</v>
@@ -1138,31 +1138,31 @@
         <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R3" t="n">
         <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
         <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X3" t="n">
         <v>16</v>
@@ -1234,7 +1234,7 @@
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H4" t="n">
         <v>4.7</v>
@@ -1386,13 +1386,13 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
         <v>2.22</v>
@@ -1401,22 +1401,22 @@
         <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>5.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="I5" t="n">
         <v>1.75</v>
@@ -1637,13 +1637,13 @@
         <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
         <v>1.29</v>
@@ -1661,7 +1661,7 @@
         <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
@@ -1670,10 +1670,10 @@
         <v>2.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
         <v>9.199999999999999</v>
@@ -1688,16 +1688,16 @@
         <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG5" t="n">
         <v>27</v>
@@ -1709,7 +1709,7 @@
         <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AK5" t="n">
         <v>95</v>
@@ -1721,10 +1721,10 @@
         <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AY5" t="n">
         <v>18.5</v>
@@ -1760,25 +1760,25 @@
         <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.7</v>
@@ -1790,7 +1790,7 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,16 +1799,16 @@
         <v>9.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1817,7 +1817,7 @@
         <v>8.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BU5" t="n">
         <v>3.35</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>1.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1</v>
+        <v>2.26</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1921,10 +1921,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.18</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O8" t="n">
         <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q8" t="n">
         <v>1.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
         <v>1.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P9" t="n">
         <v>1.29</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G13" t="n">
         <v>2.68</v>
@@ -3669,7 +3669,7 @@
         <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -3681,43 +3681,43 @@
         <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
         <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
         <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
         <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
         <v>8.800000000000001</v>
@@ -3729,10 +3729,10 @@
         <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
         <v>17</v>
@@ -3747,7 +3747,7 @@
         <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM13" t="n">
         <v>90</v>
@@ -3804,7 +3804,7 @@
         <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
         <v>16.5</v>
@@ -3813,10 +3813,10 @@
         <v>21</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.6</v>
@@ -3837,16 +3837,16 @@
         <v>4.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR13" t="n">
         <v>32</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT13" t="n">
         <v>6.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>
@@ -3932,13 +3932,13 @@
         <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
         <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R14" t="n">
         <v>1.34</v>
@@ -3959,7 +3959,7 @@
         <v>1.57</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
         <v>14.5</v>
@@ -4058,13 +4058,13 @@
         <v>34</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH14" t="n">
         <v>3.85</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-15 22:23:54</t>
+          <t>2026-06-16 00:31:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
         <v>2.78</v>
@@ -1120,55 +1120,55 @@
         <v>2.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.89</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
         <v>1.71</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>1.56</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
         <v>21</v>
@@ -1180,10 +1180,10 @@
         <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>32</v>
@@ -1201,7 +1201,7 @@
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK3" t="n">
         <v>32</v>
@@ -1210,7 +1210,7 @@
         <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
         <v>25</v>
@@ -1222,49 +1222,49 @@
         <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
         <v>34</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX3" t="n">
         <v>16</v>
       </c>
       <c r="AY3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
         <v>32</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
         <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
         <v>17</v>
@@ -1273,10 +1273,10 @@
         <v>17.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.6</v>
@@ -1297,7 +1297,7 @@
         <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ3" t="n">
         <v>7</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="n">
         <v>5.1</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
         <v>4.4</v>
@@ -1386,13 +1386,13 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
         <v>2.22</v>
@@ -1401,16 +1401,16 @@
         <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
         <v>1.24</v>
@@ -1431,10 +1431,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1464,7 +1464,7 @@
         <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
         <v>1000</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.26</v>
+        <v>9</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.8</v>
+        <v>1.28</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BE4" t="n">
         <v>1.26</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -1628,13 +1628,13 @@
         <v>1.68</v>
       </c>
       <c r="I5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
@@ -1652,22 +1652,22 @@
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.86</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.85</v>
       </c>
       <c r="U5" t="n">
         <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="W5" t="n">
         <v>1.2</v>
@@ -1679,7 +1679,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA5" t="n">
         <v>18</v>
@@ -1688,7 +1688,7 @@
         <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>10.5</v>
@@ -1730,10 +1730,10 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
         <v>14.5</v>
@@ -1745,13 +1745,13 @@
         <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
         <v>15</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY5" t="n">
         <v>18.5</v>
@@ -1760,49 +1760,49 @@
         <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD5" t="n">
         <v>7</v>
       </c>
-      <c r="BC5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG5" t="n">
         <v>8.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN5" t="n">
         <v>9.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
         <v>4.5</v>
@@ -1832,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.69</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>2.16</v>
+        <v>1.18</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,27 +2621,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2650,7 +2650,7 @@
         <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,28 +2659,28 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2800,72 +2800,72 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,27 +2875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2904,7 +2904,7 @@
         <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,28 +2913,28 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="O10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.08</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q10" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P11" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Q11" t="n">
         <v>1.13</v>
@@ -3182,7 +3182,7 @@
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3359,21 +3359,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,16 +3388,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
@@ -3406,13 +3406,13 @@
         <v>1.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>1.31</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="O12" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.92</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>1.56</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,7 +3445,7 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="W12" t="n">
         <v>1.01</v>
@@ -3613,21 +3613,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,234 +3637,234 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.44</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Q13" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="V13" t="n">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6</v>
+        <v>2.74</v>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="AA13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="AF13" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>950</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AK13" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>4.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>15</v>
+        <v>3.65</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>3.65</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>3.85</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="BD13" t="n">
-        <v>28</v>
+        <v>4.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>16.5</v>
+        <v>2.98</v>
       </c>
       <c r="BG13" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.9</v>
+        <v>3.55</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.4</v>
+        <v>1.36</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="BP13" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BR13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.8</v>
+        <v>1.3</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.2</v>
+        <v>2.84</v>
       </c>
       <c r="BV13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7</v>
+        <v>1.35</v>
       </c>
       <c r="BX13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.8</v>
+        <v>1.34</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,234 +3891,234 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.54</v>
+        <v>1.1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.86</v>
+        <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.99</v>
+        <v>1.24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>1.24</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,769 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 00:31:41</t>
+          <t>2026-06-16 02:39:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FK Kauno Zalgiris</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FK Banga Gargzdu</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K15" t="n">
+        <v>950</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:39:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:39:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:39:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,25 +878,25 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>1.13</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
         <v>1.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
         <v>2.8</v>
@@ -1129,7 +1129,7 @@
         <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1141,16 +1141,16 @@
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
         <v>1.71</v>
@@ -1210,7 +1210,7 @@
         <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
         <v>25</v>
@@ -1255,7 +1255,7 @@
         <v>32</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
         <v>7.6</v>
@@ -1267,10 +1267,10 @@
         <v>9</v>
       </c>
       <c r="BF3" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BH3" t="n">
         <v>3.65</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>4.6</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
@@ -1389,31 +1389,31 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
         <v>2.2</v>
@@ -1446,7 +1446,7 @@
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT4" t="n">
         <v>1.28</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>9</v>
-      </c>
       <c r="AU4" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AY4" t="n">
         <v>1.28</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I5" t="n">
         <v>1.74</v>
@@ -1634,7 +1634,7 @@
         <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
@@ -1661,10 +1661,10 @@
         <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
         <v>2.34</v>
@@ -1760,7 +1760,7 @@
         <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
         <v>7.4</v>
@@ -1775,7 +1775,7 @@
         <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
         <v>8.6</v>
@@ -1790,22 +1790,22 @@
         <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN5" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>9.4</v>
       </c>
       <c r="BO5" t="n">
         <v>4.9</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ5" t="n">
         <v>8.4</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT5" t="n">
         <v>4.5</v>
@@ -1826,13 +1826,13 @@
         <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BX5" t="n">
         <v>27</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,28 +1864,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>FC Iberia 1999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>FC Rustavi</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,34 +1897,34 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -2118,28 +2118,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>2.58</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>2.58</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.18</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2343,21 +2343,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,55 +2372,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
         <v>1.1</v>
       </c>
-      <c r="G8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.32</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2597,14 +2597,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -2626,67 +2626,67 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.02</v>
       </c>
-      <c r="K9" t="n">
-        <v>950</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2800,72 +2800,72 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,60 +2875,60 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.02</v>
       </c>
-      <c r="K10" t="n">
-        <v>950</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.31</v>
-      </c>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2937,10 +2937,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3105,21 +3105,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,72 +3129,72 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.02</v>
       </c>
-      <c r="K11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3251,52 +3251,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3308,65 +3308,65 @@
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -3388,16 +3388,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
@@ -3406,37 +3406,37 @@
         <v>1.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.31</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>6.8</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>1.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.96</v>
+        <v>1.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="R12" t="n">
-        <v>1.92</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.56</v>
+        <v>1.12</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
@@ -3642,34 +3642,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>1.57</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>5.9</v>
+        <v>1.18</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>1.22</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
@@ -3678,210 +3678,210 @@
         <v>1.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="P13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>220</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>270</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>250</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG13" t="n">
         <v>2.44</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="X13" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="BH13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT13" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU13" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.34</v>
+        <v>7.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,73 +3896,73 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N14" t="n">
         <v>1.1</v>
       </c>
-      <c r="G14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3971,10 +3971,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3983,142 +3983,142 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,31 +4150,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FK Kauno Zalgiris</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4186,31 +4186,31 @@
         <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
         <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4267,52 +4267,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -4324,55 +4324,55 @@
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,234 +4399,234 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>1.24</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,261 +4636,1023 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 02:39:49</t>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Georgian Umaglesi Liga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Torpedo Kutaisi</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Dinamo Batumi</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-16 04:48:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Finnish Veikkausliiga</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X18" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-16 04:48:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Gnistan</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Lahti</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="F19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK19" t="n">
         <v>2.7</v>
       </c>
-      <c r="H17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
         <v>3.4</v>
       </c>
-      <c r="K17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL17" t="n">
+      <c r="BN19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BR19" t="n">
         <v>48</v>
       </c>
-      <c r="AM17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>28</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>48</v>
-      </c>
-      <c r="BS17" t="n">
+      <c r="BS19" t="n">
         <v>3.2</v>
       </c>
-      <c r="BT17" t="n">
+      <c r="BT19" t="n">
         <v>8.6</v>
       </c>
-      <c r="BU17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BV17" t="n">
+      <c r="BU19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV19" t="n">
         <v>34</v>
       </c>
-      <c r="BW17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BX17" t="n">
+      <c r="BW19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BX19" t="n">
         <v>50</v>
       </c>
-      <c r="BY17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BZ17" t="n">
+      <c r="BY19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BZ19" t="n">
         <v>0</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CA19" t="n">
         <v>0</v>
       </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-06-16 02:39:49</t>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-16 04:48:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fort Wayne FC</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-16 04:48:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -848,121 +848,121 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kairat Almaty</t>
+          <t>Grindavik</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FK Kyzyl-Zhar</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.16</v>
+        <v>3.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="H2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" t="n">
         <v>1.23</v>
       </c>
-      <c r="I2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.13</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>1.13</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="R2" t="n">
-        <v>1.09</v>
+        <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>1.27</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AP2" t="n">
         <v>1.01</v>
@@ -1019,75 +1019,75 @@
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.66</v>
+        <v>1.98</v>
       </c>
       <c r="G3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.8</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="V3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="BN3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW3" t="n">
         <v>3.25</v>
       </c>
-      <c r="T3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="BX3" t="n">
         <v>32</v>
       </c>
-      <c r="AF3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="BY3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>16</v>
       </c>
-      <c r="AY3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,36 +1351,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Kairat Almaty</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>FK Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.16</v>
       </c>
       <c r="G4" t="n">
-        <v>1.82</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,34 +1389,34 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>1.13</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>1.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="S4" t="n">
-        <v>2.72</v>
+        <v>1.27</v>
       </c>
       <c r="T4" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
         <v>1000</v>
@@ -1446,10 +1446,10 @@
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1458,13 +1458,13 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
         <v>1000</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1581,21 +1581,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.5</v>
+        <v>1.08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.69</v>
+        <v>1.07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.74</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>1.52</v>
       </c>
       <c r="T5" t="n">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>2.34</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,28 +1864,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Iberia 1999</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Rustavi</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,34 +1897,34 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>2.24</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,121 +2372,121 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L8" t="n">
         <v>1.2</v>
       </c>
-      <c r="G8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="O8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.18</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>2.52</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
         <v>1.01</v>
@@ -2498,7 +2498,7 @@
         <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
         <v>1.01</v>
@@ -2510,7 +2510,7 @@
         <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
         <v>1.01</v>
@@ -2534,7 +2534,7 @@
         <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2543,68 +2543,68 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
@@ -2668,13 +2668,13 @@
         <v>1.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>1.74</v>
       </c>
       <c r="J10" t="n">
-        <v>1.05</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>2.34</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,72 +3129,72 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>1.09</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>2.24</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3209,7 +3209,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC11" t="n">
         <v>1000</v>
@@ -3224,10 +3224,10 @@
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -3236,13 +3236,13 @@
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
         <v>1000</v>
@@ -3251,112 +3251,112 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>2.66</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>1.29</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.13</v>
+        <v>1.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.12</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,39 +3637,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>FC Iberia 1999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>FC Rustavi</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>990</v>
       </c>
       <c r="H13" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="I13" t="n">
-        <v>1.22</v>
+        <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>6.8</v>
+        <v>1.08</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
@@ -3678,210 +3678,210 @@
         <v>1.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.06</v>
+        <v>1.09</v>
       </c>
       <c r="S13" t="n">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>4.5</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,78 +3891,78 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
       <c r="G14" t="n">
-        <v>1.63</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2</v>
+        <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
         <v>1.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>1.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.07</v>
       </c>
       <c r="S14" t="n">
-        <v>1.98</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>2.56</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3971,10 +3971,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3983,142 +3983,142 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.65</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.76</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.76</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.75</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.76</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.75</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.86</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.72</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.72</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.76</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4180,25 +4180,25 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -4375,21 +4375,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FK Kauno Zalgiris</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>1.22</v>
       </c>
       <c r="J16" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>2.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>1.07</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>1.07</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
-        <v>1.21</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,234 +4907,234 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.44</v>
+        <v>1.1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>2.92</v>
+        <v>1.1</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>1.24</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,234 +5161,234 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.58</v>
+        <v>1.07</v>
       </c>
       <c r="G19" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>2.88</v>
+        <v>1.07</v>
       </c>
       <c r="I19" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="O19" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>3.55</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.59</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,261 +5398,1023 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-16 04:48:14</t>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Georgian Umaglesi Liga</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Torpedo Kutaisi</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dinamo Batumi</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>990</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I20" t="n">
+        <v>990</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K20" t="n">
+        <v>950</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-16 06:57:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-16 06:57:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-16 06:57:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>US USL League One</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Forward Madison FC</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Fort Wayne FC</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="F23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O23" t="n">
         <v>1.3</v>
       </c>
-      <c r="T20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>2026-06-16 04:48:14</t>
+      <c r="P23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>26</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-16 06:57:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,13 +896,13 @@
         <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
         <v>2.2</v>
@@ -923,7 +923,7 @@
         <v>23</v>
       </c>
       <c r="AB2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AC2" t="n">
         <v>13.5</v>
@@ -932,7 +932,7 @@
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF2" t="n">
         <v>50</v>
@@ -965,58 +965,58 @@
         <v>8.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
@@ -1028,59 +1028,59 @@
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN2" t="n">
         <v>9</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP2" t="n">
         <v>36</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>5</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BV2" t="n">
         <v>11.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX2" t="n">
         <v>21</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>14</v>
       </c>
       <c r="CA2" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J3" t="n">
         <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
@@ -1156,7 +1156,7 @@
         <v>1.45</v>
       </c>
       <c r="U3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V3" t="n">
         <v>1.37</v>
@@ -1174,7 +1174,7 @@
         <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
         <v>21</v>
@@ -1198,7 +1198,7 @@
         <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
         <v>32</v>
@@ -1216,19 +1216,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -1243,7 +1243,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1264,77 +1264,77 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>65</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BS3" t="n">
         <v>7</v>
       </c>
-      <c r="BG3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR3" t="n">
+      <c r="BT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX3" t="n">
         <v>26</v>
       </c>
-      <c r="BS3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>32</v>
-      </c>
       <c r="BY3" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.98</v>
+        <v>5.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -1371,16 +1371,16 @@
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,22 +1389,22 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.27</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1416,7 +1416,7 @@
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.08</v>
+        <v>1.87</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.07</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>2.48</v>
       </c>
       <c r="O5" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>2.58</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.52</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG5" t="n">
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1864,31 +1864,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.93</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>2.96</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,34 +1897,34 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.18</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2035,75 +2035,75 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,121 +2118,121 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>2.82</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>2.68</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>1.34</v>
+        <v>2.32</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="P7" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>2.24</v>
+        <v>1.54</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP7" t="n">
         <v>1.01</v>
@@ -2262,7 +2262,7 @@
         <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ7" t="n">
         <v>1.01</v>
@@ -2289,75 +2289,75 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,121 +2372,121 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1.64</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.02</v>
       </c>
-      <c r="N8" t="n">
+      <c r="W8" t="n">
         <v>1.02</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.52</v>
-      </c>
       <c r="X8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
         <v>1.01</v>
@@ -2498,7 +2498,7 @@
         <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
         <v>1.01</v>
@@ -2510,7 +2510,7 @@
         <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
         <v>1.01</v>
@@ -2534,7 +2534,7 @@
         <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2543,75 +2543,75 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2</v>
+        <v>2.66</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.68</v>
+        <v>1.34</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>2.24</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="I10" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>2.88</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>1.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.86</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,67 +3134,67 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>FC Iberia 1999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>FC Rustavi</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.74</v>
+        <v>1.09</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8</v>
+        <v>990</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
-        <v>5.3</v>
+        <v>990</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>2.02</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>1.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="S11" t="n">
-        <v>2.72</v>
+        <v>1.39</v>
       </c>
       <c r="T11" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3209,7 +3209,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
         <v>1000</v>
@@ -3224,10 +3224,10 @@
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -3236,13 +3236,13 @@
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
         <v>1000</v>
@@ -3251,58 +3251,58 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3359,14 +3359,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -3388,229 +3388,229 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.66</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.86</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.68</v>
+        <v>1.69</v>
       </c>
       <c r="I12" t="n">
-        <v>2.88</v>
+        <v>1.74</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U12" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.28</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>2.34</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AA12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI12" t="n">
         <v>44</v>
       </c>
-      <c r="AB12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AJ12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU12" t="n">
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY12" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,67 +3642,67 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FC Iberia 1999</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Rustavi</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.07</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>990</v>
+        <v>1.76</v>
       </c>
       <c r="H13" t="n">
-        <v>1.07</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>990</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>1.09</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3717,22 +3717,22 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF13" t="n">
         <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
         <v>1000</v>
@@ -3741,13 +3741,13 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -3759,129 +3759,129 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,234 +3891,234 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.08</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="H14" t="n">
-        <v>1.08</v>
+        <v>2.68</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.09</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.31</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N15" t="n">
         <v>1.1</v>
       </c>
-      <c r="G15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
         <v>1.3</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,244 +4399,244 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.18</v>
+        <v>2.64</v>
       </c>
       <c r="I16" t="n">
-        <v>1.22</v>
+        <v>3.05</v>
       </c>
       <c r="J16" t="n">
-        <v>6.8</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
         <v>10</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>65</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>220</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>270</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>180</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>250</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BG16" t="n">
-        <v>2.44</v>
+        <v>21</v>
       </c>
       <c r="BH16" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="BI16" t="n">
-        <v>4.1</v>
+        <v>2.64</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BT16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT16" t="n">
+      <c r="BU16" t="n">
         <v>4.4</v>
       </c>
-      <c r="BU16" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BV16" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="BX16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paide Linnameeskond</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="I17" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>1.09</v>
       </c>
       <c r="K17" t="n">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.32</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>2.66</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>19</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
         <v>1.1</v>
       </c>
-      <c r="G18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="O18" t="n">
         <v>1.1</v>
       </c>
-      <c r="I18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.24</v>
-      </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>2.12</v>
       </c>
       <c r="S18" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ18" t="n">
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,229 +5166,229 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FK Kauno Zalgiris</t>
+          <t>Paide Linnameeskond</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.07</v>
+        <v>1.51</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>1.59</v>
       </c>
       <c r="H19" t="n">
-        <v>1.07</v>
+        <v>5.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M19" t="n">
         <v>1.03</v>
       </c>
-      <c r="K19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N19" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>2.46</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,36 +5415,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="G20" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="I20" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5456,19 +5456,19 @@
         <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5537,52 +5537,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -5594,72 +5594,72 @@
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,234 +5669,234 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.54</v>
+        <v>1.6</v>
       </c>
       <c r="G21" t="n">
-        <v>2.68</v>
+        <v>1.77</v>
       </c>
       <c r="H21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
         <v>2.94</v>
       </c>
-      <c r="I21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.85</v>
-      </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
         <v>1.98</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="X21" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,498 +5923,1006 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.46</v>
+        <v>1.09</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56</v>
+        <v>990</v>
       </c>
       <c r="H22" t="n">
-        <v>2.92</v>
+        <v>1.09</v>
       </c>
       <c r="I22" t="n">
-        <v>3.05</v>
+        <v>990</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>1.09</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.82</v>
+        <v>1.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>1.22</v>
       </c>
       <c r="T22" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-16 06:57:01</t>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:06:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:06:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>US USL League One</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Forward Madison FC</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Fort Wayne FC</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="F25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I25" t="n">
         <v>4.6</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>3.35</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>4</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="L25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O25" t="n">
         <v>1.3</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>1.35</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO25" t="n">
         <v>3.25</v>
       </c>
-      <c r="T23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X23" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z23" t="n">
+      <c r="BP25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV25" t="n">
         <v>36</v>
       </c>
-      <c r="AA23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="BW25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BZ25" t="n">
         <v>26</v>
       </c>
-      <c r="AK23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>21</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>25</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>26</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>2026-06-16 06:57:01</t>
+      <c r="CA25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:06:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="G2" t="n">
         <v>5.2</v>
@@ -869,7 +869,7 @@
         <v>1.84</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
@@ -890,19 +890,19 @@
         <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
         <v>1.57</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
         <v>2.2</v>
@@ -917,7 +917,7 @@
         <v>16</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA2" t="n">
         <v>23</v>
@@ -929,10 +929,10 @@
         <v>13.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="n">
         <v>50</v>
@@ -959,64 +959,64 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AO2" t="n">
         <v>8.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.8</v>
+        <v>17.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.65</v>
+        <v>12.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.9</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.1</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
@@ -1040,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BP2" t="n">
         <v>36</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
         <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
         <v>4.8</v>
@@ -1141,7 +1141,7 @@
         <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q3" t="n">
         <v>1.42</v>
@@ -1156,46 +1156,46 @@
         <v>1.45</v>
       </c>
       <c r="U3" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC3" t="n">
         <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI3" t="n">
         <v>32</v>
@@ -1204,7 +1204,7 @@
         <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>28</v>
@@ -1219,7 +1219,7 @@
         <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>19.5</v>
@@ -1228,7 +1228,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -1264,13 +1264,13 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="n">
         <v>5.2</v>
@@ -1282,25 +1282,25 @@
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL3" t="n">
         <v>65</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN3" t="n">
         <v>5.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP3" t="n">
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
         <v>20</v>
@@ -1312,10 +1312,10 @@
         <v>7.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW3" t="n">
         <v>7.4</v>
@@ -1324,7 +1324,7 @@
         <v>26</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>12.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.42</v>
       </c>
       <c r="H4" t="n">
-        <v>1.54</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.02</v>
+        <v>5.2</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.18</v>
+        <v>2.12</v>
       </c>
       <c r="O4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.18</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
         <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>3.35</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
         <v>3.75</v>
@@ -1640,67 +1640,67 @@
         <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.48</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.58</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
         <v>34</v>
@@ -1712,7 +1712,7 @@
         <v>30</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
         <v>80</v>
@@ -1721,128 +1721,128 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.6</v>
+        <v>3.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="AU5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BN5" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH5" t="n">
+      <c r="BO5" t="n">
         <v>3.2</v>
       </c>
-      <c r="BI5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -1864,67 +1864,67 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.93</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>1.54</v>
       </c>
       <c r="I6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>2.96</v>
+        <v>1.13</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.06</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2035,68 +2035,68 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -2169,10 +2169,10 @@
         <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -2193,22 +2193,22 @@
         <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
@@ -2235,58 +2235,58 @@
         <v>100</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH7" t="n">
         <v>2.68</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -2381,220 +2381,220 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O8" t="n">
         <v>1.2</v>
       </c>
-      <c r="G8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.18</v>
-      </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H9" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2662,13 +2662,13 @@
         <v>1.34</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
         <v>1.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -2880,239 +2880,239 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV10" t="n">
         <v>4.4</v>
       </c>
-      <c r="G10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.09</v>
+        <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>990</v>
+        <v>2.04</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>990</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.02</v>
       </c>
-      <c r="K11" t="n">
-        <v>950</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>5.5</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I12" t="n">
         <v>1.74</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.31</v>
@@ -3436,7 +3436,7 @@
         <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
         <v>1.87</v>
@@ -3445,7 +3445,7 @@
         <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="W12" t="n">
         <v>1.2</v>
@@ -3457,7 +3457,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
         <v>18.5</v>
@@ -3529,7 +3529,7 @@
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY12" t="n">
         <v>18.5</v>
@@ -3541,19 +3541,19 @@
         <v>6.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG12" t="n">
         <v>8.6</v>
@@ -3568,7 +3568,7 @@
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,7 +3580,7 @@
         <v>9.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
@@ -3598,13 +3598,13 @@
         <v>4.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV12" t="n">
         <v>12</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="BX12" t="n">
         <v>27</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H13" t="n">
         <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
         <v>4.6</v>
@@ -3675,196 +3675,196 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
         <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
         <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
         <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.46</v>
+        <v>17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.46</v>
+        <v>17.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.47</v>
+        <v>23</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="AT13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>1.46</v>
+        <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.37</v>
+        <v>15.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.47</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.41</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.46</v>
+        <v>8</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -3926,13 +3926,13 @@
         <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
         <v>3.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
         <v>2.06</v>
@@ -3944,13 +3944,13 @@
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
         <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
         <v>1.53</v>
@@ -3989,7 +3989,7 @@
         <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
         <v>50</v>
@@ -4010,7 +4010,7 @@
         <v>26</v>
       </c>
       <c r="AO14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AP14" t="n">
         <v>13.5</v>
@@ -4049,22 +4049,22 @@
         <v>29</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BC14" t="n">
         <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>28</v>
+        <v>5.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF14" t="n">
         <v>20</v>
       </c>
       <c r="BG14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BH14" t="n">
         <v>3.65</v>
@@ -4106,7 +4106,7 @@
         <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BV14" t="n">
         <v>22</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="G15" t="n">
         <v>1.77</v>
@@ -4168,46 +4168,46 @@
         <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S15" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
         <v>2.28</v>
@@ -4261,128 +4261,128 @@
         <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AO15" t="n">
         <v>42</v>
       </c>
       <c r="AP15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR15" t="n">
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
         <v>3.95</v>
       </c>
-      <c r="AS15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H16" t="n">
         <v>2.6</v>
       </c>
-      <c r="G16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.64</v>
-      </c>
       <c r="I16" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
         <v>3.75</v>
@@ -4437,7 +4437,7 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
         <v>1.33</v>
@@ -4446,25 +4446,25 @@
         <v>1.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
@@ -4482,10 +4482,10 @@
         <v>13.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
         <v>40</v>
@@ -4506,7 +4506,7 @@
         <v>55</v>
       </c>
       <c r="AK16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL16" t="n">
         <v>55</v>
@@ -4518,61 +4518,61 @@
         <v>36</v>
       </c>
       <c r="AO16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH16" t="n">
         <v>3.4</v>
@@ -4584,34 +4584,34 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO16" t="n">
         <v>5</v>
       </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>2.98</v>
+        <v>7.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU16" t="n">
         <v>4.4</v>
@@ -4620,13 +4620,13 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.98</v>
+        <v>7.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
         <v>19</v>
@@ -4933,7 +4933,7 @@
         <v>1.22</v>
       </c>
       <c r="J18" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="K18" t="n">
         <v>10</v>
@@ -4945,13 +4945,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q18" t="n">
         <v>1.29</v>
@@ -4969,7 +4969,7 @@
         <v>1.94</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
         <v>1.05</v>
@@ -5029,55 +5029,55 @@
         <v>2.74</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AX18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY18" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY18" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC18" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BD18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG18" t="n">
         <v>2.44</v>
@@ -5092,7 +5092,7 @@
         <v>13</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5122,13 +5122,13 @@
         <v>4.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="BV18" t="n">
         <v>6.4</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BX18" t="n">
         <v>18.5</v>
@@ -5140,11 +5140,11 @@
         <v>6.2</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -5181,13 +5181,13 @@
         <v>1.59</v>
       </c>
       <c r="H19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K19" t="n">
         <v>5.7</v>
@@ -5199,13 +5199,13 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
         <v>1.58</v>
@@ -5214,7 +5214,7 @@
         <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
         <v>1.74</v>
@@ -5223,7 +5223,7 @@
         <v>2.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W19" t="n">
         <v>2.68</v>
@@ -5253,13 +5253,13 @@
         <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AG19" t="n">
         <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>80</v>
@@ -5277,82 +5277,82 @@
         <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO19" t="n">
         <v>90</v>
       </c>
       <c r="AP19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD19" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BE19" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH19" t="n">
         <v>4.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.77</v>
+        <v>12</v>
       </c>
       <c r="BN19" t="n">
         <v>4.4</v>
@@ -5361,7 +5361,7 @@
         <v>3.5</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BQ19" t="n">
         <v>5.6</v>
@@ -5370,25 +5370,25 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.77</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>2.68</v>
+        <v>5.9</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -5429,220 +5429,220 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.1</v>
+        <v>2.22</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1</v>
+        <v>2.86</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>1.24</v>
+        <v>2.78</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -5683,25 +5683,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G21" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H21" t="n">
         <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
@@ -5719,22 +5719,22 @@
         <v>1.98</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V21" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -5937,58 +5937,58 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="G22" t="n">
-        <v>990</v>
+        <v>1.69</v>
       </c>
       <c r="H22" t="n">
-        <v>1.09</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>990</v>
+        <v>8.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.09</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="O22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>1.22</v>
+        <v>2.72</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,244 +6177,244 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Utsiktens</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.58</v>
+        <v>1.06</v>
       </c>
       <c r="G23" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>2.94</v>
+        <v>1.06</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K23" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>1.27</v>
       </c>
       <c r="O23" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>1.19</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>3.55</v>
+        <v>1.18</v>
       </c>
       <c r="T23" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
@@ -6436,229 +6436,229 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="G24" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H24" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.85</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="U24" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="V24" t="n">
         <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X24" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y24" t="n">
         <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD24" t="n">
         <v>13.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AF24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR24" t="n">
         <v>18</v>
       </c>
-      <c r="AG24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO24" t="n">
+      <c r="AS24" t="n">
         <v>26</v>
       </c>
-      <c r="AP24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>36</v>
-      </c>
       <c r="AT24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
         <v>15</v>
       </c>
       <c r="AY24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BB24" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BC24" t="n">
         <v>21</v>
       </c>
       <c r="BD24" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BG24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ24" t="n">
         <v>9.4</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR24" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BS24" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV24" t="n">
         <v>23</v>
       </c>
       <c r="BW24" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX24" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-16 09:06:36</t>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,244 +6685,498 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Forward Madison FC</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fort Wayne FC</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="H25" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="J25" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
         <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="V25" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="X25" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AB25" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AG25" t="n">
         <v>12.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AJ25" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AK25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL25" t="n">
         <v>44</v>
       </c>
       <c r="AM25" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AN25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR25" t="n">
         <v>17.5</v>
       </c>
-      <c r="AO25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="BJ25" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO25" t="n">
         <v>4.9</v>
       </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BP25" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BQ25" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BR25" t="n">
         <v>30</v>
       </c>
       <c r="BS25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW25" t="n">
         <v>7.2</v>
       </c>
-      <c r="BT25" t="n">
+      <c r="BX25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY25" t="n">
         <v>7.8</v>
       </c>
-      <c r="BU25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV25" t="n">
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Fort Wayne FC</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X26" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z26" t="n">
         <v>36</v>
       </c>
-      <c r="BW25" t="n">
+      <c r="AA26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT26" t="n">
         <v>7.4</v>
       </c>
-      <c r="BX25" t="n">
+      <c r="AU26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX26" t="n">
         <v>46</v>
       </c>
-      <c r="BY25" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BZ25" t="n">
+      <c r="BY26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ26" t="n">
         <v>26</v>
       </c>
-      <c r="CA25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>2026-06-16 09:06:36</t>
+      <c r="CA26" t="n">
+        <v>7</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -878,7 +878,7 @@
         <v>1.23</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
         <v>5.7</v>
@@ -896,13 +896,13 @@
         <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T2" t="n">
         <v>1.57</v>
       </c>
       <c r="U2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
         <v>2.2</v>
@@ -959,7 +959,7 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AO2" t="n">
         <v>8.4</v>
@@ -977,7 +977,7 @@
         <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AU2" t="n">
         <v>9.199999999999999</v>
@@ -995,7 +995,7 @@
         <v>16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
         <v>21</v>
@@ -1040,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="BO2" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP2" t="n">
         <v>36</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
         <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
         <v>4.8</v>
@@ -1159,7 +1159,7 @@
         <v>2.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
         <v>1.81</v>
@@ -1177,7 +1177,7 @@
         <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC3" t="n">
         <v>13.5</v>
@@ -1189,7 +1189,7 @@
         <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
@@ -1204,7 +1204,7 @@
         <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
         <v>28</v>
@@ -1219,7 +1219,7 @@
         <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ3" t="n">
         <v>19.5</v>
@@ -1228,7 +1228,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -1264,13 +1264,13 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH3" t="n">
         <v>5.2</v>
@@ -1294,7 +1294,7 @@
         <v>5.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
         <v>14</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>22</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>320</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>580</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI4" t="n">
         <v>2.8</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G5" t="n">
         <v>2.06</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.48</v>
@@ -1643,10 +1643,10 @@
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P5" t="n">
         <v>1.5</v>
@@ -1655,22 +1655,22 @@
         <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
         <v>5.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1679,7 +1679,7 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1691,7 +1691,7 @@
         <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1703,7 +1703,7 @@
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1727,82 +1727,82 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.88</v>
+        <v>4.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.72</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BN5" t="n">
         <v>5.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,10 +1814,10 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU5" t="n">
         <v>4.9</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -1873,40 +1873,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J6" t="n">
-        <v>1.13</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.54</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
         <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1921,10 +1921,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2130,28 +2130,28 @@
         <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="K7" t="n">
         <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.57</v>
@@ -2160,16 +2160,16 @@
         <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
         <v>1.71</v>
@@ -2178,16 +2178,16 @@
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="n">
         <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
         <v>90</v>
@@ -2199,7 +2199,7 @@
         <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
         <v>70</v>
@@ -2235,61 +2235,61 @@
         <v>100</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="n">
         <v>5.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC7" t="n">
         <v>5.3</v>
       </c>
-      <c r="BB7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BI7" t="n">
         <v>2.2</v>
@@ -2298,16 +2298,16 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="BN7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BO7" t="n">
         <v>4.1</v>
@@ -2316,13 +2316,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.96</v>
+        <v>7</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>2</v>
+        <v>7.8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.06</v>
+        <v>2.94</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.04</v>
+        <v>2.94</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2381,220 +2381,220 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="I8" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.52</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.51</v>
-      </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC8" t="n">
         <v>12</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
         <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN8" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AO8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>8.4</v>
       </c>
-      <c r="AP8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.3</v>
+        <v>15.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BU8" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>48</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3</v>
-      </c>
       <c r="BV8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX8" t="n">
         <v>23</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="G9" t="n">
         <v>1.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2656,25 +2656,25 @@
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>1.34</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.34</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>1.05</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2683,7 +2683,7 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
         <v>2.66</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
@@ -2913,40 +2913,40 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="O10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
         <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X10" t="n">
         <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z10" t="n">
         <v>55</v>
@@ -2955,22 +2955,22 @@
         <v>270</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE10" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG10" t="n">
         <v>11</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13</v>
       </c>
       <c r="AH10" t="n">
         <v>28</v>
@@ -2982,73 +2982,73 @@
         <v>19.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
         <v>65</v>
       </c>
       <c r="AM10" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO10" t="n">
         <v>260</v>
       </c>
-      <c r="AN10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>270</v>
-      </c>
       <c r="AP10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT10" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AU10" t="n">
-        <v>3.25</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.4</v>
+        <v>16</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="n">
         <v>3.05</v>
@@ -3060,13 +3060,13 @@
         <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN10" t="n">
         <v>4.2</v>
@@ -3078,10 +3078,10 @@
         <v>13.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS10" t="n">
         <v>8.199999999999999</v>
@@ -3090,7 +3090,7 @@
         <v>10</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3102,17 +3102,17 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10" t="n">
         <v>34</v>
       </c>
       <c r="CA10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3149,10 +3149,10 @@
         <v>2.04</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -3161,7 +3161,7 @@
         <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
@@ -3173,7 +3173,7 @@
         <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="Q11" t="n">
         <v>2.26</v>
@@ -3188,7 +3188,7 @@
         <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V11" t="n">
         <v>1.19</v>
@@ -3308,7 +3308,7 @@
         <v>3.05</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ11" t="n">
         <v>11.5</v>
@@ -3347,7 +3347,7 @@
         <v>4.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW11" t="n">
         <v>2.3</v>
@@ -3359,14 +3359,14 @@
         <v>2.32</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA11" t="n">
         <v>8.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
         <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I12" t="n">
         <v>1.74</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
@@ -3433,34 +3433,34 @@
         <v>1.86</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
         <v>3.15</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="W12" t="n">
         <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
         <v>21</v>
@@ -3529,7 +3529,7 @@
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY12" t="n">
         <v>18.5</v>
@@ -3538,22 +3538,22 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB12" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB12" t="n">
-        <v>7</v>
-      </c>
       <c r="BC12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE12" t="n">
         <v>6.6</v>
       </c>
-      <c r="BD12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF12" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
         <v>8.6</v>
@@ -3604,7 +3604,7 @@
         <v>12</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX12" t="n">
         <v>27</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H13" t="n">
         <v>5</v>
@@ -3666,7 +3666,7 @@
         <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,25 +3675,25 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
         <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U13" t="n">
         <v>2.24</v>
@@ -3702,97 +3702,97 @@
         <v>1.23</v>
       </c>
       <c r="W13" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X13" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Z13" t="n">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
         <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL13" t="n">
         <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>370</v>
+        <v>470</v>
       </c>
       <c r="AP13" t="n">
         <v>17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="BB13" t="n">
         <v>15.5</v>
@@ -3801,16 +3801,16 @@
         <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BF13" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.7</v>
+        <v>29</v>
       </c>
       <c r="BH13" t="n">
         <v>4.1</v>
@@ -3822,49 +3822,49 @@
         <v>10</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13" t="n">
         <v>4.7</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ13" t="n">
         <v>5.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS13" t="n">
         <v>7</v>
       </c>
       <c r="BT13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G14" t="n">
         <v>2.86</v>
       </c>
       <c r="H14" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I14" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
         <v>3.7</v>
@@ -3941,22 +3941,22 @@
         <v>1.89</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.53</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.54</v>
       </c>
       <c r="X14" t="n">
         <v>15.5</v>
@@ -3965,7 +3965,7 @@
         <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
         <v>55</v>
@@ -3980,37 +3980,37 @@
         <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
         <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK14" t="n">
         <v>32</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP14" t="n">
         <v>13.5</v>
@@ -4022,7 +4022,7 @@
         <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -4046,25 +4046,25 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BC14" t="n">
         <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH14" t="n">
         <v>3.65</v>
@@ -4082,13 +4082,13 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN14" t="n">
         <v>6.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BP14" t="n">
         <v>22</v>
@@ -4100,7 +4100,7 @@
         <v>34</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT14" t="n">
         <v>6.2</v>
@@ -4118,7 +4118,7 @@
         <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>1.66</v>
       </c>
       <c r="G15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
         <v>4.5</v>
@@ -4210,7 +4210,7 @@
         <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
@@ -4267,37 +4267,37 @@
         <v>42</v>
       </c>
       <c r="AP15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR15" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AS15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT15" t="n">
         <v>10.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AV15" t="n">
         <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>4.5</v>
@@ -4309,16 +4309,16 @@
         <v>11.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BF15" t="n">
         <v>4.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -4413,64 +4413,64 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I16" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
         <v>23</v>
@@ -4479,25 +4479,25 @@
         <v>55</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG16" t="n">
         <v>15.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
         <v>55</v>
@@ -4506,46 +4506,46 @@
         <v>55</v>
       </c>
       <c r="AK16" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL16" t="n">
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>9.4</v>
       </c>
       <c r="AR16" t="n">
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
         <v>10.5</v>
@@ -4554,46 +4554,46 @@
         <v>10</v>
       </c>
       <c r="BA16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF16" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.1</v>
       </c>
       <c r="BG16" t="n">
         <v>20</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO16" t="n">
         <v>5</v>
@@ -4602,16 +4602,16 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="BT16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU16" t="n">
         <v>4.4</v>
@@ -4620,13 +4620,13 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -4694,19 +4694,19 @@
         <v>1.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P17" t="n">
         <v>1.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4715,7 +4715,7 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W17" t="n">
         <v>1.02</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>1.22</v>
       </c>
       <c r="J18" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="K18" t="n">
         <v>10</v>
@@ -4945,7 +4945,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.1</v>
@@ -4957,16 +4957,16 @@
         <v>1.29</v>
       </c>
       <c r="R18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="T18" t="n">
         <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
         <v>5.5</v>
@@ -4975,7 +4975,7 @@
         <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Y18" t="n">
         <v>17</v>
@@ -4987,7 +4987,7 @@
         <v>11</v>
       </c>
       <c r="AB18" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AC18" t="n">
         <v>23</v>
@@ -4996,7 +4996,7 @@
         <v>14</v>
       </c>
       <c r="AE18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF18" t="n">
         <v>220</v>
@@ -5008,7 +5008,7 @@
         <v>36</v>
       </c>
       <c r="AI18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ18" t="n">
         <v>1000</v>
@@ -5029,7 +5029,7 @@
         <v>2.74</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
         <v>14</v>
@@ -5041,7 +5041,7 @@
         <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU18" t="n">
         <v>19</v>
@@ -5053,7 +5053,7 @@
         <v>11.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
         <v>9.199999999999999</v>
@@ -5065,22 +5065,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BB18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC18" t="n">
         <v>10</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BD18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BD18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BF18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BH18" t="n">
         <v>6.4</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -5181,16 +5181,16 @@
         <v>1.59</v>
       </c>
       <c r="H19" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
         <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.25</v>
@@ -5199,7 +5199,7 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
         <v>1.2</v>
@@ -5214,7 +5214,7 @@
         <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
         <v>1.74</v>
@@ -5259,10 +5259,10 @@
         <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
         <v>970</v>
@@ -5283,37 +5283,37 @@
         <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS19" t="n">
         <v>5.3</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU19" t="n">
         <v>3.85</v>
       </c>
       <c r="AV19" t="n">
-        <v>19</v>
+        <v>4.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.7</v>
+        <v>9.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.95</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA19" t="n">
         <v>5.1</v>
@@ -5322,7 +5322,7 @@
         <v>4.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD19" t="n">
         <v>4.7</v>
@@ -5334,7 +5334,7 @@
         <v>3.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH19" t="n">
         <v>4.4</v>
@@ -5358,7 +5358,7 @@
         <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP19" t="n">
         <v>9.4</v>
@@ -5370,7 +5370,7 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -5429,88 +5429,88 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="H20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I20" t="n">
         <v>2.86</v>
       </c>
-      <c r="I20" t="n">
-        <v>3.45</v>
-      </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="U20" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W20" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD20" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>15</v>
-      </c>
       <c r="AE20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>17</v>
@@ -5519,130 +5519,130 @@
         <v>42</v>
       </c>
       <c r="AJ20" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO20" t="n">
         <v>26</v>
       </c>
-      <c r="AL20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>27</v>
-      </c>
       <c r="AP20" t="n">
-        <v>5.4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.7</v>
+        <v>15.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="BH20" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.4</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BR20" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BS20" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BW20" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX20" t="n">
         <v>34</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
@@ -5704,7 +5704,7 @@
         <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
         <v>2.94</v>
@@ -5731,7 +5731,7 @@
         <v>1.7</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
         <v>2.32</v>
@@ -5791,52 +5791,52 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="G22" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="H22" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L22" t="n">
         <v>1.34</v>
@@ -5961,16 +5961,16 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.02</v>
+        <v>1.37</v>
       </c>
       <c r="O22" t="n">
         <v>1.23</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.68</v>
+        <v>1.23</v>
       </c>
       <c r="R22" t="n">
         <v>1.36</v>
@@ -5979,16 +5979,16 @@
         <v>2.72</v>
       </c>
       <c r="T22" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
         <v>1.93</v>
       </c>
       <c r="V22" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W22" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -6191,112 +6191,112 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.06</v>
+        <v>6.8</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>1.27</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.19</v>
       </c>
       <c r="P23" t="n">
-        <v>1.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>1.18</v>
+        <v>2.26</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>2.92</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AP23" t="n">
         <v>1.01</v>
@@ -6353,68 +6353,68 @@
         <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G24" t="n">
         <v>2.6</v>
@@ -6469,7 +6469,7 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.33</v>
@@ -6481,7 +6481,7 @@
         <v>1.98</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
         <v>3.55</v>
@@ -6520,7 +6520,7 @@
         <v>13.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AF24" t="n">
         <v>21</v>
@@ -6529,7 +6529,7 @@
         <v>14.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI24" t="n">
         <v>55</v>
@@ -6553,7 +6553,7 @@
         <v>36</v>
       </c>
       <c r="AP24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>11</v>
@@ -6571,7 +6571,7 @@
         <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
@@ -6616,28 +6616,28 @@
         <v>9.4</v>
       </c>
       <c r="BK24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN24" t="n">
         <v>5.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BP24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ24" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BR24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS24" t="n">
         <v>10.5</v>
@@ -6646,19 +6646,19 @@
         <v>6.2</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX24" t="n">
         <v>36</v>
       </c>
       <c r="BY24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G25" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H25" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I25" t="n">
         <v>3.05</v>
@@ -6714,10 +6714,10 @@
         <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -6735,13 +6735,13 @@
         <v>1.82</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
         <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="U25" t="n">
         <v>2.32</v>
@@ -6870,13 +6870,13 @@
         <v>9.4</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN25" t="n">
         <v>5.9</v>
@@ -6888,13 +6888,13 @@
         <v>19</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR25" t="n">
         <v>30</v>
       </c>
       <c r="BS25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT25" t="n">
         <v>6.4</v>
@@ -6906,10 +6906,10 @@
         <v>23</v>
       </c>
       <c r="BW25" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY25" t="n">
         <v>7.8</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="H26" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L26" t="n">
         <v>1.39</v>
@@ -6983,52 +6983,52 @@
         <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
         <v>3.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U26" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="X26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z26" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA26" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB26" t="n">
         <v>11</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
         <v>15</v>
@@ -7040,7 +7040,7 @@
         <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
         <v>29</v>
@@ -7052,13 +7052,13 @@
         <v>44</v>
       </c>
       <c r="AM26" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN26" t="n">
         <v>17.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
         <v>11</v>
@@ -7067,13 +7067,13 @@
         <v>11.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU26" t="n">
         <v>6.4</v>
@@ -7088,13 +7088,13 @@
         <v>10</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ26" t="n">
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
         <v>18.5</v>
@@ -7103,80 +7103,80 @@
         <v>16.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
         <v>11.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
         <v>3.55</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BJ26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BP26" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>27</v>
+      </c>
+      <c r="CA26" t="n">
         <v>7.4</v>
       </c>
-      <c r="BT26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ26" t="n">
-        <v>26</v>
-      </c>
-      <c r="CA26" t="n">
-        <v>7</v>
-      </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-16 11:17:21</t>
+          <t>2026-06-16 13:41:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -866,43 +866,43 @@
         <v>1.67</v>
       </c>
       <c r="I2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J2" t="n">
         <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
         <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V2" t="n">
         <v>2.2</v>
@@ -914,7 +914,7 @@
         <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
         <v>14.5</v>
@@ -932,7 +932,7 @@
         <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF2" t="n">
         <v>50</v>
@@ -956,13 +956,13 @@
         <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
         <v>46</v>
       </c>
       <c r="AO2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP2" t="n">
         <v>20</v>
@@ -971,10 +971,10 @@
         <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="AS2" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AT2" t="n">
         <v>20</v>
@@ -986,76 +986,76 @@
         <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
         <v>16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>30</v>
+        <v>5.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG2" t="n">
         <v>6</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>9</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU2" t="n">
         <v>3.75</v>
@@ -1064,23 +1064,23 @@
         <v>11.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX2" t="n">
         <v>21</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>3.35</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
         <v>4.8</v>
@@ -1135,34 +1135,34 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="Q3" t="n">
         <v>1.42</v>
       </c>
       <c r="R3" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
         <v>1.45</v>
       </c>
       <c r="U3" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V3" t="n">
         <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
@@ -1174,7 +1174,7 @@
         <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
         <v>21</v>
@@ -1183,7 +1183,7 @@
         <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
         <v>32</v>
@@ -1204,22 +1204,22 @@
         <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AM3" t="n">
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>19.5</v>
@@ -1228,7 +1228,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -1264,31 +1264,31 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
         <v>14</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>5.9</v>
@@ -1297,44 +1297,44 @@
         <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR3" t="n">
         <v>20</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT3" t="n">
         <v>7.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>23</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX3" t="n">
         <v>26</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -1398,16 +1398,16 @@
         <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
         <v>1.6</v>
@@ -1476,43 +1476,43 @@
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS4" t="n">
         <v>5.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
         <v>5.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB4" t="n">
         <v>9</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="BD4" t="n">
         <v>4.9</v>
@@ -1521,7 +1521,7 @@
         <v>5.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
         <v>5.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.48</v>
@@ -1664,13 +1664,13 @@
         <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1730,7 +1730,7 @@
         <v>6.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
         <v>4.6</v>
@@ -1781,7 +1781,7 @@
         <v>2.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="BI5" t="n">
         <v>2.24</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.75</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BN5" t="n">
         <v>5.8</v>
@@ -1808,13 +1808,13 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BT5" t="n">
         <v>11.5</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
         <v>5.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
         <v>5.1</v>
@@ -1894,13 +1894,13 @@
         <v>1.54</v>
       </c>
       <c r="M6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
         <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P6" t="n">
         <v>1.45</v>
@@ -1921,7 +1921,7 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="W6" t="n">
         <v>1.21</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H7" t="n">
         <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K7" t="n">
         <v>3.25</v>
@@ -2160,25 +2160,25 @@
         <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
         <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X7" t="n">
         <v>9</v>
@@ -2193,10 +2193,10 @@
         <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
         <v>19</v>
@@ -2208,7 +2208,7 @@
         <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
@@ -2244,7 +2244,7 @@
         <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT7" t="n">
         <v>5.9</v>
@@ -2256,7 +2256,7 @@
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX7" t="n">
         <v>11.5</v>
@@ -2268,25 +2268,25 @@
         <v>18</v>
       </c>
       <c r="BA7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB7" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB7" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BC7" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BE7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF7" t="n">
         <v>5.7</v>
       </c>
-      <c r="BF7" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH7" t="n">
         <v>2.7</v>
@@ -2295,7 +2295,7 @@
         <v>2.2</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK7" t="n">
         <v>5.5</v>
@@ -2304,10 +2304,10 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.12</v>
+        <v>5.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="BO7" t="n">
         <v>4.1</v>
@@ -2325,7 +2325,7 @@
         <v>6.2</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU7" t="n">
         <v>4</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         <v>5.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
@@ -2399,13 +2399,13 @@
         <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.21</v>
@@ -2414,13 +2414,13 @@
         <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
         <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
         <v>1.65</v>
@@ -2429,13 +2429,13 @@
         <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W8" t="n">
         <v>1.23</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
         <v>13.5</v>
@@ -2447,7 +2447,7 @@
         <v>19.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC8" t="n">
         <v>12</v>
@@ -2459,25 +2459,25 @@
         <v>17.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AG8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
         <v>95</v>
@@ -2513,7 +2513,7 @@
         <v>12.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY8" t="n">
         <v>14</v>
@@ -2525,22 +2525,22 @@
         <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC8" t="n">
         <v>38</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="n">
         <v>4.3</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -2638,22 +2638,22 @@
         <v>1.51</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2683,10 +2683,10 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
         <v>1.82</v>
@@ -2904,7 +2904,7 @@
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
@@ -2916,13 +2916,13 @@
         <v>2.86</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P10" t="n">
         <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
@@ -2946,7 +2946,7 @@
         <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z10" t="n">
         <v>55</v>
@@ -3006,10 +3006,10 @@
         <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AU10" t="n">
         <v>7.2</v>
@@ -3033,22 +3033,22 @@
         <v>7.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="BC10" t="n">
         <v>16</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
         <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="n">
         <v>3.05</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -3149,10 +3149,10 @@
         <v>2.04</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -3173,7 +3173,7 @@
         <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
         <v>2.26</v>
@@ -3188,10 +3188,10 @@
         <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.96</v>
@@ -3263,7 +3263,7 @@
         <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AU11" t="n">
         <v>3.3</v>
@@ -3275,7 +3275,7 @@
         <v>4.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AY11" t="n">
         <v>3.65</v>
@@ -3347,7 +3347,7 @@
         <v>4.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
         <v>2.3</v>
@@ -3359,14 +3359,14 @@
         <v>2.32</v>
       </c>
       <c r="BZ11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
         <v>8.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>5.5</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I12" t="n">
         <v>1.74</v>
@@ -3421,7 +3421,7 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>1.29</v>
@@ -3472,7 +3472,7 @@
         <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AF12" t="n">
         <v>60</v>
@@ -3484,7 +3484,7 @@
         <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
         <v>180</v>
@@ -3538,7 +3538,7 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB12" t="n">
         <v>6.6</v>
@@ -3553,10 +3553,10 @@
         <v>6.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12" t="n">
         <v>3.75</v>
@@ -3598,13 +3598,13 @@
         <v>4.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BV12" t="n">
         <v>12</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX12" t="n">
         <v>27</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="G13" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,7 +3675,7 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.24</v>
@@ -3684,7 +3684,7 @@
         <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
         <v>1.52</v>
@@ -3696,13 +3696,13 @@
         <v>1.76</v>
       </c>
       <c r="U13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="X13" t="n">
         <v>21</v>
@@ -3723,25 +3723,25 @@
         <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
         <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK13" t="n">
         <v>16</v>
@@ -3750,16 +3750,16 @@
         <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AO13" t="n">
-        <v>470</v>
+        <v>680</v>
       </c>
       <c r="AP13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ13" t="n">
         <v>18.5</v>
@@ -3768,7 +3768,7 @@
         <v>24</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
@@ -3780,7 +3780,7 @@
         <v>17.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3792,10 +3792,10 @@
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC13" t="n">
         <v>14</v>
@@ -3804,22 +3804,22 @@
         <v>22</v>
       </c>
       <c r="BE13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK13" t="n">
         <v>5</v>
@@ -3828,43 +3828,43 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BR13" t="n">
         <v>24</v>
       </c>
       <c r="BS13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU13" t="n">
         <v>4.8</v>
       </c>
       <c r="BV13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G14" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H14" t="n">
         <v>2.66</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>1.32</v>
@@ -3929,7 +3929,7 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
@@ -3938,25 +3938,25 @@
         <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
         <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X14" t="n">
         <v>15.5</v>
@@ -3965,7 +3965,7 @@
         <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
         <v>55</v>
@@ -3974,13 +3974,13 @@
         <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
         <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF14" t="n">
         <v>21</v>
@@ -3989,7 +3989,7 @@
         <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
         <v>42</v>
@@ -4010,22 +4010,22 @@
         <v>25</v>
       </c>
       <c r="AO14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP14" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
         <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU14" t="n">
         <v>7.2</v>
@@ -4034,37 +4034,37 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AX14" t="n">
         <v>16</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
         <v>32</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BC14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BF14" t="n">
         <v>17.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH14" t="n">
         <v>3.65</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H15" t="n">
         <v>4.5</v>
@@ -4174,43 +4174,43 @@
         <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="S15" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U15" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
@@ -4225,7 +4225,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AC15" t="n">
         <v>970</v>
@@ -4237,7 +4237,7 @@
         <v>60</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
         <v>970</v>
@@ -4255,7 +4255,7 @@
         <v>970</v>
       </c>
       <c r="AL15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM15" t="n">
         <v>70</v>
@@ -4264,43 +4264,43 @@
         <v>7.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
         <v>10.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AV15" t="n">
         <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
         <v>13.5</v>
@@ -4309,22 +4309,22 @@
         <v>11.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BI15" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>3.85</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4336,25 +4336,25 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.06</v>
+        <v>2</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.07</v>
+        <v>1.85</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H16" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -4443,7 +4443,7 @@
         <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
         <v>1.92</v>
@@ -4455,16 +4455,16 @@
         <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
         <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
         <v>17.5</v>
@@ -4473,13 +4473,13 @@
         <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
         <v>55</v>
       </c>
       <c r="AB16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC16" t="n">
         <v>8.4</v>
@@ -4491,7 +4491,7 @@
         <v>38</v>
       </c>
       <c r="AF16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG16" t="n">
         <v>15.5</v>
@@ -4530,7 +4530,7 @@
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -4542,7 +4542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
@@ -4554,22 +4554,22 @@
         <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF16" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.2</v>
       </c>
       <c r="BG16" t="n">
         <v>20</v>
@@ -4584,7 +4584,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>6.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -4945,13 +4945,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q18" t="n">
         <v>1.29</v>
@@ -4975,13 +4975,13 @@
         <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Y18" t="n">
         <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA18" t="n">
         <v>11</v>
@@ -5002,7 +5002,7 @@
         <v>220</v>
       </c>
       <c r="AG18" t="n">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AH18" t="n">
         <v>36</v>
@@ -5029,7 +5029,7 @@
         <v>2.74</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ18" t="n">
         <v>14</v>
@@ -5041,7 +5041,7 @@
         <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
         <v>19</v>
@@ -5053,10 +5053,10 @@
         <v>11.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
         <v>9.199999999999999</v>
@@ -5065,19 +5065,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BB18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC18" t="n">
         <v>10.5</v>
       </c>
-      <c r="BC18" t="n">
-        <v>10</v>
-      </c>
       <c r="BD18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG18" t="n">
         <v>2.46</v>
@@ -5086,7 +5086,7 @@
         <v>6.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ18" t="n">
         <v>13</v>
@@ -5098,28 +5098,28 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN18" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU18" t="n">
         <v>3.8</v>
@@ -5134,7 +5134,7 @@
         <v>18.5</v>
       </c>
       <c r="BY18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>6.2</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -5184,13 +5184,13 @@
         <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J19" t="n">
         <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.25</v>
@@ -5208,7 +5208,7 @@
         <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R19" t="n">
         <v>1.58</v>
@@ -5262,7 +5262,7 @@
         <v>950</v>
       </c>
       <c r="AI19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
         <v>970</v>
@@ -5292,7 +5292,7 @@
         <v>5.1</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -5358,7 +5358,7 @@
         <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BP19" t="n">
         <v>9.4</v>
@@ -5370,7 +5370,7 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>15.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -5429,43 +5429,43 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="G20" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I20" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="J20" t="n">
         <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
         <v>1.29</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
         <v>3.15</v>
@@ -5477,22 +5477,22 @@
         <v>2.2</v>
       </c>
       <c r="V20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.53</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.54</v>
       </c>
       <c r="X20" t="n">
         <v>16</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB20" t="n">
         <v>12.5</v>
@@ -5501,7 +5501,7 @@
         <v>8.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>32</v>
@@ -5519,10 +5519,10 @@
         <v>42</v>
       </c>
       <c r="AJ20" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL20" t="n">
         <v>40</v>
@@ -5531,7 +5531,7 @@
         <v>95</v>
       </c>
       <c r="AN20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
@@ -5546,7 +5546,7 @@
         <v>15.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT20" t="n">
         <v>9.4</v>
@@ -5558,7 +5558,7 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX20" t="n">
         <v>13.5</v>
@@ -5570,19 +5570,19 @@
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
         <v>15</v>
@@ -5591,10 +5591,10 @@
         <v>19</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.4</v>
@@ -5606,43 +5606,43 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
         <v>6.2</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV20" t="n">
         <v>22</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX20" t="n">
         <v>34</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
         <v>1.64</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I22" t="n">
         <v>8</v>
@@ -5961,22 +5961,22 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="O22" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="R22" t="n">
         <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T22" t="n">
         <v>1.83</v>
@@ -5985,7 +5985,7 @@
         <v>1.93</v>
       </c>
       <c r="V22" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
         <v>2.56</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -6191,31 +6191,31 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O23" t="n">
         <v>1.19</v>
@@ -6230,157 +6230,157 @@
         <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="V23" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
         <v>29</v>
       </c>
       <c r="Y23" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD23" t="n">
         <v>12</v>
       </c>
-      <c r="Z23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE23" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AF23" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AG23" t="n">
         <v>40</v>
       </c>
       <c r="AH23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI23" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ23" t="n">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="AK23" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AL23" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM23" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN23" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH23" t="n">
         <v>4.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>6.4</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
@@ -6389,13 +6389,13 @@
         <v>6.4</v>
       </c>
       <c r="BT23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU23" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BV23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW23" t="n">
         <v>3.95</v>
@@ -6404,17 +6404,17 @@
         <v>24</v>
       </c>
       <c r="BY23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BZ23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA23" t="n">
         <v>4.6</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K24" t="n">
         <v>3.65</v>
@@ -6469,13 +6469,13 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
         <v>1.98</v>
@@ -6520,7 +6520,7 @@
         <v>13.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF24" t="n">
         <v>21</v>
@@ -6541,7 +6541,7 @@
         <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -6553,10 +6553,10 @@
         <v>36</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR24" t="n">
         <v>18</v>
@@ -6598,7 +6598,7 @@
         <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF24" t="n">
         <v>20</v>
@@ -6628,7 +6628,7 @@
         <v>5.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP24" t="n">
         <v>19.5</v>
@@ -6646,7 +6646,7 @@
         <v>6.2</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV24" t="n">
         <v>24</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
         <v>2.56</v>
       </c>
       <c r="H25" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I25" t="n">
         <v>3.05</v>
@@ -6714,10 +6714,10 @@
         <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -6729,22 +6729,22 @@
         <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
         <v>1.82</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
         <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V25" t="n">
         <v>1.48</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN25" t="n">
         <v>5.9</v>
@@ -6888,13 +6888,13 @@
         <v>19</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR25" t="n">
         <v>30</v>
       </c>
       <c r="BS25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT25" t="n">
         <v>6.4</v>
@@ -6906,10 +6906,10 @@
         <v>23</v>
       </c>
       <c r="BW25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY25" t="n">
         <v>7.8</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         <v>2.36</v>
       </c>
       <c r="H26" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I26" t="n">
         <v>4.1</v>
@@ -7064,55 +7064,55 @@
         <v>11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV26" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ26" t="n">
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>18.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC26" t="n">
-        <v>16.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.05</v>
+        <v>5.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH26" t="n">
         <v>3.55</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-16 13:41:22</t>
+          <t>2026-06-16 15:50:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G2" t="n">
         <v>5.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="I2" t="n">
         <v>1.83</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.22</v>
@@ -893,7 +893,7 @@
         <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S2" t="n">
         <v>2.28</v>
@@ -989,7 +989,7 @@
         <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AY2" t="n">
         <v>16</v>
@@ -1004,10 +1004,10 @@
         <v>5.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE2" t="n">
         <v>5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
         <v>2.24</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
         <v>4.2</v>
@@ -1135,31 +1135,31 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="U3" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
         <v>1.8</v>
@@ -1168,7 +1168,7 @@
         <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z3" t="n">
         <v>32</v>
@@ -1198,28 +1198,28 @@
         <v>15.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ3" t="n">
         <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
       </c>
       <c r="AM3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AN3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
         <v>19.5</v>
@@ -1228,7 +1228,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -1252,7 +1252,7 @@
         <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="BB3" t="n">
         <v>9.199999999999999</v>
@@ -1264,19 +1264,19 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="n">
         <v>5.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.6</v>
@@ -1288,13 +1288,13 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP3" t="n">
         <v>13.5</v>
@@ -1303,38 +1303,38 @@
         <v>5.9</v>
       </c>
       <c r="BR3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS3" t="n">
         <v>6.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU3" t="n">
         <v>5.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW3" t="n">
         <v>7.2</v>
       </c>
       <c r="BX3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY3" t="n">
         <v>7.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V4" t="n">
         <v>1.08</v>
@@ -1476,7 +1476,7 @@
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
         <v>5.3</v>
@@ -1494,7 +1494,7 @@
         <v>5</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX4" t="n">
         <v>6</v>
@@ -1515,10 +1515,10 @@
         <v>4.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
         <v>6.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -1625,16 +1625,16 @@
         <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.48</v>
@@ -1652,7 +1652,7 @@
         <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
         <v>1.19</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
         <v>1.85</v>
@@ -1885,10 +1885,10 @@
         <v>2.06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.54</v>
@@ -1927,7 +1927,7 @@
         <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K7" t="n">
         <v>3.25</v>
@@ -2151,7 +2151,7 @@
         <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
         <v>1.57</v>
@@ -2175,10 +2175,10 @@
         <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X7" t="n">
         <v>9</v>
@@ -2199,7 +2199,7 @@
         <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>70</v>
@@ -2220,7 +2220,7 @@
         <v>50</v>
       </c>
       <c r="AK7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL7" t="n">
         <v>85</v>
@@ -2244,49 +2244,49 @@
         <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="AV7" t="n">
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX7" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18</v>
+        <v>5.4</v>
       </c>
       <c r="BA7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB7" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB7" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BC7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF7" t="n">
         <v>6</v>
       </c>
-      <c r="BF7" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="n">
         <v>2.7</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>5.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I8" t="n">
         <v>1.83</v>
@@ -2501,7 +2501,7 @@
         <v>13.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AU8" t="n">
         <v>7.4</v>
@@ -2513,7 +2513,7 @@
         <v>12.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY8" t="n">
         <v>14</v>
@@ -2534,7 +2534,7 @@
         <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF8" t="n">
         <v>6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="G9" t="n">
         <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.27</v>
@@ -2689,7 +2689,7 @@
         <v>2.72</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
@@ -3039,7 +3039,7 @@
         <v>16</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE10" t="n">
         <v>7.8</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -3149,16 +3149,16 @@
         <v>2.04</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
         <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
         <v>1.49</v>
@@ -3263,7 +3263,7 @@
         <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AU11" t="n">
         <v>3.3</v>
@@ -3275,7 +3275,7 @@
         <v>4.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AY11" t="n">
         <v>3.65</v>
@@ -3347,7 +3347,7 @@
         <v>4.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW11" t="n">
         <v>2.3</v>
@@ -3359,14 +3359,14 @@
         <v>2.32</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA11" t="n">
         <v>8.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G12" t="n">
         <v>6.2</v>
@@ -3442,16 +3442,16 @@
         <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
         <v>2.34</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y12" t="n">
         <v>9.199999999999999</v>
@@ -3541,13 +3541,13 @@
         <v>6.2</v>
       </c>
       <c r="BB12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC12" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC12" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE12" t="n">
         <v>6.6</v>
@@ -3568,49 +3568,49 @@
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BV12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="BX12" t="n">
         <v>27</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="n">
         <v>4.4</v>
@@ -3675,40 +3675,40 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="T13" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z13" t="n">
         <v>46</v>
@@ -3717,7 +3717,7 @@
         <v>140</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC13" t="n">
         <v>10.5</v>
@@ -3741,10 +3741,10 @@
         <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL13" t="n">
         <v>32</v>
@@ -3753,37 +3753,37 @@
         <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>680</v>
+        <v>640</v>
       </c>
       <c r="AP13" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AR13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY13" t="n">
         <v>9.199999999999999</v>
@@ -3795,22 +3795,22 @@
         <v>30</v>
       </c>
       <c r="BB13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
         <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BE13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G14" t="n">
         <v>2.84</v>
       </c>
       <c r="H14" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="I14" t="n">
         <v>2.82</v>
@@ -3926,7 +3926,7 @@
         <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
         <v>4</v>
@@ -3938,10 +3938,10 @@
         <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
         <v>3.3</v>
@@ -3968,7 +3968,7 @@
         <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB14" t="n">
         <v>12.5</v>
@@ -3995,7 +3995,7 @@
         <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK14" t="n">
         <v>32</v>
@@ -4010,7 +4010,7 @@
         <v>25</v>
       </c>
       <c r="AO14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP14" t="n">
         <v>13.5</v>
@@ -4022,7 +4022,7 @@
         <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT14" t="n">
         <v>11</v>
@@ -4031,16 +4031,16 @@
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX14" t="n">
         <v>16</v>
       </c>
       <c r="AY14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
         <v>14.5</v>
@@ -4064,7 +4064,7 @@
         <v>17.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH14" t="n">
         <v>3.65</v>
@@ -4076,49 +4076,49 @@
         <v>9.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN14" t="n">
         <v>6.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP14" t="n">
         <v>22</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR14" t="n">
         <v>34</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU14" t="n">
         <v>4.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX14" t="n">
         <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -4183,19 +4183,19 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S15" t="n">
         <v>2.08</v>
@@ -4279,7 +4279,7 @@
         <v>5</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="AU15" t="n">
         <v>3.95</v>
@@ -4300,13 +4300,13 @@
         <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
         <v>4.5</v>
@@ -4315,7 +4315,7 @@
         <v>4.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BG15" t="n">
         <v>4.9</v>
@@ -4339,7 +4339,7 @@
         <v>2</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO15" t="n">
         <v>3.8</v>
@@ -4348,7 +4348,7 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
@@ -4378,11 +4378,11 @@
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H16" t="n">
         <v>2.64</v>
@@ -4464,7 +4464,7 @@
         <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X16" t="n">
         <v>17.5</v>
@@ -4482,7 +4482,7 @@
         <v>14</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>15</v>
@@ -4503,7 +4503,7 @@
         <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AK16" t="n">
         <v>36</v>
@@ -4530,7 +4530,7 @@
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -4542,7 +4542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
@@ -4554,22 +4554,22 @@
         <v>10</v>
       </c>
       <c r="BA16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF16" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG16" t="n">
         <v>20</v>
@@ -4590,10 +4590,10 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO16" t="n">
         <v>5</v>
@@ -4602,31 +4602,31 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT16" t="n">
         <v>6.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -4670,16 +4670,16 @@
         <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.09</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
         <v>950</v>
@@ -4691,22 +4691,22 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4715,10 +4715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -4930,16 +4930,16 @@
         <v>1.18</v>
       </c>
       <c r="I18" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="J18" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
         <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
@@ -4969,7 +4969,7 @@
         <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W18" t="n">
         <v>1.05</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
         <v>1.59</v>
@@ -5313,7 +5313,7 @@
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA19" t="n">
         <v>5.1</v>
@@ -5322,7 +5322,7 @@
         <v>4.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BD19" t="n">
         <v>4.7</v>
@@ -5346,7 +5346,7 @@
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G20" t="n">
         <v>2.9</v>
@@ -5438,13 +5438,13 @@
         <v>2.66</v>
       </c>
       <c r="I20" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.38</v>
@@ -5462,7 +5462,7 @@
         <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
         <v>1.37</v>
@@ -5477,7 +5477,7 @@
         <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
         <v>1.53</v>
@@ -5546,7 +5546,7 @@
         <v>15.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AT20" t="n">
         <v>9.4</v>
@@ -5558,7 +5558,7 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20" t="n">
         <v>13.5</v>
@@ -5573,7 +5573,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
@@ -5606,10 +5606,10 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO20" t="n">
         <v>5</v>
@@ -5618,31 +5618,31 @@
         <v>21</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT20" t="n">
         <v>6.2</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV20" t="n">
         <v>22</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX20" t="n">
         <v>34</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
         <v>2.32</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="G22" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
         <v>8</v>
@@ -5955,7 +5955,7 @@
         <v>5.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
@@ -5985,13 +5985,13 @@
         <v>1.93</v>
       </c>
       <c r="V22" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W22" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -6191,40 +6191,40 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="G23" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="H23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="I23" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.19</v>
       </c>
       <c r="P23" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R23" t="n">
         <v>1.51</v>
@@ -6233,169 +6233,169 @@
         <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="U23" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="V23" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
         <v>29</v>
       </c>
       <c r="Y23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z23" t="n">
         <v>11</v>
       </c>
-      <c r="Z23" t="n">
-        <v>10</v>
-      </c>
       <c r="AA23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB23" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AC23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>290</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL23" t="n">
         <v>110</v>
       </c>
-      <c r="AG23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>390</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL23" t="n">
+      <c r="AM23" t="n">
         <v>140</v>
       </c>
-      <c r="AM23" t="n">
-        <v>160</v>
-      </c>
       <c r="AN23" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="AO23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB23" t="n">
         <v>5.8</v>
       </c>
-      <c r="AP23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>6</v>
-      </c>
       <c r="BC23" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH23" t="n">
         <v>4.7</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BJ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BN23" t="n">
         <v>12.5</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BO23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT23" t="n">
         <v>4.5</v>
       </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BU23" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BV23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BW23" t="n">
         <v>3.95</v>
@@ -6404,17 +6404,17 @@
         <v>24</v>
       </c>
       <c r="BY23" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BZ23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CA23" t="n">
         <v>4.6</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G24" t="n">
         <v>2.6</v>
@@ -6463,34 +6463,34 @@
         <v>3.65</v>
       </c>
       <c r="L24" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R24" t="n">
         <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V24" t="n">
         <v>1.48</v>
@@ -6538,7 +6538,7 @@
         <v>46</v>
       </c>
       <c r="AK24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL24" t="n">
         <v>48</v>
@@ -6553,7 +6553,7 @@
         <v>36</v>
       </c>
       <c r="AP24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>10.5</v>
@@ -6571,7 +6571,7 @@
         <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
@@ -6580,7 +6580,7 @@
         <v>15</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
         <v>15</v>
@@ -6601,22 +6601,22 @@
         <v>7.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG24" t="n">
         <v>19</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK24" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
@@ -6628,13 +6628,13 @@
         <v>5.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR24" t="n">
         <v>32</v>
@@ -6649,13 +6649,13 @@
         <v>5.4</v>
       </c>
       <c r="BV24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW24" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY24" t="n">
         <v>11</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
         <v>2.56</v>
@@ -6714,7 +6714,7 @@
         <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
         <v>1.31</v>
@@ -6735,7 +6735,7 @@
         <v>1.82</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
         <v>3.05</v>
@@ -6744,7 +6744,7 @@
         <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V25" t="n">
         <v>1.48</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN25" t="n">
         <v>5.9</v>
@@ -6888,13 +6888,13 @@
         <v>19</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR25" t="n">
         <v>30</v>
       </c>
       <c r="BS25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT25" t="n">
         <v>6.4</v>
@@ -6906,10 +6906,10 @@
         <v>23</v>
       </c>
       <c r="BW25" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY25" t="n">
         <v>7.8</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>
@@ -7064,10 +7064,10 @@
         <v>11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AS26" t="n">
         <v>5.5</v>
@@ -7076,7 +7076,7 @@
         <v>7.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AV26" t="n">
         <v>4.4</v>
@@ -7094,7 +7094,7 @@
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB26" t="n">
         <v>4.9</v>
@@ -7103,10 +7103,10 @@
         <v>4.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF26" t="n">
         <v>4.4</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-16 15:50:53</t>
+          <t>2026-06-16 18:00:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -887,22 +887,22 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
         <v>1.58</v>
       </c>
       <c r="U2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V2" t="n">
         <v>2.2</v>
@@ -920,49 +920,49 @@
         <v>14.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AB2" t="n">
         <v>26</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
         <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF2" t="n">
         <v>50</v>
       </c>
       <c r="AG2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
         <v>32</v>
       </c>
       <c r="AJ2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK2" t="n">
         <v>120</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>60</v>
       </c>
       <c r="AL2" t="n">
         <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AN2" t="n">
         <v>46</v>
       </c>
       <c r="AO2" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AP2" t="n">
         <v>20</v>
@@ -971,7 +971,7 @@
         <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
         <v>13.5</v>
@@ -989,7 +989,7 @@
         <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2" t="n">
         <v>16</v>
@@ -1001,19 +1001,19 @@
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BG2" t="n">
         <v>6</v>
@@ -1022,13 +1022,13 @@
         <v>4.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1058,13 +1058,13 @@
         <v>5.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BV2" t="n">
         <v>11.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>21</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.21</v>
@@ -1135,34 +1135,34 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="T3" t="n">
         <v>1.43</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
@@ -1195,7 +1195,7 @@
         <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
         <v>30</v>
@@ -1207,28 +1207,28 @@
         <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM3" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP3" t="n">
         <v>16</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7</v>
       </c>
       <c r="AQ3" t="n">
         <v>19.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -1240,7 +1240,7 @@
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AX3" t="n">
         <v>16</v>
@@ -1255,7 +1255,7 @@
         <v>19</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>16</v>
@@ -1264,7 +1264,7 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>6.8</v>
@@ -1273,7 +1273,7 @@
         <v>11.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BI3" t="n">
         <v>4.6</v>
@@ -1282,10 +1282,10 @@
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM3" t="n">
         <v>9</v>
@@ -1294,7 +1294,7 @@
         <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BP3" t="n">
         <v>13.5</v>
@@ -1309,10 +1309,10 @@
         <v>6.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV3" t="n">
         <v>22</v>
@@ -1330,11 +1330,11 @@
         <v>12</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
         <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
@@ -1407,10 +1407,10 @@
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
         <v>1.08</v>
@@ -1422,10 +1422,10 @@
         <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1437,7 +1437,7 @@
         <v>14.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AE4" t="n">
         <v>320</v>
@@ -1449,13 +1449,13 @@
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
         <v>260</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
@@ -1479,52 +1479,52 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
         <v>5.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX4" t="n">
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
         <v>9</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
         <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="n">
         <v>3.7</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G5" t="n">
         <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
         <v>5.5</v>
@@ -1634,16 +1634,16 @@
         <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O5" t="n">
         <v>1.55</v>
@@ -1655,7 +1655,7 @@
         <v>2.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
         <v>5.5</v>
@@ -1673,58 +1673,58 @@
         <v>1.92</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>30</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
         <v>6.4</v>
@@ -1733,10 +1733,10 @@
         <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="AT5" t="n">
         <v>4.9</v>
@@ -1745,46 +1745,46 @@
         <v>5.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.9</v>
+        <v>2.82</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1796,25 +1796,25 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BT5" t="n">
         <v>11.5</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I6" t="n">
         <v>2.06</v>
       </c>
       <c r="J6" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.54</v>
@@ -1897,22 +1897,22 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
         <v>1.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1930,109 +1930,109 @@
         <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K7" t="n">
         <v>3.25</v>
@@ -2181,16 +2181,16 @@
         <v>1.56</v>
       </c>
       <c r="X7" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>7.8</v>
@@ -2199,40 +2199,40 @@
         <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AE7" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="AL7" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
         <v>6.2</v>
@@ -2244,49 +2244,49 @@
         <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AV7" t="n">
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7" t="n">
         <v>2.7</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
         <v>12.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
         <v>14</v>
@@ -2525,19 +2525,19 @@
         <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC8" t="n">
         <v>38</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG8" t="n">
         <v>7.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -2641,19 +2641,19 @@
         <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2665,7 +2665,7 @@
         <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
         <v>1.73</v>
@@ -2683,7 +2683,7 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
         <v>2.72</v>
@@ -2692,7 +2692,7 @@
         <v>950</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2701,7 +2701,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
         <v>1000</v>
@@ -2713,88 +2713,88 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -2889,46 +2889,46 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O10" t="n">
         <v>1.46</v>
       </c>
       <c r="P10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T10" t="n">
         <v>2.16</v>
@@ -2937,10 +2937,10 @@
         <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X10" t="n">
         <v>12.5</v>
@@ -2952,7 +2952,7 @@
         <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>270</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>6.8</v>
@@ -2967,7 +2967,7 @@
         <v>150</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2979,22 +2979,22 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
         <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AP10" t="n">
         <v>7.6</v>
@@ -3003,13 +3003,13 @@
         <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AU10" t="n">
         <v>7.2</v>
@@ -3018,7 +3018,7 @@
         <v>18.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX10" t="n">
         <v>7.8</v>
@@ -3030,7 +3030,7 @@
         <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -3042,40 +3042,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF10" t="n">
         <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH10" t="n">
         <v>3.05</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10" t="n">
         <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN10" t="n">
         <v>4.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ10" t="n">
         <v>9.6</v>
@@ -3084,7 +3084,7 @@
         <v>36</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT10" t="n">
         <v>10</v>
@@ -3093,26 +3093,26 @@
         <v>7.2</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>1.49</v>
@@ -3197,43 +3197,43 @@
         <v>1.96</v>
       </c>
       <c r="X11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
         <v>16.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AA11" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC11" t="n">
-        <v>9</v>
-      </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK11" t="n">
         <v>28</v>
@@ -3242,67 +3242,67 @@
         <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="AQ11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT11" t="n">
         <v>3.95</v>
       </c>
-      <c r="AR11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AU11" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BH11" t="n">
         <v>3.05</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G12" t="n">
         <v>6.2</v>
@@ -3406,10 +3406,10 @@
         <v>1.69</v>
       </c>
       <c r="I12" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
@@ -3442,13 +3442,13 @@
         <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
         <v>19.5</v>
@@ -3460,7 +3460,7 @@
         <v>10.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AB12" t="n">
         <v>21</v>
@@ -3481,25 +3481,25 @@
         <v>27</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>95</v>
+        <v>700</v>
       </c>
       <c r="AL12" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AM12" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AO12" t="n">
         <v>10.5</v>
@@ -3529,7 +3529,7 @@
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY12" t="n">
         <v>18.5</v>
@@ -3538,22 +3538,22 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG12" t="n">
         <v>8.800000000000001</v>
@@ -3568,7 +3568,7 @@
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3598,7 +3598,7 @@
         <v>4.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BV12" t="n">
         <v>11.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G13" t="n">
         <v>1.68</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I13" t="n">
         <v>5.7</v>
@@ -3684,7 +3684,7 @@
         <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R13" t="n">
         <v>1.55</v>
@@ -3702,10 +3702,10 @@
         <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y13" t="n">
         <v>25</v>
@@ -3714,7 +3714,7 @@
         <v>46</v>
       </c>
       <c r="AA13" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>11.5</v>
@@ -3735,31 +3735,31 @@
         <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
         <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
         <v>7.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>640</v>
+        <v>140</v>
       </c>
       <c r="AP13" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
         <v>21</v>
@@ -3768,13 +3768,13 @@
         <v>25</v>
       </c>
       <c r="AS13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
         <v>18.5</v>
@@ -3783,10 +3783,10 @@
         <v>32</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
         <v>16.5</v>
@@ -3795,7 +3795,7 @@
         <v>30</v>
       </c>
       <c r="BB13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC13" t="n">
         <v>14</v>
@@ -3804,7 +3804,7 @@
         <v>19</v>
       </c>
       <c r="BE13" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF13" t="n">
         <v>7</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN13" t="n">
         <v>4.6</v>
@@ -3840,16 +3840,16 @@
         <v>11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR13" t="n">
         <v>24</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU13" t="n">
         <v>4.8</v>
@@ -3864,7 +3864,7 @@
         <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H14" t="n">
         <v>2.72</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.74</v>
       </c>
       <c r="I14" t="n">
         <v>2.82</v>
@@ -3926,40 +3926,40 @@
         <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
         <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V14" t="n">
         <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="n">
         <v>12.5</v>
@@ -3974,7 +3974,7 @@
         <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>13</v>
@@ -3989,37 +3989,37 @@
         <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
         <v>24</v>
@@ -4031,10 +4031,10 @@
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX14" t="n">
         <v>16</v>
@@ -4043,82 +4043,82 @@
         <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BB14" t="n">
         <v>34</v>
       </c>
       <c r="BC14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF14" t="n">
         <v>17.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH14" t="n">
         <v>3.65</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BN14" t="n">
         <v>6.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP14" t="n">
         <v>22</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR14" t="n">
         <v>34</v>
       </c>
       <c r="BS14" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX14" t="n">
         <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.21</v>
@@ -4183,145 +4183,145 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="S15" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X15" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="Y15" t="n">
         <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB15" t="n">
         <v>17.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AE15" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="n">
         <v>17</v>
       </c>
       <c r="AG15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>970</v>
       </c>
-      <c r="AH15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>23</v>
-      </c>
       <c r="AK15" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AL15" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AM15" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
         <v>7.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI15" t="n">
         <v>4.5</v>
@@ -4342,7 +4342,7 @@
         <v>9</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="H16" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
         <v>3.8</v>
@@ -4434,154 +4434,154 @@
         <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="O16" t="n">
         <v>1.31</v>
       </c>
       <c r="P16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.92</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="U16" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W16" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X16" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AA16" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AE16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF16" t="n">
         <v>38</v>
       </c>
-      <c r="AF16" t="n">
-        <v>23</v>
-      </c>
       <c r="AG16" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
         <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO16" t="n">
         <v>44</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>32</v>
       </c>
       <c r="AP16" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
       </c>
       <c r="AY16" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA16" t="n">
         <v>10</v>
       </c>
-      <c r="BA16" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BB16" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK16" t="n">
         <v>7</v>
@@ -4626,7 +4626,7 @@
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -4670,10 +4670,10 @@
         <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
@@ -4691,13 +4691,13 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
         <v>1.14</v>
       </c>
       <c r="P17" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
         <v>1.14</v>
@@ -4718,7 +4718,7 @@
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4757,7 +4757,7 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -4936,16 +4936,16 @@
         <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.1</v>
@@ -4966,7 +4966,7 @@
         <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
         <v>5.8</v>
@@ -5020,16 +5020,16 @@
         <v>180</v>
       </c>
       <c r="AM18" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN18" t="n">
         <v>250</v>
       </c>
       <c r="AO18" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>14</v>
@@ -5041,7 +5041,7 @@
         <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU18" t="n">
         <v>19</v>
@@ -5053,31 +5053,31 @@
         <v>11.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA18" t="n">
         <v>9.4</v>
       </c>
-      <c r="AZ18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC18" t="n">
         <v>11</v>
       </c>
-      <c r="BC18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE18" t="n">
         <v>10.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG18" t="n">
         <v>2.46</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G19" t="n">
         <v>1.59</v>
@@ -5193,7 +5193,7 @@
         <v>5.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
         <v>1.03</v>
@@ -5205,19 +5205,19 @@
         <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R19" t="n">
         <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
         <v>2.16</v>
@@ -5235,25 +5235,25 @@
         <v>950</v>
       </c>
       <c r="Z19" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AD19" t="n">
         <v>950</v>
       </c>
       <c r="AE19" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AF19" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>12</v>
@@ -5262,16 +5262,16 @@
         <v>950</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ19" t="n">
         <v>970</v>
       </c>
       <c r="AK19" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL19" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -5283,28 +5283,28 @@
         <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX19" t="n">
         <v>9.4</v>
@@ -5313,58 +5313,58 @@
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC19" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BD19" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BH19" t="n">
         <v>4.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BK19" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN19" t="n">
         <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BP19" t="n">
         <v>9.4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
@@ -5376,19 +5376,19 @@
         <v>10.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -5429,70 +5429,70 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
         <v>2.66</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V20" t="n">
         <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB20" t="n">
         <v>12.5</v>
@@ -5513,28 +5513,28 @@
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AK20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL20" t="n">
         <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>95</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
         <v>12.5</v>
@@ -5552,7 +5552,7 @@
         <v>9.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
@@ -5570,7 +5570,7 @@
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB20" t="n">
         <v>8.4</v>
@@ -5579,10 +5579,10 @@
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF20" t="n">
         <v>15</v>
@@ -5591,13 +5591,13 @@
         <v>19</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="BJ20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
         <v>5.9</v>
@@ -5609,16 +5609,16 @@
         <v>10.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR20" t="n">
         <v>32</v>
@@ -5627,22 +5627,22 @@
         <v>8.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW20" t="n">
         <v>7.6</v>
       </c>
       <c r="BX20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -5686,19 +5686,19 @@
         <v>1.58</v>
       </c>
       <c r="G21" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="I21" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K21" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
         <v>1.33</v>
@@ -5707,13 +5707,13 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>2.94</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q21" t="n">
         <v>1.98</v>
@@ -5731,118 +5731,118 @@
         <v>1.7</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="W21" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -5952,16 +5952,16 @@
         <v>4.2</v>
       </c>
       <c r="K22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.25</v>
@@ -5994,109 +5994,109 @@
         <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
         <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.19</v>
@@ -6245,7 +6245,7 @@
         <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y23" t="n">
         <v>11.5</v>
@@ -6287,7 +6287,7 @@
         <v>140</v>
       </c>
       <c r="AL23" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AM23" t="n">
         <v>140</v>
@@ -6302,55 +6302,55 @@
         <v>4.9</v>
       </c>
       <c r="AQ23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR23" t="n">
         <v>3.9</v>
       </c>
-      <c r="AR23" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AS23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU23" t="n">
         <v>4.1</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC23" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC23" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BH23" t="n">
         <v>4.7</v>
@@ -6392,7 +6392,7 @@
         <v>4.5</v>
       </c>
       <c r="BU23" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="BV23" t="n">
         <v>9.4</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G24" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J24" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
         <v>3.65</v>
@@ -6472,10 +6472,10 @@
         <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
         <v>1.96</v>
@@ -6493,10 +6493,10 @@
         <v>2.24</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X24" t="n">
         <v>16.5</v>
@@ -6511,7 +6511,7 @@
         <v>60</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
         <v>7.8</v>
@@ -6541,7 +6541,7 @@
         <v>28</v>
       </c>
       <c r="AL24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
@@ -6568,13 +6568,13 @@
         <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
         <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
         <v>15</v>
@@ -6598,13 +6598,13 @@
         <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BF24" t="n">
         <v>19</v>
       </c>
       <c r="BG24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH24" t="n">
         <v>3.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -6702,10 +6702,10 @@
         <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H25" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="I25" t="n">
         <v>3.05</v>
@@ -6729,10 +6729,10 @@
         <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R25" t="n">
         <v>1.44</v>
@@ -6744,13 +6744,13 @@
         <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V25" t="n">
         <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X25" t="n">
         <v>17.5</v>
@@ -6777,10 +6777,10 @@
         <v>34</v>
       </c>
       <c r="AF25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>17</v>
@@ -6801,16 +6801,16 @@
         <v>90</v>
       </c>
       <c r="AN25" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO25" t="n">
         <v>26</v>
       </c>
       <c r="AP25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
         <v>17.5</v>
@@ -6819,7 +6819,7 @@
         <v>36</v>
       </c>
       <c r="AT25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU25" t="n">
         <v>7.4</v>
@@ -6837,7 +6837,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA25" t="n">
         <v>30</v>
@@ -6849,10 +6849,10 @@
         <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BF25" t="n">
         <v>16</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>
@@ -6995,16 +6995,16 @@
         <v>3.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X26" t="n">
         <v>16.5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-16 18:00:14</t>
+          <t>2026-06-16 20:09:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -1022,7 +1022,7 @@
         <v>4.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
         <v>2.2</v>
@@ -1120,7 +1120,7 @@
         <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
@@ -1159,7 +1159,7 @@
         <v>2.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
         <v>1.83</v>
@@ -1228,7 +1228,7 @@
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -1365,64 +1365,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
         <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="n">
         <v>540</v>
@@ -1437,13 +1437,13 @@
         <v>14.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AE4" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
@@ -1455,22 +1455,22 @@
         <v>260</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>580</v>
+        <v>520</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1479,61 +1479,61 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT4" t="n">
         <v>6</v>
       </c>
-      <c r="AT4" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AU4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW4" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.9</v>
       </c>
       <c r="AX4" t="n">
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD4" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK4" t="n">
         <v>5.6</v>
@@ -1545,10 +1545,10 @@
         <v>9</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BP4" t="n">
         <v>8.800000000000001</v>
@@ -1557,10 +1557,10 @@
         <v>4.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT4" t="n">
         <v>15</v>
@@ -1572,7 +1572,7 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
@@ -1581,14 +1581,14 @@
         <v>8.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CA4" t="n">
         <v>6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G5" t="n">
         <v>2.08</v>
@@ -1628,7 +1628,7 @@
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.1</v>
@@ -1736,7 +1736,7 @@
         <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AT5" t="n">
         <v>4.9</v>
@@ -1748,7 +1748,7 @@
         <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="AX5" t="n">
         <v>4.7</v>
@@ -1760,7 +1760,7 @@
         <v>6.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="BB5" t="n">
         <v>6.2</v>
@@ -1769,7 +1769,7 @@
         <v>6.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BE5" t="n">
         <v>3.55</v>
@@ -1778,7 +1778,7 @@
         <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
@@ -1796,13 +1796,13 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BN5" t="n">
         <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT5" t="n">
         <v>11.5</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="I6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J6" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.54</v>
@@ -1900,7 +1900,7 @@
         <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="P6" t="n">
         <v>1.45</v>
@@ -1921,13 +1921,13 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W6" t="n">
         <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Y6" t="n">
         <v>970</v>
@@ -1942,7 +1942,7 @@
         <v>950</v>
       </c>
       <c r="AC6" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD6" t="n">
         <v>950</v>
@@ -1978,61 +1978,61 @@
         <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>1.47</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.52</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.9</v>
+        <v>1.47</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AW6" t="n">
         <v>1.58</v>
       </c>
       <c r="AX6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.58</v>
       </c>
-      <c r="AY6" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.5</v>
+        <v>1.61</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
         <v>3.25</v>
@@ -2184,7 +2184,7 @@
         <v>8.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
         <v>90</v>
@@ -2265,7 +2265,7 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA7" t="n">
         <v>8</v>
@@ -2274,19 +2274,19 @@
         <v>7.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
         <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
         <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="n">
         <v>2.7</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>4.5</v>
       </c>
       <c r="G8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H8" t="n">
         <v>1.72</v>
@@ -2423,7 +2423,7 @@
         <v>2.58</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U8" t="n">
         <v>2.24</v>
@@ -2471,7 +2471,7 @@
         <v>36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
         <v>65</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
         <v>10.5</v>
@@ -2650,13 +2650,13 @@
         <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
         <v>3.25</v>
@@ -2794,7 +2794,7 @@
         <v>2.58</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.69</v>
       </c>
       <c r="G10" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="H10" t="n">
         <v>6.2</v>
@@ -2940,7 +2940,7 @@
         <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X10" t="n">
         <v>12.5</v>
@@ -3009,7 +3009,7 @@
         <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU10" t="n">
         <v>7.2</v>
@@ -3018,7 +3018,7 @@
         <v>18.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX10" t="n">
         <v>7.8</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
         <v>1.49</v>
@@ -3179,10 +3179,10 @@
         <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
         <v>2.02</v>
@@ -3239,7 +3239,7 @@
         <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
@@ -3263,13 +3263,13 @@
         <v>8</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW11" t="n">
         <v>7.8</v>
@@ -3290,13 +3290,13 @@
         <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD11" t="n">
         <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
         <v>5.9</v>
@@ -3359,14 +3359,14 @@
         <v>2.32</v>
       </c>
       <c r="BZ11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
         <v>8.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G12" t="n">
         <v>6.2</v>
@@ -3409,10 +3409,10 @@
         <v>1.72</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.31</v>
@@ -3430,13 +3430,13 @@
         <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
         <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
         <v>1.86</v>
@@ -3448,10 +3448,10 @@
         <v>2.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="n">
         <v>9.199999999999999</v>
@@ -3466,7 +3466,7 @@
         <v>21</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
         <v>10.5</v>
@@ -3481,7 +3481,7 @@
         <v>27</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>95</v>
@@ -3493,7 +3493,7 @@
         <v>700</v>
       </c>
       <c r="AL12" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
@@ -3523,13 +3523,13 @@
         <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
         <v>18.5</v>
@@ -3538,22 +3538,22 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC12" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC12" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
         <v>8.800000000000001</v>
@@ -3568,40 +3568,40 @@
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN12" t="n">
         <v>9.4</v>
       </c>
-      <c r="BN12" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BO12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BV12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW12" t="n">
         <v>5.4</v>
@@ -3610,7 +3610,7 @@
         <v>27</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -3678,22 +3678,22 @@
         <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
         <v>2.28</v>
@@ -3717,7 +3717,7 @@
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
         <v>10.5</v>
@@ -3726,10 +3726,10 @@
         <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
         <v>10</v>
@@ -3738,13 +3738,13 @@
         <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ13" t="n">
         <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL13" t="n">
         <v>30</v>
@@ -3756,10 +3756,10 @@
         <v>7.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>21</v>
@@ -3771,7 +3771,7 @@
         <v>12.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
         <v>9</v>
@@ -3801,13 +3801,13 @@
         <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BF13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG13" t="n">
         <v>29</v>
@@ -3816,19 +3816,19 @@
         <v>4.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN13" t="n">
         <v>4.6</v>
@@ -3840,10 +3840,10 @@
         <v>11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS13" t="n">
         <v>7</v>
@@ -3852,19 +3852,19 @@
         <v>9.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV13" t="n">
         <v>46</v>
       </c>
       <c r="BW13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G14" t="n">
         <v>2.82</v>
       </c>
       <c r="H14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I14" t="n">
         <v>2.82</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.32</v>
@@ -3983,7 +3983,7 @@
         <v>30</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG14" t="n">
         <v>13</v>
@@ -4031,10 +4031,10 @@
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX14" t="n">
         <v>16</v>
@@ -4052,7 +4052,7 @@
         <v>34</v>
       </c>
       <c r="BC14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD14" t="n">
         <v>24</v>
@@ -4070,13 +4070,13 @@
         <v>3.65</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4088,10 +4088,10 @@
         <v>6.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ14" t="n">
         <v>6.6</v>
@@ -4112,7 +4112,7 @@
         <v>22</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX14" t="n">
         <v>34</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
         <v>5.1</v>
@@ -4204,7 +4204,7 @@
         <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
@@ -4267,16 +4267,16 @@
         <v>500</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS15" t="n">
         <v>5.6</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.2</v>
       </c>
       <c r="AT15" t="n">
         <v>6.2</v>
@@ -4285,10 +4285,10 @@
         <v>5.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AW15" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AX15" t="n">
         <v>7.6</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H16" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I16" t="n">
         <v>2.94</v>
@@ -4455,13 +4455,13 @@
         <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U16" t="n">
         <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
         <v>1.54</v>
@@ -4488,7 +4488,7 @@
         <v>12.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AF16" t="n">
         <v>38</v>
@@ -4506,7 +4506,7 @@
         <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AL16" t="n">
         <v>500</v>
@@ -4515,7 +4515,7 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
         <v>44</v>
@@ -4566,13 +4566,13 @@
         <v>8</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="n">
         <v>3.55</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="H17" t="n">
         <v>2.04</v>
@@ -4718,7 +4718,7 @@
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4811,7 +4811,7 @@
         <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -4921,67 +4921,67 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L18" t="n">
         <v>1.19</v>
-      </c>
-      <c r="J18" t="n">
-        <v>9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.18</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R18" t="n">
         <v>2.14</v>
       </c>
       <c r="S18" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>65</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA18" t="n">
         <v>11</v>
@@ -4990,43 +4990,43 @@
         <v>95</v>
       </c>
       <c r="AC18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="n">
         <v>950</v>
       </c>
       <c r="AH18" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ18" t="n">
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AL18" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AM18" t="n">
         <v>500</v>
       </c>
       <c r="AN18" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AO18" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="AP18" t="n">
         <v>10.5</v>
@@ -5041,10 +5041,10 @@
         <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>11.5</v>
@@ -5053,10 +5053,10 @@
         <v>11.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>16</v>
@@ -5065,31 +5065,31 @@
         <v>9.4</v>
       </c>
       <c r="BB18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD18" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC18" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>11</v>
-      </c>
       <c r="BE18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="BH18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BJ18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK18" t="n">
         <v>9.4</v>
@@ -5098,25 +5098,25 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN18" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT18" t="n">
         <v>4.3</v>
@@ -5131,10 +5131,10 @@
         <v>5.4</v>
       </c>
       <c r="BX18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BY18" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ18" t="n">
         <v>6.2</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC19" t="n">
         <v>19</v>
@@ -5292,7 +5292,7 @@
         <v>6.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -5319,7 +5319,7 @@
         <v>6.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BC19" t="n">
         <v>5.1</v>
@@ -5340,10 +5340,10 @@
         <v>4.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="BJ19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
         <v>5.7</v>
@@ -5358,7 +5358,7 @@
         <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="BP19" t="n">
         <v>9.4</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G20" t="n">
         <v>2.86</v>
@@ -5438,52 +5438,52 @@
         <v>2.66</v>
       </c>
       <c r="I20" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
         <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
         <v>1.54</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="n">
         <v>13.5</v>
@@ -5495,19 +5495,19 @@
         <v>44</v>
       </c>
       <c r="AB20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>13</v>
@@ -5525,19 +5525,19 @@
         <v>29</v>
       </c>
       <c r="AL20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
         <v>10</v>
@@ -5549,7 +5549,7 @@
         <v>32</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU20" t="n">
         <v>7.2</v>
@@ -5558,10 +5558,10 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY20" t="n">
         <v>9.4</v>
@@ -5570,31 +5570,31 @@
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BG20" t="n">
         <v>19</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.199999999999999</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN20" t="n">
         <v>5.8</v>
@@ -5615,16 +5615,16 @@
         <v>4.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
         <v>6</v>
@@ -5636,13 +5636,13 @@
         <v>21</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX20" t="n">
         <v>32</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G21" t="n">
         <v>1.71</v>
       </c>
       <c r="H21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
         <v>7.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.33</v>
@@ -5707,13 +5707,13 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
         <v>1.98</v>
@@ -5752,7 +5752,7 @@
         <v>32</v>
       </c>
       <c r="AC21" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="AD21" t="n">
         <v>950</v>
@@ -5761,10 +5761,10 @@
         <v>700</v>
       </c>
       <c r="AF21" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AG21" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AH21" t="n">
         <v>950</v>
@@ -5797,7 +5797,7 @@
         <v>1.99</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AS21" t="n">
         <v>1.99</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
         <v>1.62</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I22" t="n">
         <v>8</v>
@@ -5952,7 +5952,7 @@
         <v>4.2</v>
       </c>
       <c r="K22" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.12</v>
@@ -5961,7 +5961,7 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O22" t="n">
         <v>1.25</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
         <v>1.19</v>
       </c>
       <c r="P23" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="Q23" t="n">
         <v>1.55</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G24" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H24" t="n">
         <v>2.92</v>
       </c>
       <c r="I24" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J24" t="n">
         <v>3.55</v>
@@ -6472,7 +6472,7 @@
         <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
         <v>1.99</v>
@@ -6493,7 +6493,7 @@
         <v>2.24</v>
       </c>
       <c r="V24" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
         <v>1.61</v>
@@ -6511,10 +6511,10 @@
         <v>60</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD24" t="n">
         <v>13.5</v>
@@ -6574,7 +6574,7 @@
         <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
         <v>15</v>
@@ -6604,7 +6604,7 @@
         <v>19</v>
       </c>
       <c r="BG24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH24" t="n">
         <v>3.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -6702,10 +6702,10 @@
         <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H25" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
         <v>3.05</v>
@@ -6723,34 +6723,34 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R25" t="n">
         <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U25" t="n">
         <v>2.34</v>
       </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W25" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X25" t="n">
         <v>17.5</v>
@@ -6768,7 +6768,7 @@
         <v>12.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
         <v>13.5</v>
@@ -6822,7 +6822,7 @@
         <v>11</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV25" t="n">
         <v>11.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>
@@ -6995,16 +6995,16 @@
         <v>3.3</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
         <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X26" t="n">
         <v>16.5</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-16 20:09:59</t>
+          <t>2026-06-16 22:19:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -887,16 +887,16 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T2" t="n">
         <v>1.58</v>
@@ -905,10 +905,10 @@
         <v>2.46</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
         <v>34</v>
@@ -974,7 +974,7 @@
         <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
         <v>20</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>3.4</v>
@@ -1129,13 +1129,13 @@
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
         <v>1.13</v>
@@ -1147,22 +1147,22 @@
         <v>1.39</v>
       </c>
       <c r="R3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T3" t="n">
         <v>1.43</v>
       </c>
       <c r="U3" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V3" t="n">
         <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
@@ -1192,7 +1192,7 @@
         <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH3" t="n">
         <v>15</v>
@@ -1219,7 +1219,7 @@
         <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
         <v>19.5</v>
@@ -1228,10 +1228,10 @@
         <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU3" t="n">
         <v>9.800000000000001</v>
@@ -1273,7 +1273,7 @@
         <v>11.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI3" t="n">
         <v>4.6</v>
@@ -1285,13 +1285,13 @@
         <v>6.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO3" t="n">
         <v>5</v>
@@ -1300,13 +1300,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>19.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT3" t="n">
         <v>7.6</v>
@@ -1318,13 +1318,13 @@
         <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX3" t="n">
         <v>25</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>12</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>1.29</v>
       </c>
       <c r="G4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>6.4</v>
@@ -1395,31 +1395,31 @@
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
         <v>3.6</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -1443,13 +1443,13 @@
         <v>330</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AI4" t="n">
         <v>260</v>
@@ -1470,10 +1470,10 @@
         <v>7.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>14</v>
@@ -1482,7 +1482,7 @@
         <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
         <v>6</v>
@@ -1494,28 +1494,28 @@
         <v>6</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
         <v>8.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
         <v>6.6</v>
@@ -1524,16 +1524,16 @@
         <v>5.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="n">
         <v>3.75</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BJ4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BK4" t="n">
         <v>5.6</v>
@@ -1542,53 +1542,53 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
         <v>7</v>
       </c>
       <c r="BT4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
         <v>17</v>
       </c>
       <c r="CA4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G5" t="n">
         <v>2.08</v>
@@ -1628,16 +1628,16 @@
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
         <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
@@ -1652,13 +1652,13 @@
         <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
         <v>2.2</v>
@@ -1721,7 +1721,7 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
@@ -1730,55 +1730,55 @@
         <v>6.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -1873,91 +1873,91 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
         <v>1.52</v>
       </c>
       <c r="P6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>2.56</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB6" t="n">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="AC6" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AF6" t="n">
         <v>500</v>
       </c>
       <c r="AG6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH6" t="n">
         <v>950</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>500</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
@@ -1969,134 +1969,134 @@
         <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.47</v>
+        <v>4.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.44</v>
+        <v>5.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.52</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.47</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.58</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.58</v>
+        <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.58</v>
+        <v>5.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.61</v>
+        <v>2.94</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.61</v>
+        <v>3.95</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.61</v>
+        <v>4.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.61</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.61</v>
+        <v>4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.61</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
         <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H7" t="n">
         <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="K7" t="n">
         <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="M7" t="n">
         <v>1.14</v>
@@ -2157,10 +2157,10 @@
         <v>1.57</v>
       </c>
       <c r="P7" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -2175,19 +2175,19 @@
         <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y7" t="n">
         <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -2205,10 +2205,10 @@
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
@@ -2220,7 +2220,7 @@
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
         <v>500</v>
@@ -2229,67 +2229,67 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
         <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BG7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BI7" t="n">
         <v>2.2</v>
@@ -2298,13 +2298,13 @@
         <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN7" t="n">
         <v>5.5</v>
@@ -2316,7 +2316,7 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H8" t="n">
         <v>1.72</v>
@@ -2399,7 +2399,7 @@
         <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
@@ -2420,10 +2420,10 @@
         <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
         <v>2.24</v>
@@ -2432,7 +2432,7 @@
         <v>2.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
@@ -2489,25 +2489,25 @@
         <v>10</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW8" t="n">
         <v>12.5</v>
@@ -2543,40 +2543,40 @@
         <v>7.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO8" t="n">
         <v>6.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
         <v>4.8</v>
@@ -2585,7 +2585,7 @@
         <v>4.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW8" t="n">
         <v>8.4</v>
@@ -2594,7 +2594,7 @@
         <v>23</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G9" t="n">
         <v>1.58</v>
       </c>
       <c r="H9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K9" t="n">
         <v>5.1</v>
       </c>
-      <c r="I9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.8</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
         <v>2.72</v>
       </c>
       <c r="X9" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
         <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF9" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>190</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.46</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN9" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="BO9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>5.1</v>
       </c>
-      <c r="AU9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H10" t="n">
         <v>6.2</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
@@ -2934,13 +2934,13 @@
         <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
         <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
         <v>12.5</v>
@@ -2979,7 +2979,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK10" t="n">
         <v>23</v>
@@ -2997,10 +2997,10 @@
         <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
         <v>9.199999999999999</v>
@@ -3024,10 +3024,10 @@
         <v>7.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA10" t="n">
         <v>8.199999999999999</v>
@@ -3036,7 +3036,7 @@
         <v>15.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
         <v>9.199999999999999</v>
@@ -3060,13 +3060,13 @@
         <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BN10" t="n">
         <v>4.2</v>
@@ -3084,10 +3084,10 @@
         <v>36</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU10" t="n">
         <v>7.2</v>
@@ -3096,23 +3096,23 @@
         <v>75</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BZ10" t="n">
         <v>32</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="X11" t="n">
         <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AE11" t="n">
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="n">
         <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>24</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AL11" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AO11" t="n">
         <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.9</v>
+        <v>18.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI11" t="n">
         <v>2.48</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.38</v>
+        <v>12</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BP11" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU11" t="n">
         <v>4.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.32</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -3427,10 +3427,10 @@
         <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
         <v>1.43</v>
@@ -3439,16 +3439,16 @@
         <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
         <v>2.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
         <v>19</v>
@@ -3475,7 +3475,7 @@
         <v>18.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AG12" t="n">
         <v>27</v>
@@ -3508,7 +3508,7 @@
         <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
         <v>9</v>
@@ -3517,7 +3517,7 @@
         <v>14.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
         <v>8</v>
@@ -3538,22 +3538,22 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC12" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
         <v>8.800000000000001</v>
@@ -3562,7 +3562,7 @@
         <v>3.75</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3577,7 +3577,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BO12" t="n">
         <v>4.8</v>
@@ -3589,7 +3589,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS12" t="n">
         <v>8.4</v>
@@ -3601,10 +3601,10 @@
         <v>3.35</v>
       </c>
       <c r="BV12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX12" t="n">
         <v>27</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -3654,28 +3654,28 @@
         <v>1.66</v>
       </c>
       <c r="G13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
         <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
@@ -3684,7 +3684,7 @@
         <v>2.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R13" t="n">
         <v>1.57</v>
@@ -3696,7 +3696,7 @@
         <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
         <v>1.21</v>
@@ -3747,10 +3747,10 @@
         <v>15.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN13" t="n">
         <v>7.6</v>
@@ -3759,16 +3759,16 @@
         <v>130</v>
       </c>
       <c r="AP13" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AQ13" t="n">
         <v>21</v>
       </c>
       <c r="AR13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -3801,16 +3801,16 @@
         <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BE13" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BF13" t="n">
         <v>6.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
@@ -3819,7 +3819,7 @@
         <v>3.3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK13" t="n">
         <v>5.2</v>
@@ -3828,43 +3828,43 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN13" t="n">
         <v>4.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
         <v>11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR13" t="n">
         <v>23</v>
       </c>
       <c r="BS13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT13" t="n">
         <v>9.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV13" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX13" t="n">
         <v>46</v>
       </c>
-      <c r="BW13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>48</v>
-      </c>
       <c r="BY13" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="H14" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="I14" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3935,13 +3935,13 @@
         <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
         <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
         <v>3.15</v>
@@ -3950,22 +3950,22 @@
         <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
         <v>44</v>
@@ -3986,7 +3986,7 @@
         <v>19.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
         <v>16</v>
@@ -3995,10 +3995,10 @@
         <v>40</v>
       </c>
       <c r="AJ14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL14" t="n">
         <v>40</v>
@@ -4007,10 +4007,10 @@
         <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP14" t="n">
         <v>14</v>
@@ -4019,10 +4019,10 @@
         <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AT14" t="n">
         <v>11</v>
@@ -4034,7 +4034,7 @@
         <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AX14" t="n">
         <v>16</v>
@@ -4046,46 +4046,46 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB14" t="n">
         <v>24</v>
       </c>
-      <c r="BB14" t="n">
-        <v>34</v>
-      </c>
       <c r="BC14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE14" t="n">
         <v>34</v>
       </c>
       <c r="BF14" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG14" t="n">
         <v>19.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO14" t="n">
         <v>4.4</v>
@@ -4094,13 +4094,13 @@
         <v>21</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT14" t="n">
         <v>6.2</v>
@@ -4112,13 +4112,13 @@
         <v>22</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX14" t="n">
         <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J15" t="n">
         <v>4.5</v>
@@ -4177,7 +4177,7 @@
         <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
@@ -4195,10 +4195,10 @@
         <v>1.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T15" t="n">
         <v>1.51</v>
@@ -4207,10 +4207,10 @@
         <v>2.68</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X15" t="n">
         <v>85</v>
@@ -4219,7 +4219,7 @@
         <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AA15" t="n">
         <v>500</v>
@@ -4246,13 +4246,13 @@
         <v>60</v>
       </c>
       <c r="AI15" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
         <v>970</v>
       </c>
       <c r="AK15" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AL15" t="n">
         <v>48</v>
@@ -4264,31 +4264,31 @@
         <v>7.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU15" t="n">
         <v>5.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX15" t="n">
         <v>7.6</v>
@@ -4300,22 +4300,22 @@
         <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
         <v>8.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE15" t="n">
         <v>7.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="BG15" t="n">
         <v>5.3</v>
@@ -4324,7 +4324,7 @@
         <v>5.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4336,10 +4336,10 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="BN15" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="BO15" t="n">
         <v>3.85</v>
@@ -4348,13 +4348,13 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.85</v>
+        <v>2.96</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
@@ -4366,13 +4366,13 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.94</v>
+        <v>3.2</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I16" t="n">
         <v>2.94</v>
@@ -4443,13 +4443,13 @@
         <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
         <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
         <v>3.1</v>
@@ -4458,7 +4458,7 @@
         <v>1.68</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
         <v>1.52</v>
@@ -4488,7 +4488,7 @@
         <v>12.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AF16" t="n">
         <v>38</v>
@@ -4506,7 +4506,7 @@
         <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AL16" t="n">
         <v>500</v>
@@ -4530,7 +4530,7 @@
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
@@ -4557,22 +4557,22 @@
         <v>10</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC16" t="n">
         <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="n">
         <v>3.55</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="H17" t="n">
         <v>2.04</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
         <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4715,13 +4715,13 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y17" t="n">
         <v>1000</v>
@@ -4778,52 +4778,52 @@
         <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB17" t="n">
         <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG17" t="n">
         <v>1.55</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -4927,16 +4927,16 @@
         <v>17.5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="J18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.19</v>
@@ -4945,28 +4945,28 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="T18" t="n">
         <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
         <v>5.4</v>
@@ -4975,16 +4975,16 @@
         <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="Y18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
         <v>12</v>
       </c>
       <c r="AA18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AB18" t="n">
         <v>95</v>
@@ -5002,7 +5002,7 @@
         <v>210</v>
       </c>
       <c r="AG18" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AH18" t="n">
         <v>32</v>
@@ -5014,16 +5014,16 @@
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AL18" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM18" t="n">
         <v>500</v>
       </c>
       <c r="AN18" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AO18" t="n">
         <v>2.78</v>
@@ -5059,13 +5059,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
         <v>12</v>
@@ -5074,13 +5074,13 @@
         <v>11.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BF18" t="n">
         <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BH18" t="n">
         <v>6.2</v>
@@ -5089,10 +5089,10 @@
         <v>5.4</v>
       </c>
       <c r="BJ18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5104,7 +5104,7 @@
         <v>18.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
@@ -5113,10 +5113,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BS18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT18" t="n">
         <v>4.3</v>
@@ -5131,20 +5131,20 @@
         <v>5.4</v>
       </c>
       <c r="BX18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BY18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>6.2</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -5178,10 +5178,10 @@
         <v>1.51</v>
       </c>
       <c r="G19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I19" t="n">
         <v>7.8</v>
@@ -5190,7 +5190,7 @@
         <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.26</v>
@@ -5208,7 +5208,7 @@
         <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R19" t="n">
         <v>1.58</v>
@@ -5226,7 +5226,7 @@
         <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -5265,7 +5265,7 @@
         <v>170</v>
       </c>
       <c r="AJ19" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AK19" t="n">
         <v>500</v>
@@ -5277,34 +5277,34 @@
         <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO19" t="n">
         <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX19" t="n">
         <v>9.4</v>
@@ -5313,28 +5313,28 @@
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD19" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6</v>
-      </c>
       <c r="BE19" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19" t="n">
         <v>3.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH19" t="n">
         <v>4.4</v>
@@ -5370,7 +5370,7 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H20" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I20" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.33</v>
@@ -5453,22 +5453,22 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
         <v>1.77</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T20" t="n">
         <v>1.66</v>
@@ -5477,10 +5477,10 @@
         <v>2.28</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X20" t="n">
         <v>18</v>
@@ -5507,10 +5507,10 @@
         <v>30</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
         <v>16.5</v>
@@ -5519,10 +5519,10 @@
         <v>55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AK20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="n">
         <v>38</v>
@@ -5531,7 +5531,7 @@
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
         <v>24</v>
@@ -5558,7 +5558,7 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
         <v>16</v>
@@ -5570,7 +5570,7 @@
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB20" t="n">
         <v>28</v>
@@ -5579,13 +5579,13 @@
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF20" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BG20" t="n">
         <v>19</v>
@@ -5594,7 +5594,7 @@
         <v>4</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.199999999999999</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN20" t="n">
         <v>5.8</v>
@@ -5615,7 +5615,7 @@
         <v>4.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ20" t="n">
         <v>7.2</v>
@@ -5636,13 +5636,13 @@
         <v>21</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX20" t="n">
         <v>32</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
         <v>32</v>
       </c>
       <c r="AC21" t="n">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="AD21" t="n">
         <v>950</v>
@@ -5791,16 +5791,16 @@
         <v>700</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AR21" t="n">
         <v>1.99</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AT21" t="n">
         <v>5.7</v>
@@ -5809,40 +5809,40 @@
         <v>1.7</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AY21" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="BF21" t="n">
         <v>7.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G22" t="n">
         <v>1.62</v>
       </c>
       <c r="H22" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J22" t="n">
         <v>4.2</v>
@@ -5961,7 +5961,7 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.25</v>
@@ -5985,7 +5985,7 @@
         <v>1.93</v>
       </c>
       <c r="V22" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
         <v>2.58</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -6191,34 +6191,34 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="G23" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="H23" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="I23" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="J23" t="n">
         <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
         <v>2.28</v>
@@ -6233,34 +6233,34 @@
         <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="V23" t="n">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y23" t="n">
         <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AC23" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD23" t="n">
         <v>11.5</v>
@@ -6269,97 +6269,97 @@
         <v>16.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AG23" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ23" t="n">
-        <v>290</v>
+        <v>200</v>
       </c>
       <c r="AK23" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="AL23" t="n">
         <v>240</v>
       </c>
       <c r="AM23" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AN23" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AT23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW23" t="n">
         <v>5.1</v>
       </c>
-      <c r="AU23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AX23" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BH23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK23" t="n">
         <v>4.3</v>
@@ -6368,53 +6368,53 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN23" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ23" t="n">
         <v>6.2</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS23" t="n">
         <v>6.2</v>
       </c>
       <c r="BT23" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BU23" t="n">
         <v>3.25</v>
       </c>
       <c r="BV23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BW23" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BX23" t="n">
         <v>24</v>
       </c>
       <c r="BY23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BZ23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CA23" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
         <v>2.62</v>
       </c>
       <c r="H24" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I24" t="n">
         <v>3.05</v>
@@ -6463,7 +6463,7 @@
         <v>3.65</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
@@ -6472,19 +6472,19 @@
         <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R24" t="n">
         <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T24" t="n">
         <v>1.75</v>
@@ -6607,22 +6607,22 @@
         <v>19</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ24" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN24" t="n">
         <v>5.6</v>
@@ -6634,7 +6634,7 @@
         <v>19</v>
       </c>
       <c r="BQ24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR24" t="n">
         <v>32</v>
@@ -6652,13 +6652,13 @@
         <v>23</v>
       </c>
       <c r="BW24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX24" t="n">
         <v>34</v>
       </c>
       <c r="BY24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -6702,13 +6702,13 @@
         <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
         <v>3.65</v>
@@ -6717,7 +6717,7 @@
         <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -6726,13 +6726,13 @@
         <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P25" t="n">
         <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R25" t="n">
         <v>1.44</v>
@@ -6747,10 +6747,10 @@
         <v>2.34</v>
       </c>
       <c r="V25" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X25" t="n">
         <v>17.5</v>
@@ -6789,10 +6789,10 @@
         <v>42</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL25" t="n">
         <v>44</v>
@@ -6828,7 +6828,7 @@
         <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX25" t="n">
         <v>15</v>
@@ -6840,7 +6840,7 @@
         <v>14.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB25" t="n">
         <v>28</v>
@@ -6858,10 +6858,10 @@
         <v>16</v>
       </c>
       <c r="BG25" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI25" t="n">
         <v>3.25</v>
@@ -6870,31 +6870,31 @@
         <v>9.4</v>
       </c>
       <c r="BK25" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BN25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO25" t="n">
         <v>4.9</v>
       </c>
       <c r="BP25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR25" t="n">
         <v>30</v>
       </c>
       <c r="BS25" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT25" t="n">
         <v>6.4</v>
@@ -6906,13 +6906,13 @@
         <v>23</v>
       </c>
       <c r="BW25" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BX25" t="n">
         <v>34</v>
       </c>
       <c r="BY25" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-16 22:19:28</t>
+          <t>2026-06-17 00:29:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -860,10 +860,10 @@
         <v>4.4</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="I2" t="n">
         <v>1.8</v>
@@ -872,7 +872,7 @@
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.27</v>
@@ -881,22 +881,22 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.58</v>
@@ -908,7 +908,7 @@
         <v>2.24</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
         <v>34</v>
@@ -938,10 +938,10 @@
         <v>50</v>
       </c>
       <c r="AG2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
         <v>32</v>
@@ -989,7 +989,7 @@
         <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
         <v>16</v>
@@ -1001,7 +1001,7 @@
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
         <v>9.199999999999999</v>
@@ -1022,10 +1022,10 @@
         <v>4.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
         <v>6.8</v>
@@ -1034,31 +1034,31 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>9</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>5.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV2" t="n">
         <v>11.5</v>
@@ -1067,20 +1067,20 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BZ2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -1114,58 +1114,58 @@
         <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
         <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="R3" t="n">
         <v>1.86</v>
       </c>
       <c r="S3" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="T3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="V3" t="n">
         <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y3" t="n">
         <v>25</v>
@@ -1174,13 +1174,13 @@
         <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
         <v>15.5</v>
@@ -1189,10 +1189,10 @@
         <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>15</v>
@@ -1201,10 +1201,10 @@
         <v>30</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
@@ -1216,34 +1216,34 @@
         <v>8</v>
       </c>
       <c r="AO3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT3" t="n">
         <v>16</v>
       </c>
-      <c r="AS3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AU3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1252,10 +1252,10 @@
         <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
         <v>16</v>
@@ -1264,49 +1264,49 @@
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
         <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR3" t="n">
         <v>19.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT3" t="n">
         <v>7.6</v>
@@ -1318,23 +1318,23 @@
         <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX3" t="n">
         <v>25</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>12</v>
       </c>
       <c r="CA3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -1365,49 +1365,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G4" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
         <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="U4" t="n">
         <v>1.57</v>
@@ -1416,55 +1416,55 @@
         <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
       </c>
       <c r="Z4" t="n">
-        <v>540</v>
+        <v>160</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC4" t="n">
         <v>14.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AE4" t="n">
-        <v>330</v>
+        <v>430</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="n">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="AN4" t="n">
         <v>7.2</v>
@@ -1476,119 +1476,119 @@
         <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB4" t="n">
         <v>8.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
         <v>5.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
         <v>15</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="BP4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G5" t="n">
         <v>2.08</v>
@@ -1628,28 +1628,28 @@
         <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
         <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
         <v>2.92</v>
@@ -1658,16 +1658,16 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
         <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
         <v>1.92</v>
@@ -1727,58 +1727,58 @@
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV5" t="n">
         <v>3.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG5" t="n">
         <v>2.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.52</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BN5" t="n">
         <v>4.6</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -1873,67 +1873,67 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="I6" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="n">
         <v>160</v>
@@ -1981,16 +1981,16 @@
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AR6" t="n">
         <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
@@ -1999,76 +1999,76 @@
         <v>6</v>
       </c>
       <c r="AV6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
         <v>4.9</v>
       </c>
-      <c r="AW6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.57</v>
+        <v>4.5</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT6" t="n">
         <v>4.5</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -2127,64 +2127,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G7" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="K7" t="n">
         <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
         <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="P7" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -2238,7 +2238,7 @@
         <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
         <v>18</v>
@@ -2256,28 +2256,28 @@
         <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
         <v>9</v>
       </c>
       <c r="BB7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BE7" t="n">
         <v>9.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G8" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="I8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.28</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.24</v>
       </c>
       <c r="V8" t="n">
         <v>2.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
@@ -2447,25 +2447,25 @@
         <v>19.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC8" t="n">
         <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE8" t="n">
         <v>17.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AG8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI8" t="n">
         <v>36</v>
@@ -2501,7 +2501,7 @@
         <v>16</v>
       </c>
       <c r="AT8" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU8" t="n">
         <v>8.6</v>
@@ -2525,16 +2525,16 @@
         <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC8" t="n">
         <v>38</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BF8" t="n">
         <v>7</v>
@@ -2546,22 +2546,22 @@
         <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO8" t="n">
         <v>6.4</v>
@@ -2570,22 +2570,22 @@
         <v>36</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT8" t="n">
         <v>4.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW8" t="n">
         <v>8.4</v>
@@ -2594,7 +2594,7 @@
         <v>23</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -2635,70 +2635,70 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="G9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
         <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>170</v>
       </c>
       <c r="Z9" t="n">
         <v>150</v>
       </c>
       <c r="AA9" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB9" t="n">
         <v>9.199999999999999</v>
@@ -2707,13 +2707,13 @@
         <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AE9" t="n">
         <v>260</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
@@ -2737,22 +2737,22 @@
         <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9" t="n">
         <v>7.6</v>
@@ -2761,10 +2761,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX9" t="n">
         <v>8</v>
@@ -2773,52 +2773,52 @@
         <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB9" t="n">
         <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF9" t="n">
         <v>6.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI9" t="n">
         <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP9" t="n">
         <v>10</v>
@@ -2827,38 +2827,38 @@
         <v>5.1</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT9" t="n">
         <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY9" t="n">
         <v>9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA9" t="n">
         <v>6.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -2889,58 +2889,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H10" t="n">
         <v>6.2</v>
       </c>
       <c r="I10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
         <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
         <v>1.46</v>
       </c>
       <c r="P10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T10" t="n">
         <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X10" t="n">
         <v>12.5</v>
@@ -3003,10 +3003,10 @@
         <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
         <v>5.6</v>
@@ -3030,7 +3030,7 @@
         <v>21</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -3048,7 +3048,7 @@
         <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="n">
         <v>3.05</v>
@@ -3060,13 +3060,13 @@
         <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN10" t="n">
         <v>4.2</v>
@@ -3084,10 +3084,10 @@
         <v>36</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU10" t="n">
         <v>7.2</v>
@@ -3096,23 +3096,23 @@
         <v>75</v>
       </c>
       <c r="BW10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>32</v>
       </c>
       <c r="CA10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -3143,73 +3143,73 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC11" t="n">
         <v>7.8</v>
@@ -3221,10 +3221,10 @@
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>60</v>
@@ -3233,7 +3233,7 @@
         <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK11" t="n">
         <v>65</v>
@@ -3245,128 +3245,128 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AO11" t="n">
         <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AT11" t="n">
         <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF11" t="n">
         <v>9.4</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BG11" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BH11" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
       </c>
       <c r="BK11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU11" t="n">
         <v>6</v>
       </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -3397,61 +3397,61 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
         <v>1.69</v>
       </c>
       <c r="I12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U12" t="n">
         <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="W12" t="n">
         <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="n">
         <v>9.199999999999999</v>
@@ -3460,31 +3460,31 @@
         <v>10.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB12" t="n">
         <v>21</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AF12" t="n">
         <v>130</v>
       </c>
       <c r="AG12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AH12" t="n">
         <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="n">
         <v>900</v>
@@ -3502,13 +3502,13 @@
         <v>700</v>
       </c>
       <c r="AO12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR12" t="n">
         <v>9</v>
@@ -3517,43 +3517,43 @@
         <v>14.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
         <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="AY12" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BD12" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BG12" t="n">
         <v>8.800000000000001</v>
@@ -3562,7 +3562,7 @@
         <v>3.75</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3574,22 +3574,22 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
         <v>9.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
         <v>8.4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G13" t="n">
         <v>1.66</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.69</v>
-      </c>
       <c r="H13" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J13" t="n">
         <v>4.4</v>
@@ -3669,28 +3669,28 @@
         <v>4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q13" t="n">
         <v>1.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T13" t="n">
         <v>1.72</v>
@@ -3699,34 +3699,34 @@
         <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X13" t="n">
         <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z13" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC13" t="n">
         <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF13" t="n">
         <v>11.5</v>
@@ -3747,7 +3747,7 @@
         <v>15.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM13" t="n">
         <v>320</v>
@@ -3756,7 +3756,7 @@
         <v>7.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AP13" t="n">
         <v>18</v>
@@ -3765,10 +3765,10 @@
         <v>21</v>
       </c>
       <c r="AR13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AS13" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -3777,7 +3777,7 @@
         <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>32</v>
@@ -3810,61 +3810,61 @@
         <v>6.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BJ13" t="n">
         <v>10</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN13" t="n">
         <v>4.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP13" t="n">
         <v>11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR13" t="n">
         <v>23</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX13" t="n">
         <v>46</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="I14" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3923,13 +3923,13 @@
         <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.29</v>
@@ -3938,13 +3938,13 @@
         <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
         <v>1.7</v>
@@ -3953,10 +3953,10 @@
         <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X14" t="n">
         <v>16.5</v>
@@ -3965,7 +3965,7 @@
         <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
         <v>44</v>
@@ -3983,7 +3983,7 @@
         <v>30</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG14" t="n">
         <v>12.5</v>
@@ -4022,7 +4022,7 @@
         <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT14" t="n">
         <v>11</v>
@@ -4031,13 +4031,13 @@
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY14" t="n">
         <v>11</v>
@@ -4046,25 +4046,25 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BC14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BD14" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH14" t="n">
         <v>3.7</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="G15" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.24</v>
@@ -4183,7 +4183,7 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
@@ -4192,25 +4192,25 @@
         <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S15" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U15" t="n">
         <v>2.68</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="X15" t="n">
         <v>85</v>
@@ -4225,19 +4225,19 @@
         <v>500</v>
       </c>
       <c r="AB15" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD15" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AE15" t="n">
         <v>200</v>
       </c>
       <c r="AF15" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
         <v>19</v>
@@ -4249,70 +4249,70 @@
         <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AK15" t="n">
         <v>970</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AO15" t="n">
         <v>600</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT15" t="n">
         <v>8.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AX15" t="n">
         <v>7.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
         <v>8.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BF15" t="n">
         <v>5</v>
@@ -4324,10 +4324,10 @@
         <v>5.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK15" t="n">
         <v>6.6</v>
@@ -4336,28 +4336,28 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>3.35</v>
+        <v>12.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS15" t="n">
-        <v>2.96</v>
+        <v>8.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU15" t="n">
         <v>6.6</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="BX15" t="n">
         <v>46</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA15" t="n">
         <v>8.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G16" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H16" t="n">
         <v>2.72</v>
@@ -4425,64 +4425,64 @@
         <v>2.94</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V16" t="n">
         <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
         <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD16" t="n">
         <v>12.5</v>
@@ -4491,7 +4491,7 @@
         <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
@@ -4515,22 +4515,22 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AO16" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
         <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
@@ -4542,7 +4542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
@@ -4551,34 +4551,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BC16" t="n">
         <v>14.5</v>
       </c>
       <c r="BD16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG16" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>7.2</v>
       </c>
       <c r="BH16" t="n">
         <v>3.55</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.6</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BN16" t="n">
         <v>6</v>
@@ -4599,16 +4599,16 @@
         <v>5</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT16" t="n">
         <v>6.2</v>
@@ -4617,16 +4617,16 @@
         <v>5.1</v>
       </c>
       <c r="BV16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -4667,64 +4667,64 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="G17" t="n">
-        <v>2.52</v>
+        <v>1.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.04</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="K17" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>2.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="S17" t="n">
-        <v>1.13</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>1.66</v>
+        <v>2.96</v>
       </c>
       <c r="X17" t="n">
         <v>48</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -4733,10 +4733,10 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -4745,10 +4745,10 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH17" t="n">
         <v>1000</v>
@@ -4757,76 +4757,76 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="G18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="J18" t="n">
         <v>8.199999999999999</v>
@@ -4939,7 +4939,7 @@
         <v>9.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
@@ -4954,19 +4954,19 @@
         <v>3.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="R18" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="T18" t="n">
         <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
         <v>5.4</v>
@@ -4984,7 +4984,7 @@
         <v>12</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AB18" t="n">
         <v>95</v>
@@ -4993,7 +4993,7 @@
         <v>21</v>
       </c>
       <c r="AD18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>13.5</v>
@@ -5029,7 +5029,7 @@
         <v>2.78</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>14</v>
@@ -5041,7 +5041,7 @@
         <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
         <v>18</v>
@@ -5050,37 +5050,37 @@
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
         <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC18" t="n">
         <v>13</v>
       </c>
-      <c r="BC18" t="n">
-        <v>12</v>
-      </c>
       <c r="BD18" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BE18" t="n">
         <v>20</v>
       </c>
       <c r="BF18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BH18" t="n">
         <v>6.2</v>
@@ -5098,25 +5098,25 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BN18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BO18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BR18" t="n">
         <v>90</v>
       </c>
       <c r="BS18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT18" t="n">
         <v>4.3</v>
@@ -5128,23 +5128,23 @@
         <v>6.4</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BX18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CA18" t="n">
         <v>5.5</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -5178,46 +5178,46 @@
         <v>1.51</v>
       </c>
       <c r="G19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N19" t="n">
         <v>5.3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5.2</v>
       </c>
       <c r="O19" t="n">
         <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="Q19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.59</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.58</v>
-      </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U19" t="n">
         <v>2.16</v>
@@ -5226,10 +5226,10 @@
         <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y19" t="n">
         <v>950</v>
@@ -5238,13 +5238,13 @@
         <v>160</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="AD19" t="n">
         <v>950</v>
@@ -5256,7 +5256,7 @@
         <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
         <v>950</v>
@@ -5283,28 +5283,28 @@
         <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AV19" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX19" t="n">
         <v>9.4</v>
@@ -5313,46 +5313,46 @@
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="BC19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF19" t="n">
         <v>5.6</v>
       </c>
-      <c r="BD19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BG19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="n">
         <v>4.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN19" t="n">
         <v>4.4</v>
@@ -5364,19 +5364,19 @@
         <v>9.4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -5429,46 +5429,46 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H20" t="n">
         <v>2.8</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.72</v>
-      </c>
       <c r="I20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="R20" t="n">
         <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
         <v>1.66</v>
@@ -5480,10 +5480,10 @@
         <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="n">
         <v>13.5</v>
@@ -5495,25 +5495,25 @@
         <v>44</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
         <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
         <v>55</v>
@@ -5522,7 +5522,7 @@
         <v>38</v>
       </c>
       <c r="AK20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL20" t="n">
         <v>38</v>
@@ -5534,7 +5534,7 @@
         <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
         <v>14</v>
@@ -5558,7 +5558,7 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX20" t="n">
         <v>16</v>
@@ -5567,22 +5567,22 @@
         <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF20" t="n">
         <v>16.5</v>
@@ -5591,13 +5591,13 @@
         <v>19</v>
       </c>
       <c r="BH20" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BI20" t="n">
         <v>3.45</v>
       </c>
       <c r="BJ20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK20" t="n">
         <v>5.9</v>
@@ -5606,25 +5606,25 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO20" t="n">
         <v>4.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BR20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BT20" t="n">
         <v>6</v>
@@ -5636,13 +5636,13 @@
         <v>21</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BX20" t="n">
         <v>32</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -5683,58 +5683,58 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="G21" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H21" t="n">
         <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T21" t="n">
         <v>1.98</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.82</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="V21" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X21" t="n">
         <v>950</v>
@@ -5746,13 +5746,13 @@
         <v>500</v>
       </c>
       <c r="AA21" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AD21" t="n">
         <v>950</v>
@@ -5761,10 +5761,10 @@
         <v>700</v>
       </c>
       <c r="AF21" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AH21" t="n">
         <v>950</v>
@@ -5773,130 +5773,130 @@
         <v>700</v>
       </c>
       <c r="AJ21" t="n">
-        <v>900</v>
+        <v>180</v>
       </c>
       <c r="AK21" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL21" t="n">
         <v>500</v>
       </c>
       <c r="AM21" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AO21" t="n">
         <v>700</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.86</v>
+        <v>4.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.99</v>
+        <v>3.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.86</v>
+        <v>3.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.7</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.85</v>
+        <v>7.2</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.61</v>
+        <v>4.9</v>
       </c>
       <c r="AY21" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.86</v>
+        <v>7</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.82</v>
+        <v>4.7</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.86</v>
+        <v>3.15</v>
       </c>
       <c r="BF21" t="n">
         <v>7.8</v>
       </c>
       <c r="BG21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
         <v>1.93</v>
       </c>
-      <c r="BH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -5937,230 +5937,230 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H22" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I22" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
         <v>4.2</v>
       </c>
       <c r="K22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.26</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U22" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="V22" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
         <v>2.58</v>
       </c>
       <c r="X22" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="Y22" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Z22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA22" t="n">
         <v>220</v>
       </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF22" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AL22" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>29</v>
+        <v>8.4</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.45</v>
+        <v>15.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.53</v>
+        <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.49</v>
+        <v>13</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.5</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.54</v>
+        <v>19.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.56</v>
+        <v>9.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.58</v>
+        <v>7.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.56</v>
+        <v>9.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -6191,58 +6191,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="G23" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="I23" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K23" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
         <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.55</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.51</v>
-      </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="U23" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V23" t="n">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
         <v>26</v>
@@ -6251,16 +6251,16 @@
         <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD23" t="n">
         <v>11.5</v>
@@ -6269,19 +6269,19 @@
         <v>16.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AG23" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AJ23" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AK23" t="n">
         <v>230</v>
@@ -6290,79 +6290,79 @@
         <v>240</v>
       </c>
       <c r="AM23" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN23" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD23" t="n">
         <v>5.8</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT23" t="n">
+      <c r="BE23" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA23" t="n">
+      <c r="BF23" t="n">
         <v>6</v>
       </c>
-      <c r="BB23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG23" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BH23" t="n">
         <v>4.6</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6371,50 +6371,50 @@
         <v>6.6</v>
       </c>
       <c r="BN23" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT23" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="BV23" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BW23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BX23" t="n">
         <v>24</v>
       </c>
       <c r="BY23" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G24" t="n">
         <v>2.62</v>
@@ -6460,37 +6460,37 @@
         <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
         <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q24" t="n">
         <v>1.93</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U24" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V24" t="n">
         <v>1.48</v>
@@ -6511,10 +6511,10 @@
         <v>60</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD24" t="n">
         <v>13.5</v>
@@ -6529,7 +6529,7 @@
         <v>14.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI24" t="n">
         <v>55</v>
@@ -6544,7 +6544,7 @@
         <v>46</v>
       </c>
       <c r="AM24" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN24" t="n">
         <v>27</v>
@@ -6586,7 +6586,7 @@
         <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BB24" t="n">
         <v>22</v>
@@ -6646,7 +6646,7 @@
         <v>6.2</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV24" t="n">
         <v>23</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -6699,46 +6699,46 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="G25" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J25" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O25" t="n">
         <v>1.27</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R25" t="n">
         <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
         <v>1.68</v>
@@ -6747,10 +6747,10 @@
         <v>2.34</v>
       </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="X25" t="n">
         <v>17.5</v>
@@ -6762,7 +6762,7 @@
         <v>22</v>
       </c>
       <c r="AA25" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AB25" t="n">
         <v>12.5</v>
@@ -6774,19 +6774,19 @@
         <v>13.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF25" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG25" t="n">
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ25" t="n">
         <v>36</v>
@@ -6795,16 +6795,16 @@
         <v>26</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
         <v>90</v>
       </c>
       <c r="AN25" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP25" t="n">
         <v>15</v>
@@ -6828,7 +6828,7 @@
         <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX25" t="n">
         <v>15</v>
@@ -6837,10 +6837,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB25" t="n">
         <v>28</v>
@@ -6858,7 +6858,7 @@
         <v>16</v>
       </c>
       <c r="BG25" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BH25" t="n">
         <v>3.75</v>
@@ -6870,13 +6870,13 @@
         <v>9.4</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN25" t="n">
         <v>5.8</v>
@@ -6888,13 +6888,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR25" t="n">
         <v>30</v>
       </c>
       <c r="BS25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT25" t="n">
         <v>6.4</v>
@@ -6903,16 +6903,16 @@
         <v>5.3</v>
       </c>
       <c r="BV25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW25" t="n">
         <v>7.8</v>
       </c>
       <c r="BX25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>
@@ -6953,112 +6953,112 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H26" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R26" t="n">
         <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X26" t="n">
         <v>16.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF26" t="n">
         <v>15</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
         <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK26" t="n">
         <v>26</v>
       </c>
       <c r="AL26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM26" t="n">
         <v>110</v>
       </c>
       <c r="AN26" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP26" t="n">
         <v>11</v>
@@ -7067,25 +7067,25 @@
         <v>11.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.5</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX26" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>4.2</v>
       </c>
       <c r="AY26" t="n">
         <v>8.6</v>
@@ -7094,89 +7094,89 @@
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD26" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC26" t="n">
+      <c r="BE26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF26" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG26" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ26" t="n">
         <v>10</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BN26" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BO26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP26" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ26" t="n">
         <v>6.4</v>
       </c>
       <c r="BR26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW26" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>7.8</v>
       </c>
       <c r="BX26" t="n">
         <v>42</v>
       </c>
       <c r="BY26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ26" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="CA26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-17 00:29:11</t>
+          <t>2026-06-17 02:38:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G2" t="n">
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -887,25 +887,25 @@
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="W2" t="n">
         <v>1.25</v>
@@ -929,7 +929,7 @@
         <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>16.5</v>
@@ -947,13 +947,13 @@
         <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
         <v>120</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AM2" t="n">
         <v>250</v>
@@ -965,10 +965,10 @@
         <v>7</v>
       </c>
       <c r="AP2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AR2" t="n">
         <v>7</v>
@@ -977,10 +977,10 @@
         <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="AV2" t="n">
         <v>9</v>
@@ -995,28 +995,28 @@
         <v>16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="n">
         <v>4.8</v>
@@ -1049,7 +1049,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS2" t="n">
         <v>8.199999999999999</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
         <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.23</v>
@@ -1135,37 +1135,37 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.42</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.41</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y3" t="n">
         <v>25</v>
@@ -1177,7 +1177,7 @@
         <v>75</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC3" t="n">
         <v>12.5</v>
@@ -1198,10 +1198,10 @@
         <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
         <v>19</v>
@@ -1213,13 +1213,13 @@
         <v>55</v>
       </c>
       <c r="AN3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
         <v>20</v>
@@ -1228,55 +1228,55 @@
         <v>22</v>
       </c>
       <c r="AS3" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
         <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BC3" t="n">
         <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE3" t="n">
         <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="n">
         <v>5.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.4</v>
@@ -1285,28 +1285,28 @@
         <v>6.4</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>5.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP3" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
         <v>7.6</v>
@@ -1318,23 +1318,23 @@
         <v>22</v>
       </c>
       <c r="BW3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
         <v>25</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA3" t="n">
         <v>9.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
         <v>1.35</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -1404,127 +1404,127 @@
         <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
         <v>14.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE4" t="n">
-        <v>430</v>
+        <v>350</v>
       </c>
       <c r="AF4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="AJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="AN4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>650</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS4" t="n">
         <v>7.2</v>
       </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW4" t="n">
         <v>7</v>
       </c>
-      <c r="AW4" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AX4" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH4" t="n">
         <v>3.65</v>
@@ -1533,7 +1533,7 @@
         <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK4" t="n">
         <v>6.2</v>
@@ -1542,31 +1542,31 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA4" t="n">
         <v>6.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -1610,184 +1610,184 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.99</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD5" t="n">
         <v>27</v>
       </c>
-      <c r="AC5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>950</v>
-      </c>
       <c r="AE5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM5" t="n">
         <v>700</v>
       </c>
-      <c r="AF5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>3</v>
+        <v>12.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.4</v>
+        <v>19</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
         <v>7.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.98</v>
+        <v>12.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.44</v>
+        <v>24</v>
       </c>
       <c r="BE5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BF5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
         <v>6</v>
@@ -1796,53 +1796,53 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="BT5" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>4.9</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="H6" t="n">
         <v>1.88</v>
@@ -1885,7 +1885,7 @@
         <v>1.97</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>3.6</v>
@@ -1900,7 +1900,7 @@
         <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
         <v>1.53</v>
@@ -1918,7 +1918,7 @@
         <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V6" t="n">
         <v>2.02</v>
@@ -1933,7 +1933,7 @@
         <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="n">
         <v>160</v>
@@ -1945,7 +1945,7 @@
         <v>14</v>
       </c>
       <c r="AD6" t="n">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE6" t="n">
         <v>240</v>
@@ -1960,7 +1960,7 @@
         <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ6" t="n">
         <v>900</v>
@@ -1975,13 +1975,13 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>230</v>
       </c>
       <c r="AO6" t="n">
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.2</v>
@@ -1993,7 +1993,7 @@
         <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
@@ -2002,76 +2002,76 @@
         <v>5.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY6" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC6" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH6" t="n">
         <v>2.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU6" t="n">
         <v>3.7</v>
@@ -2080,23 +2080,23 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -2130,37 +2130,37 @@
         <v>2.48</v>
       </c>
       <c r="G7" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="M7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
         <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R7" t="n">
         <v>1.17</v>
@@ -2169,22 +2169,22 @@
         <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X7" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -2196,19 +2196,19 @@
         <v>7.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
@@ -2217,7 +2217,7 @@
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -2232,125 +2232,125 @@
         <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX7" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12</v>
-      </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>2.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>2.26</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.5</v>
+        <v>2.26</v>
       </c>
       <c r="BC7" t="n">
-        <v>16.5</v>
+        <v>2.26</v>
       </c>
       <c r="BD7" t="n">
-        <v>27</v>
+        <v>2.24</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.6</v>
+        <v>2.26</v>
       </c>
       <c r="BF7" t="n">
-        <v>13</v>
+        <v>2.26</v>
       </c>
       <c r="BG7" t="n">
-        <v>9</v>
+        <v>2.26</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I8" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
@@ -2405,40 +2405,40 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="T8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
         <v>13</v>
@@ -2447,10 +2447,10 @@
         <v>19.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
         <v>10.5</v>
@@ -2459,7 +2459,7 @@
         <v>17.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AG8" t="n">
         <v>19</v>
@@ -2468,34 +2468,34 @@
         <v>17.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AJ8" t="n">
         <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AO8" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AP8" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
         <v>16</v>
@@ -2504,40 +2504,40 @@
         <v>18.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX8" t="n">
         <v>16</v>
       </c>
       <c r="AY8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BE8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF8" t="n">
         <v>27</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7</v>
       </c>
       <c r="BG8" t="n">
         <v>7.4</v>
@@ -2552,25 +2552,25 @@
         <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN8" t="n">
         <v>8.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP8" t="n">
         <v>36</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR8" t="n">
         <v>40</v>
@@ -2582,19 +2582,19 @@
         <v>4.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="BV8" t="n">
         <v>11.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX8" t="n">
         <v>23</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.52</v>
       </c>
       <c r="G9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="n">
         <v>6.8</v>
@@ -2650,7 +2650,7 @@
         <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.35</v>
@@ -2659,37 +2659,37 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T9" t="n">
         <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
         <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
         <v>170</v>
@@ -2698,7 +2698,7 @@
         <v>150</v>
       </c>
       <c r="AA9" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB9" t="n">
         <v>9.199999999999999</v>
@@ -2728,7 +2728,7 @@
         <v>15</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
@@ -2746,13 +2746,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT9" t="n">
         <v>7.6</v>
@@ -2761,10 +2761,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX9" t="n">
         <v>8</v>
@@ -2776,7 +2776,7 @@
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
         <v>11.5</v>
@@ -2788,16 +2788,16 @@
         <v>18</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
         <v>6.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI9" t="n">
         <v>3.15</v>
@@ -2806,59 +2806,59 @@
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN9" t="n">
         <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP9" t="n">
         <v>10</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
         <v>25</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT9" t="n">
         <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>16.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -2880,142 +2880,142 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="G10" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.51</v>
       </c>
-      <c r="M10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.64</v>
-      </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="U10" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.4</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18.5</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>16.5</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV10" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>18.5</v>
       </c>
       <c r="AW10" t="n">
         <v>9.199999999999999</v>
@@ -3024,95 +3024,95 @@
         <v>7.8</v>
       </c>
       <c r="AY10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BE10" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BT10" t="n">
         <v>8.6</v>
       </c>
-      <c r="BH10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>10</v>
-      </c>
       <c r="BU10" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BV10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -3143,28 +3143,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="G11" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
         <v>3</v>
@@ -3173,10 +3173,10 @@
         <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
@@ -3185,34 +3185,34 @@
         <v>4.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="X11" t="n">
         <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC11" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
         <v>40</v>
@@ -3221,19 +3221,19 @@
         <v>700</v>
       </c>
       <c r="AF11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI11" t="n">
         <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
         <v>65</v>
@@ -3251,82 +3251,82 @@
         <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX11" t="n">
         <v>11</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AY11" t="n">
         <v>10</v>
       </c>
-      <c r="AS11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>16</v>
       </c>
-      <c r="AW11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY11" t="n">
+      <c r="BA11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB11" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
         <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BE11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="BG11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH11" t="n">
         <v>2.94</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>15.5</v>
+        <v>2.44</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
@@ -3338,35 +3338,35 @@
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>11.5</v>
+        <v>2.34</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>2.34</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>13.5</v>
+        <v>2.38</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>11.5</v>
+        <v>2.34</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
         <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
@@ -3427,16 +3427,16 @@
         <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
         <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
         <v>1.88</v>
@@ -3451,7 +3451,7 @@
         <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
         <v>9.199999999999999</v>
@@ -3466,91 +3466,91 @@
         <v>21</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG12" t="n">
         <v>22</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>24</v>
       </c>
       <c r="AH12" t="n">
         <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AJ12" t="n">
         <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="n">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="AO12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AP12" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT12" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AY12" t="n">
         <v>19.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BD12" t="n">
         <v>34</v>
       </c>
       <c r="BE12" t="n">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="BF12" t="n">
         <v>36</v>
@@ -3562,10 +3562,10 @@
         <v>3.75</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK12" t="n">
         <v>5.2</v>
@@ -3574,25 +3574,25 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN12" t="n">
         <v>9.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12" t="n">
         <v>4.5</v>
@@ -3604,13 +3604,13 @@
         <v>11.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BX12" t="n">
         <v>27</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -3651,31 +3651,31 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I13" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="n">
         <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
         <v>1.22</v>
@@ -3684,88 +3684,88 @@
         <v>2.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R13" t="n">
         <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
         <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AB13" t="n">
         <v>11.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
         <v>11.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL13" t="n">
         <v>28</v>
       </c>
       <c r="AM13" t="n">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
         <v>7.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR13" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AS13" t="n">
         <v>48</v>
@@ -3774,13 +3774,13 @@
         <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV13" t="n">
         <v>19</v>
       </c>
       <c r="AW13" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3792,25 +3792,25 @@
         <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BB13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC13" t="n">
         <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG13" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G14" t="n">
         <v>2.7</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.76</v>
-      </c>
       <c r="H14" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="I14" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3929,7 +3929,7 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.29</v>
@@ -3947,16 +3947,16 @@
         <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
         <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X14" t="n">
         <v>16.5</v>
@@ -3974,7 +3974,7 @@
         <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
         <v>13</v>
@@ -3986,7 +3986,7 @@
         <v>18.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
         <v>16</v>
@@ -3995,19 +3995,19 @@
         <v>40</v>
       </c>
       <c r="AJ14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK14" t="n">
         <v>29</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO14" t="n">
         <v>25</v>
@@ -4022,25 +4022,25 @@
         <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT14" t="n">
         <v>11</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>14</v>
@@ -4049,19 +4049,19 @@
         <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BC14" t="n">
         <v>22</v>
       </c>
       <c r="BD14" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BE14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF14" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG14" t="n">
         <v>21</v>
@@ -4070,55 +4070,55 @@
         <v>3.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO14" t="n">
         <v>4.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR14" t="n">
         <v>32</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT14" t="n">
         <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV14" t="n">
         <v>22</v>
       </c>
       <c r="BW14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BX14" t="n">
         <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H15" t="n">
         <v>4.5</v>
       </c>
       <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K15" t="n">
         <v>5.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.24</v>
@@ -4195,31 +4195,31 @@
         <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T15" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X15" t="n">
         <v>85</v>
       </c>
       <c r="Y15" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z15" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AA15" t="n">
         <v>500</v>
@@ -4228,55 +4228,55 @@
         <v>29</v>
       </c>
       <c r="AC15" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
         <v>200</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AG15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AJ15" t="n">
         <v>32</v>
       </c>
       <c r="AK15" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AL15" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM15" t="n">
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AO15" t="n">
         <v>600</v>
       </c>
       <c r="AP15" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.7</v>
+        <v>12.5</v>
       </c>
       <c r="AT15" t="n">
         <v>8.4</v>
@@ -4288,43 +4288,43 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BF15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="n">
         <v>5.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BJ15" t="n">
         <v>8.800000000000001</v>
@@ -4336,16 +4336,16 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO15" t="n">
         <v>4.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BQ15" t="n">
         <v>6</v>
@@ -4354,10 +4354,10 @@
         <v>18.5</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU15" t="n">
         <v>6.6</v>
@@ -4366,13 +4366,13 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX15" t="n">
         <v>46</v>
       </c>
       <c r="BY15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
         <v>11</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>2.66</v>
       </c>
       <c r="G16" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H16" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I16" t="n">
         <v>2.94</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.4</v>
@@ -4452,7 +4452,7 @@
         <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T16" t="n">
         <v>1.7</v>
@@ -4461,7 +4461,7 @@
         <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W16" t="n">
         <v>1.55</v>
@@ -4512,28 +4512,28 @@
         <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN16" t="n">
         <v>24</v>
       </c>
       <c r="AO16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>10</v>
-      </c>
       <c r="AR16" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AS16" t="n">
         <v>18</v>
       </c>
       <c r="AT16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
         <v>7.4</v>
@@ -4545,10 +4545,10 @@
         <v>14.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
         <v>13.5</v>
@@ -4569,16 +4569,16 @@
         <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BH16" t="n">
         <v>3.55</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.6</v>
@@ -4602,13 +4602,13 @@
         <v>21</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT16" t="n">
         <v>6.2</v>
@@ -4626,7 +4626,7 @@
         <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>FK Kauno Zalgiris</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I17" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="R17" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W17" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="X17" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="Y17" t="n">
         <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD17" t="n">
         <v>950</v>
       </c>
-      <c r="AC17" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF17" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AG17" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ17" t="n">
         <v>500</v>
       </c>
       <c r="AK17" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL17" t="n">
         <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.28</v>
+        <v>6.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.26</v>
+        <v>8.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.28</v>
+        <v>5.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.31</v>
+        <v>7.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.29</v>
+        <v>6.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.31</v>
+        <v>9</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.21</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,239 +4912,239 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>14.5</v>
+        <v>2.66</v>
       </c>
       <c r="G18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X18" t="n">
         <v>17</v>
       </c>
-      <c r="H18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>200</v>
-      </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="AB18" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="AD18" t="n">
         <v>13</v>
       </c>
       <c r="AE18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>13.5</v>
       </c>
-      <c r="AF18" t="n">
-        <v>210</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AH18" t="n">
+      <c r="BA18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX18" t="n">
         <v>32</v>
       </c>
-      <c r="AI18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>220</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>200</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>18</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>90</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>18</v>
-      </c>
       <c r="BY18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G19" t="n">
         <v>1.59</v>
@@ -5184,10 +5184,10 @@
         <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K19" t="n">
         <v>5.2</v>
@@ -5199,16 +5199,16 @@
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R19" t="n">
         <v>1.59</v>
@@ -5220,7 +5220,7 @@
         <v>1.74</v>
       </c>
       <c r="U19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V19" t="n">
         <v>1.16</v>
@@ -5256,7 +5256,7 @@
         <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="AH19" t="n">
         <v>950</v>
@@ -5274,7 +5274,7 @@
         <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN19" t="n">
         <v>6.4</v>
@@ -5283,16 +5283,16 @@
         <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -5301,10 +5301,10 @@
         <v>10</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AX19" t="n">
         <v>9.4</v>
@@ -5313,10 +5313,10 @@
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB19" t="n">
         <v>12.5</v>
@@ -5325,19 +5325,19 @@
         <v>13</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF19" t="n">
         <v>5.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI19" t="n">
         <v>3.5</v>
@@ -5346,13 +5346,13 @@
         <v>10</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN19" t="n">
         <v>4.4</v>
@@ -5364,31 +5364,31 @@
         <v>9.4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,246 +5420,246 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.54</v>
+        <v>1.51</v>
       </c>
       <c r="G20" t="n">
-        <v>2.72</v>
+        <v>1.55</v>
       </c>
       <c r="H20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.8</v>
       </c>
-      <c r="I20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q20" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>1.59</v>
+        <v>2.8</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="Y20" t="n">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="Z20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV20" t="n">
         <v>21</v>
       </c>
-      <c r="AA20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AW20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB20" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="BC20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD20" t="n">
         <v>13</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BE20" t="n">
         <v>10.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>16.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BH20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI20" t="n">
         <v>3.85</v>
       </c>
-      <c r="BI20" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BJ20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP20" t="n">
-        <v>18.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ20" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BR20" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BS20" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BT20" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BV20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
         <v>9</v>
       </c>
       <c r="BX20" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BY20" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,239 +5674,239 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FK Kauno Zalgiris</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.64</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>1.69</v>
+        <v>18</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>1.22</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="K21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>210</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>650</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>220</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>18</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>90</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT21" t="n">
         <v>4.3</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X21" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT21" t="n">
+      <c r="BU21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BV21" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW21" t="n">
-        <v>1.93</v>
+        <v>5.6</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.93</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -5937,148 +5937,148 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="G22" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H22" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T22" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="U22" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W22" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="X22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
         <v>24</v>
       </c>
       <c r="Z22" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AA22" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC22" t="n">
         <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
         <v>240</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG22" t="n">
         <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AJ22" t="n">
         <v>15.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN22" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AO22" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP22" t="n">
-        <v>15.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ22" t="n">
         <v>20</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="AV22" t="n">
         <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="AY22" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB22" t="n">
         <v>13</v>
@@ -6087,25 +6087,25 @@
         <v>14</v>
       </c>
       <c r="BD22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BJ22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK22" t="n">
         <v>5.7</v>
@@ -6114,28 +6114,28 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>2.84</v>
+        <v>11</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BP22" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU22" t="n">
         <v>5.4</v>
@@ -6144,23 +6144,23 @@
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>2.76</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY22" t="n">
-        <v>2.78</v>
+        <v>10</v>
       </c>
       <c r="BZ22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CA22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="I23" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="J23" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K23" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.3</v>
@@ -6215,73 +6215,73 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="V23" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
         <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD23" t="n">
         <v>11</v>
       </c>
-      <c r="AA23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AE23" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF23" t="n">
         <v>160</v>
       </c>
       <c r="AG23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="AK23" t="n">
         <v>230</v>
@@ -6290,131 +6290,131 @@
         <v>240</v>
       </c>
       <c r="AM23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN23" t="n">
         <v>130</v>
       </c>
-      <c r="AN23" t="n">
-        <v>140</v>
-      </c>
       <c r="AO23" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AP23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>5</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>4</v>
-      </c>
       <c r="AR23" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AV23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH23" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="BI23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO23" t="n">
         <v>5.7</v>
       </c>
-      <c r="AY23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC23" t="n">
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>22</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="CA23" t="n">
         <v>5.9</v>
       </c>
-      <c r="BD23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>24</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>4.7</v>
-      </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -6436,145 +6436,145 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="G24" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="H24" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="U24" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W24" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="X24" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y24" t="n">
         <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB24" t="n">
         <v>12.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
         <v>13.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AG24" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AJ24" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AK24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL24" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM24" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="AN24" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="AO24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS24" t="n">
         <v>36</v>
       </c>
-      <c r="AP24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>26</v>
-      </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV24" t="n">
         <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AX24" t="n">
         <v>15</v>
@@ -6583,64 +6583,64 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD24" t="n">
         <v>30</v>
       </c>
-      <c r="BB24" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>32</v>
-      </c>
       <c r="BE24" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF24" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BQ24" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BR24" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT24" t="n">
         <v>6.2</v>
@@ -6652,13 +6652,13 @@
         <v>23</v>
       </c>
       <c r="BW24" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
@@ -6690,70 +6690,70 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H25" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I25" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.6</v>
       </c>
-      <c r="K25" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U25" t="n">
         <v>2.34</v>
       </c>
       <c r="V25" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X25" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y25" t="n">
         <v>14</v>
@@ -6762,157 +6762,157 @@
         <v>22</v>
       </c>
       <c r="AA25" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AB25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AF25" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG25" t="n">
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AJ25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL25" t="n">
         <v>36</v>
       </c>
-      <c r="AK25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>38</v>
-      </c>
       <c r="AM25" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN25" t="n">
         <v>19.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AT25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU25" t="n">
         <v>7.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA25" t="n">
         <v>30</v>
       </c>
       <c r="BB25" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BC25" t="n">
         <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BE25" t="n">
         <v>34</v>
       </c>
       <c r="BF25" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BI25" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK25" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BN25" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP25" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="BR25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS25" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BT25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV25" t="n">
         <v>22</v>
       </c>
       <c r="BW25" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BX25" t="n">
         <v>32</v>
       </c>
       <c r="BY25" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-17 02:38:54</t>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,244 +6939,752 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Forward Madison FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fort Wayne FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U26" t="n">
         <v>2.22</v>
       </c>
-      <c r="G26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.06</v>
-      </c>
       <c r="V26" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="W26" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="X26" t="n">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="Y26" t="n">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="Z26" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AA26" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AB26" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AD26" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AF26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG26" t="n">
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO26" t="n">
         <v>60</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>48</v>
-      </c>
       <c r="AP26" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AZ26" t="n">
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-17 04:48:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks FC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Monterey Bay FC</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X27" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-17 04:48:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Fort Wayne FC</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW28" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="AX28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB28" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BC28" t="n">
         <v>5</v>
       </c>
-      <c r="BD26" t="n">
+      <c r="BD28" t="n">
         <v>5.4</v>
       </c>
-      <c r="BE26" t="n">
+      <c r="BE28" t="n">
         <v>5.8</v>
       </c>
-      <c r="BF26" t="n">
+      <c r="BF28" t="n">
         <v>4.8</v>
       </c>
-      <c r="BG26" t="n">
+      <c r="BG28" t="n">
         <v>5.5</v>
       </c>
-      <c r="BH26" t="n">
+      <c r="BH28" t="n">
         <v>3.5</v>
       </c>
-      <c r="BI26" t="n">
+      <c r="BI28" t="n">
         <v>2.78</v>
       </c>
-      <c r="BJ26" t="n">
+      <c r="BJ28" t="n">
         <v>10</v>
       </c>
-      <c r="BK26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO26" t="n">
+      <c r="BK28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO28" t="n">
         <v>4.1</v>
       </c>
-      <c r="BP26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ26" t="n">
+      <c r="BP28" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ28" t="n">
         <v>6.4</v>
       </c>
-      <c r="BR26" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS26" t="n">
+      <c r="BR28" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS28" t="n">
         <v>7.6</v>
       </c>
-      <c r="BT26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV26" t="n">
+      <c r="BT28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV28" t="n">
         <v>29</v>
       </c>
-      <c r="BW26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>42</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ26" t="n">
+      <c r="BW28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ28" t="n">
         <v>29</v>
       </c>
-      <c r="CA26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>2026-06-17 02:38:54</t>
+      <c r="CA28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-17 04:48:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G2" t="n">
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="I2" t="n">
         <v>1.78</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
         <v>4.9</v>
@@ -881,28 +881,28 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V2" t="n">
         <v>2.26</v>
@@ -911,31 +911,31 @@
         <v>1.25</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="Y2" t="n">
         <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
         <v>16.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AG2" t="n">
         <v>20</v>
@@ -944,16 +944,16 @@
         <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK2" t="n">
         <v>120</v>
       </c>
       <c r="AL2" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
         <v>250</v>
@@ -965,31 +965,31 @@
         <v>7</v>
       </c>
       <c r="AP2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AV2" t="n">
         <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AY2" t="n">
         <v>16</v>
@@ -1001,86 +1001,86 @@
         <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BC2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN2" t="n">
         <v>9</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR2" t="n">
         <v>36</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>5.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BV2" t="n">
         <v>11.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BX2" t="n">
         <v>20</v>
       </c>
       <c r="BY2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>13</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
         <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
         <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P3" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T3" t="n">
         <v>1.41</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="V3" t="n">
         <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Y3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
         <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>19</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM3" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AR3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS3" t="n">
         <v>22</v>
       </c>
-      <c r="AS3" t="n">
-        <v>10</v>
-      </c>
       <c r="AT3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>22</v>
       </c>
       <c r="BB3" t="n">
         <v>22</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.4</v>
       </c>
       <c r="BK3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>6.4</v>
       </c>
-      <c r="BL3" t="n">
-        <v>60</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN3" t="n">
+      <c r="BR3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CA3" t="n">
         <v>5.8</v>
       </c>
-      <c r="BO3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>9.4</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="G4" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="I4" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="Z4" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC4" t="n">
         <v>14.5</v>
       </c>
       <c r="AD4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>440</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL4" t="n">
         <v>55</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AM4" t="n">
         <v>350</v>
       </c>
-      <c r="AF4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>280</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>340</v>
-      </c>
       <c r="AN4" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AU4" t="n">
         <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BO4" t="n">
         <v>3.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA4" t="n">
         <v>6.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H5" t="n">
         <v>6.4</v>
@@ -1643,19 +1643,19 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
         <v>4.7</v>
@@ -1664,22 +1664,22 @@
         <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X5" t="n">
         <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1688,43 +1688,43 @@
         <v>6.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE5" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AG5" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
         <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>700</v>
+        <v>280</v>
       </c>
       <c r="AP5" t="n">
         <v>9.199999999999999</v>
@@ -1733,10 +1733,10 @@
         <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
         <v>5.6</v>
@@ -1745,25 +1745,25 @@
         <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
         <v>18.5</v>
@@ -1772,13 +1772,13 @@
         <v>24</v>
       </c>
       <c r="BE5" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.05</v>
@@ -1790,13 +1790,13 @@
         <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
         <v>4.1</v>
@@ -1808,41 +1808,41 @@
         <v>13</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BR5" t="n">
         <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BT5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY5" t="n">
         <v>10</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>75</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>7.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>32</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>5.5</v>
@@ -1891,19 +1891,19 @@
         <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="O6" t="n">
         <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
         <v>2.7</v>
@@ -1915,46 +1915,46 @@
         <v>5.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W6" t="n">
         <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
         <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AB6" t="n">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AE6" t="n">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AG6" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AH6" t="n">
         <v>950</v>
@@ -1981,94 +1981,94 @@
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.2</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="n">
         <v>2.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT6" t="n">
         <v>4.4</v>
@@ -2080,23 +2080,23 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G7" t="n">
         <v>2.64</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="K7" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="L7" t="n">
         <v>1.64</v>
@@ -2151,10 +2151,10 @@
         <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P7" t="n">
         <v>1.47</v>
@@ -2166,19 +2166,19 @@
         <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
         <v>1.43</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2193,7 +2193,7 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
         <v>42</v>
@@ -2205,10 +2205,10 @@
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
@@ -2244,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="AT7" t="n">
         <v>4.2</v>
@@ -2253,40 +2253,40 @@
         <v>4.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.26</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -2405,10 +2405,10 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
         <v>2.44</v>
@@ -2420,16 +2420,16 @@
         <v>1.56</v>
       </c>
       <c r="S8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="W8" t="n">
         <v>1.25</v>
@@ -2438,13 +2438,13 @@
         <v>27</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
         <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AB8" t="n">
         <v>22</v>
@@ -2459,7 +2459,7 @@
         <v>17.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AG8" t="n">
         <v>19</v>
@@ -2474,40 +2474,40 @@
         <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AL8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN8" t="n">
         <v>55</v>
       </c>
-      <c r="AM8" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>48</v>
-      </c>
       <c r="AO8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
         <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT8" t="n">
         <v>18.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
         <v>14.5</v>
@@ -2516,85 +2516,85 @@
         <v>16</v>
       </c>
       <c r="AY8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="n">
         <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN8" t="n">
         <v>8.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BV8" t="n">
         <v>11.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>23</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G9" t="n">
         <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
         <v>7.8</v>
@@ -2650,7 +2650,7 @@
         <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.35</v>
@@ -2659,28 +2659,28 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="R9" t="n">
         <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V9" t="n">
         <v>1.15</v>
@@ -2689,37 +2689,37 @@
         <v>2.72</v>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="Z9" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AA9" t="n">
         <v>230</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
         <v>260</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>190</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>240</v>
@@ -2731,19 +2731,19 @@
         <v>16.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
         <v>7.8</v>
       </c>
       <c r="AO9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
         <v>20</v>
@@ -2752,10 +2752,10 @@
         <v>8.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
         <v>8.800000000000001</v>
@@ -2764,22 +2764,22 @@
         <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
         <v>13.5</v>
@@ -2788,13 +2788,13 @@
         <v>18</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
         <v>6.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
@@ -2818,7 +2818,7 @@
         <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP9" t="n">
         <v>10</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -2889,64 +2889,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="O10" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2955,10 +2955,10 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>27</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
         <v>950</v>
@@ -2970,10 +2970,10 @@
         <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="n">
         <v>700</v>
@@ -2982,137 +2982,137 @@
         <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
         <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC10" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC10" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BD10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN10" t="n">
         <v>4.6</v>
       </c>
-      <c r="BH10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BO10" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP10" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
         <v>2.22</v>
       </c>
       <c r="H11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
         <v>4.3</v>
@@ -3158,76 +3158,76 @@
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
         <v>1.81</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="AD11" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>700</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>700</v>
@@ -3245,128 +3245,128 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.5</v>
+        <v>2.64</v>
       </c>
       <c r="AS11" t="n">
-        <v>12</v>
+        <v>2.64</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="AU11" t="n">
         <v>5.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>11.5</v>
+        <v>2.86</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>2.74</v>
       </c>
       <c r="BA11" t="n">
-        <v>12</v>
+        <v>2.64</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>2.76</v>
       </c>
       <c r="BD11" t="n">
-        <v>11</v>
+        <v>2.82</v>
       </c>
       <c r="BE11" t="n">
-        <v>13</v>
+        <v>2.64</v>
       </c>
       <c r="BF11" t="n">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>12</v>
+        <v>2.86</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
@@ -3439,7 +3439,7 @@
         <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U12" t="n">
         <v>2.06</v>
@@ -3454,34 +3454,34 @@
         <v>16.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
         <v>10.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
         <v>10</v>
       </c>
       <c r="AE12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AF12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AG12" t="n">
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>36</v>
@@ -3496,13 +3496,13 @@
         <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AN12" t="n">
         <v>90</v>
       </c>
       <c r="AO12" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP12" t="n">
         <v>14.5</v>
@@ -3541,19 +3541,19 @@
         <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BD12" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BE12" t="n">
         <v>48</v>
       </c>
       <c r="BF12" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BG12" t="n">
         <v>8.800000000000001</v>
@@ -3562,37 +3562,37 @@
         <v>3.75</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BO12" t="n">
         <v>5</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT12" t="n">
         <v>4.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -3657,46 +3657,46 @@
         <v>1.68</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J13" t="n">
         <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
         <v>1.21</v>
@@ -3705,10 +3705,10 @@
         <v>2.46</v>
       </c>
       <c r="X13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z13" t="n">
         <v>46</v>
@@ -3717,7 +3717,7 @@
         <v>140</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
@@ -3726,19 +3726,19 @@
         <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
         <v>16.5</v>
@@ -3747,34 +3747,34 @@
         <v>16</v>
       </c>
       <c r="AL13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR13" t="n">
         <v>40</v>
       </c>
       <c r="AS13" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
         <v>19</v>
@@ -3786,85 +3786,85 @@
         <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BB13" t="n">
         <v>15.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE13" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BF13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="BJ13" t="n">
         <v>10</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL13" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BM13" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
         <v>11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BR13" t="n">
         <v>23</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT13" t="n">
         <v>9.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>46</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H14" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I14" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3938,28 +3938,28 @@
         <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
         <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
         <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3986,46 +3986,46 @@
         <v>18.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
         <v>16</v>
       </c>
       <c r="AI14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>40</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>38</v>
-      </c>
       <c r="AK14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL14" t="n">
         <v>38</v>
       </c>
       <c r="AM14" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT14" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>11</v>
       </c>
       <c r="AU14" t="n">
         <v>7.4</v>
@@ -4034,34 +4034,34 @@
         <v>11.5</v>
       </c>
       <c r="AW14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC14" t="n">
         <v>24</v>
       </c>
-      <c r="AX14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>22</v>
-      </c>
       <c r="BD14" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BF14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG14" t="n">
         <v>21</v>
@@ -4076,49 +4076,49 @@
         <v>9.4</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO14" t="n">
         <v>4.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR14" t="n">
         <v>32</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT14" t="n">
         <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV14" t="n">
         <v>22</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX14" t="n">
         <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H15" t="n">
         <v>4.5</v>
@@ -4171,10 +4171,10 @@
         <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.24</v>
@@ -4183,43 +4183,43 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="S15" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U15" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="V15" t="n">
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X15" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="Y15" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="Z15" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AA15" t="n">
         <v>500</v>
@@ -4228,31 +4228,31 @@
         <v>29</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>17.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE15" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AF15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH15" t="n">
         <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
         <v>32</v>
       </c>
       <c r="AK15" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
         <v>48</v>
@@ -4261,43 +4261,43 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO15" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AP15" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
         <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BA15" t="n">
         <v>16.5</v>
@@ -4306,40 +4306,40 @@
         <v>10.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD15" t="n">
         <v>13.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BI15" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BJ15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO15" t="n">
         <v>4.5</v>
@@ -4348,41 +4348,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BR15" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BS15" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU15" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G16" t="n">
         <v>2.84</v>
       </c>
       <c r="H16" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I16" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
         <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
         <v>1.4</v>
@@ -4443,31 +4443,31 @@
         <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
         <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
         <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
         <v>13</v>
@@ -4479,13 +4479,13 @@
         <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
         <v>8.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>65</v>
@@ -4494,28 +4494,28 @@
         <v>20</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI16" t="n">
         <v>150</v>
       </c>
       <c r="AJ16" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AK16" t="n">
         <v>48</v>
       </c>
       <c r="AL16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM16" t="n">
         <v>500</v>
       </c>
-      <c r="AM16" t="n">
-        <v>320</v>
-      </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
         <v>26</v>
@@ -4536,7 +4536,7 @@
         <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
@@ -4545,13 +4545,13 @@
         <v>14.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>18.5</v>
@@ -4566,19 +4566,19 @@
         <v>16.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
         <v>19.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.6</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN16" t="n">
         <v>6</v>
@@ -4602,13 +4602,13 @@
         <v>21</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BT16" t="n">
         <v>6.2</v>
@@ -4620,13 +4620,13 @@
         <v>22</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX16" t="n">
         <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -4667,76 +4667,76 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="H17" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="X17" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y17" t="n">
         <v>500</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>950</v>
       </c>
       <c r="Z17" t="n">
         <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB17" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
@@ -4745,22 +4745,22 @@
         <v>700</v>
       </c>
       <c r="AF17" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
         <v>36</v>
       </c>
       <c r="AH17" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
         <v>700</v>
       </c>
       <c r="AJ17" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AK17" t="n">
-        <v>65</v>
+        <v>15.5</v>
       </c>
       <c r="AL17" t="n">
         <v>500</v>
@@ -4769,85 +4769,85 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ17" t="n">
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV17" t="n">
         <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB17" t="n">
         <v>7.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="BH17" t="n">
         <v>3.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BO17" t="n">
         <v>3.7</v>
@@ -4856,31 +4856,31 @@
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.9</v>
+        <v>2.96</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.14</v>
+        <v>2.96</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -4921,25 +4921,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H18" t="n">
         <v>2.76</v>
       </c>
       <c r="I18" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -4948,193 +4948,193 @@
         <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T18" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF18" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
         <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI18" t="n">
         <v>38</v>
       </c>
       <c r="AJ18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>70</v>
       </c>
       <c r="AN18" t="n">
         <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="BB18" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BC18" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BD18" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE18" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG18" t="n">
         <v>18.5</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BJ18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO18" t="n">
         <v>4.9</v>
       </c>
       <c r="BP18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -5181,16 +5181,16 @@
         <v>1.59</v>
       </c>
       <c r="H19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
         <v>7</v>
       </c>
       <c r="J19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.3</v>
@@ -5217,10 +5217,10 @@
         <v>2.52</v>
       </c>
       <c r="T19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V19" t="n">
         <v>1.16</v>
@@ -5229,97 +5229,97 @@
         <v>2.68</v>
       </c>
       <c r="X19" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="Y19" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="Z19" t="n">
         <v>160</v>
       </c>
       <c r="AA19" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AE19" t="n">
         <v>210</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
         <v>9.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="AI19" t="n">
         <v>170</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16.5</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
         <v>6.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AQ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV19" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AW19" t="n">
         <v>11</v>
       </c>
-      <c r="AS19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT19" t="n">
+      <c r="AX19" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>9.4</v>
       </c>
       <c r="AY19" t="n">
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="BB19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC19" t="n">
         <v>13</v>
@@ -5328,22 +5328,22 @@
         <v>13.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF19" t="n">
         <v>5.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
         <v>6</v>
@@ -5358,7 +5358,7 @@
         <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP19" t="n">
         <v>9.4</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="G20" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L20" t="n">
         <v>1.26</v>
@@ -5459,28 +5459,28 @@
         <v>1.17</v>
       </c>
       <c r="P20" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="S20" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V20" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X20" t="n">
         <v>32</v>
@@ -5489,19 +5489,19 @@
         <v>34</v>
       </c>
       <c r="Z20" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AA20" t="n">
         <v>190</v>
       </c>
       <c r="AB20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE20" t="n">
         <v>190</v>
@@ -5510,7 +5510,7 @@
         <v>12</v>
       </c>
       <c r="AG20" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
         <v>20</v>
@@ -5519,58 +5519,58 @@
         <v>160</v>
       </c>
       <c r="AJ20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP20" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR20" t="n">
         <v>26</v>
       </c>
       <c r="AS20" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV20" t="n">
         <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BB20" t="n">
         <v>12.5</v>
@@ -5579,10 +5579,10 @@
         <v>12</v>
       </c>
       <c r="BD20" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BE20" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="BF20" t="n">
         <v>4.8</v>
@@ -5591,31 +5591,31 @@
         <v>15</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BJ20" t="n">
         <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BQ20" t="n">
         <v>5</v>
@@ -5624,16 +5624,16 @@
         <v>20</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT20" t="n">
         <v>11</v>
       </c>
       <c r="BU20" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW20" t="n">
         <v>9</v>
@@ -5642,17 +5642,17 @@
         <v>46</v>
       </c>
       <c r="BY20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CA20" t="n">
         <v>5.7</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -5686,22 +5686,22 @@
         <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
         <v>1.2</v>
       </c>
       <c r="I21" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="J21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="K21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
@@ -5713,22 +5713,22 @@
         <v>1.09</v>
       </c>
       <c r="P21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R21" t="n">
         <v>2.2</v>
       </c>
       <c r="S21" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="T21" t="n">
         <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
         <v>5.5</v>
@@ -5737,19 +5737,19 @@
         <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="Y21" t="n">
         <v>17.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA21" t="n">
         <v>11.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AC21" t="n">
         <v>21</v>
@@ -5761,10 +5761,10 @@
         <v>13.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AH21" t="n">
         <v>32</v>
@@ -5773,73 +5773,73 @@
         <v>30</v>
       </c>
       <c r="AJ21" t="n">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AL21" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AM21" t="n">
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AO21" t="n">
         <v>2.76</v>
       </c>
       <c r="AP21" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT21" t="n">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="AU21" t="n">
         <v>18</v>
       </c>
       <c r="AV21" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="n">
         <v>11</v>
       </c>
       <c r="AX21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AZ21" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
         <v>16</v>
       </c>
       <c r="BB21" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD21" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="BE21" t="n">
         <v>20</v>
       </c>
       <c r="BF21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG21" t="n">
         <v>2.52</v>
@@ -5854,37 +5854,37 @@
         <v>12</v>
       </c>
       <c r="BK21" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN21" t="n">
         <v>18</v>
       </c>
       <c r="BO21" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR21" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BT21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV21" t="n">
         <v>6.4</v>
@@ -5896,7 +5896,7 @@
         <v>17.5</v>
       </c>
       <c r="BY21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ21" t="n">
         <v>6.4</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="G22" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.35</v>
@@ -5961,37 +5961,37 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T22" t="n">
         <v>1.79</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.81</v>
-      </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
         <v>2.52</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="n">
         <v>24</v>
@@ -6009,43 +6009,43 @@
         <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AF22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
         <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
         <v>700</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK22" t="n">
         <v>16.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="n">
         <v>700</v>
       </c>
       <c r="AN22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO22" t="n">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>20</v>
@@ -6057,34 +6057,34 @@
         <v>10.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AV22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AY22" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB22" t="n">
         <v>13</v>
       </c>
       <c r="BC22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD22" t="n">
         <v>20</v>
@@ -6093,19 +6093,19 @@
         <v>10</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ22" t="n">
         <v>10</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>10.5</v>
       </c>
       <c r="BK22" t="n">
         <v>5.7</v>
@@ -6114,53 +6114,53 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN22" t="n">
         <v>4.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP22" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX22" t="n">
         <v>55</v>
       </c>
       <c r="BY22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA22" t="n">
         <v>7.2</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I23" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K23" t="n">
         <v>5.8</v>
@@ -6212,40 +6212,40 @@
         <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="T23" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
         <v>2.02</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="W23" t="n">
         <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y23" t="n">
         <v>11</v>
@@ -6257,7 +6257,7 @@
         <v>13.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AC23" t="n">
         <v>12.5</v>
@@ -6272,13 +6272,13 @@
         <v>160</v>
       </c>
       <c r="AG23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH23" t="n">
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AJ23" t="n">
         <v>290</v>
@@ -6290,103 +6290,103 @@
         <v>240</v>
       </c>
       <c r="AM23" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN23" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AO23" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AP23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AW23" t="n">
         <v>12</v>
       </c>
       <c r="AX23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF23" t="n">
         <v>8.4</v>
       </c>
-      <c r="AY23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH23" t="n">
         <v>4.5</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BJ23" t="n">
         <v>11</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN23" t="n">
         <v>12</v>
       </c>
       <c r="BO23" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT23" t="n">
         <v>4.3</v>
@@ -6395,26 +6395,26 @@
         <v>3.6</v>
       </c>
       <c r="BV23" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BW23" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ23" t="n">
         <v>13</v>
       </c>
       <c r="CA23" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J24" t="n">
         <v>3.7</v>
@@ -6472,19 +6472,19 @@
         <v>4.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T24" t="n">
         <v>1.68</v>
@@ -6493,43 +6493,43 @@
         <v>2.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W24" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y24" t="n">
         <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB24" t="n">
         <v>12.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>32</v>
       </c>
       <c r="AF24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG24" t="n">
         <v>12</v>
       </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI24" t="n">
         <v>40</v>
@@ -6538,19 +6538,19 @@
         <v>36</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="n">
         <v>18.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
         <v>15.5</v>
@@ -6559,10 +6559,10 @@
         <v>12.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
@@ -6577,19 +6577,19 @@
         <v>26</v>
       </c>
       <c r="AX24" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY24" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB24" t="n">
         <v>32</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>28</v>
       </c>
       <c r="BC24" t="n">
         <v>22</v>
@@ -6598,67 +6598,67 @@
         <v>30</v>
       </c>
       <c r="BE24" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG24" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BJ24" t="n">
         <v>9</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL24" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM24" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="BN24" t="n">
         <v>5.5</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP24" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BR24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX24" t="n">
         <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -6699,31 +6699,31 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G25" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H25" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J25" t="n">
         <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>1.29</v>
@@ -6738,70 +6738,70 @@
         <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
         <v>1.71</v>
       </c>
       <c r="U25" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V25" t="n">
         <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="AB25" t="n">
         <v>12</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD25" t="n">
         <v>13</v>
       </c>
       <c r="AE25" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AF25" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AG25" t="n">
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AJ25" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AK25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL25" t="n">
         <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO25" t="n">
         <v>26</v>
@@ -6813,64 +6813,64 @@
         <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS25" t="n">
         <v>25</v>
       </c>
       <c r="AT25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
         <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY25" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BD25" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF25" t="n">
         <v>17.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ25" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK25" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6885,10 +6885,10 @@
         <v>5</v>
       </c>
       <c r="BP25" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ25" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR25" t="n">
         <v>29</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -6953,58 +6953,58 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G26" t="n">
         <v>1.72</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.81</v>
-      </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J26" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
         <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R26" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S26" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="T26" t="n">
         <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V26" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W26" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="X26" t="n">
         <v>26</v>
@@ -7037,28 +7037,28 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
         <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM26" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AO26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
         <v>16.5</v>
@@ -7076,7 +7076,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
         <v>14.5</v>
@@ -7115,68 +7115,68 @@
         <v>1.01</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ26" t="n">
         <v>9.6</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN26" t="n">
         <v>4.9</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR26" t="n">
         <v>23</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
         <v>4.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
         <v>3.95</v>
@@ -7231,40 +7231,40 @@
         <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U27" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V27" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W27" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="X27" t="n">
         <v>18</v>
       </c>
       <c r="Y27" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z27" t="n">
         <v>40</v>
@@ -7279,37 +7279,37 @@
         <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>65</v>
       </c>
       <c r="AF27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM27" t="n">
         <v>120</v>
       </c>
       <c r="AN27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
         <v>70</v>
@@ -7330,28 +7330,28 @@
         <v>7</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA27" t="n">
         <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC27" t="n">
         <v>15</v>
@@ -7369,22 +7369,22 @@
         <v>1.01</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="BN27" t="n">
         <v>4.8</v>
@@ -7396,16 +7396,16 @@
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT27" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
         <v>5.7</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>
@@ -7461,61 +7461,61 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G28" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H28" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I28" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V28" t="n">
         <v>1.4</v>
       </c>
-      <c r="M28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W28" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X28" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="Y28" t="n">
         <v>15.5</v>
@@ -7524,167 +7524,167 @@
         <v>29</v>
       </c>
       <c r="AA28" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI28" t="n">
         <v>50</v>
       </c>
-      <c r="AF28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>60</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK28" t="n">
         <v>26</v>
       </c>
       <c r="AL28" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN28" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AO28" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX28" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AY28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA28" t="n">
         <v>5.1</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="BB28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN28" t="n">
         <v>5.7</v>
       </c>
-      <c r="AT28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BO28" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP28" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR28" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW28" t="n">
         <v>7</v>
       </c>
-      <c r="BU28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>29</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BX28" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BY28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ28" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-17 04:48:45</t>
+          <t>2026-06-17 06:58:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -857,88 +857,88 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="I2" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K2" t="n">
         <v>4.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="Y2" t="n">
         <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF2" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH2" t="n">
         <v>17</v>
@@ -950,19 +950,19 @@
         <v>500</v>
       </c>
       <c r="AK2" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>250</v>
       </c>
       <c r="AN2" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AP2" t="n">
         <v>14</v>
@@ -974,7 +974,7 @@
         <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
         <v>15.5</v>
@@ -992,16 +992,16 @@
         <v>34</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
         <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>40</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
         <v>22</v>
@@ -1013,74 +1013,74 @@
         <v>28</v>
       </c>
       <c r="BF2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="n">
         <v>4.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU2" t="n">
         <v>3.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BW2" t="n">
         <v>5.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.7</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
         <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.21</v>
@@ -1135,79 +1135,79 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S3" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="T3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="U3" t="n">
         <v>3.15</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
         <v>1.89</v>
       </c>
       <c r="X3" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AB3" t="n">
         <v>23</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM3" t="n">
         <v>40</v>
@@ -1216,46 +1216,46 @@
         <v>7.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AR3" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AT3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU3" t="n">
         <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="BB3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC3" t="n">
         <v>15.5</v>
@@ -1267,10 +1267,10 @@
         <v>29</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH3" t="n">
         <v>5.8</v>
@@ -1279,19 +1279,19 @@
         <v>4.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO3" t="n">
         <v>5.2</v>
@@ -1300,13 +1300,13 @@
         <v>13</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR3" t="n">
         <v>18</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT3" t="n">
         <v>7.8</v>
@@ -1324,17 +1324,17 @@
         <v>23</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>10.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -1365,97 +1365,97 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="G4" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="H4" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="L4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.38</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.43</v>
-      </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="Z4" t="n">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AB4" t="n">
         <v>7.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AE4" t="n">
-        <v>440</v>
+        <v>200</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>320</v>
+        <v>170</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AK4" t="n">
         <v>16</v>
@@ -1464,31 +1464,31 @@
         <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>350</v>
+        <v>790</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AP4" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
         <v>10</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
         <v>21</v>
@@ -1497,98 +1497,98 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
         <v>10</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BJ4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>29</v>
       </c>
       <c r="BS4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BU4" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>7.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -1619,67 +1619,67 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.69</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.67</v>
-      </c>
       <c r="Q5" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
         <v>1.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1688,16 +1688,16 @@
         <v>6.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
@@ -1709,10 +1709,10 @@
         <v>170</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
@@ -1721,7 +1721,7 @@
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO5" t="n">
         <v>280</v>
@@ -1730,43 +1730,43 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AR5" t="n">
         <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5" t="n">
         <v>5.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD5" t="n">
         <v>24</v>
@@ -1775,74 +1775,74 @@
         <v>9.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="n">
         <v>3.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="BJ5" t="n">
         <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO5" t="n">
         <v>3.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BR5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU5" t="n">
         <v>8.6</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="BV5" t="n">
+        <v>95</v>
+      </c>
+      <c r="BW5" t="n">
         <v>10.5</v>
       </c>
-      <c r="BU5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV5" t="n">
+      <c r="BX5" t="n">
         <v>1000</v>
       </c>
-      <c r="BW5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>90</v>
-      </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -1882,43 +1882,43 @@
         <v>1.88</v>
       </c>
       <c r="I6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
         <v>2.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T6" t="n">
         <v>2.26</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
         <v>2.04</v>
@@ -1936,7 +1936,7 @@
         <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AB6" t="n">
         <v>23</v>
@@ -1948,13 +1948,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE6" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="AG6" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="AH6" t="n">
         <v>950</v>
@@ -1975,25 +1975,25 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>230</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
         <v>6.6</v>
@@ -2005,40 +2005,40 @@
         <v>12</v>
       </c>
       <c r="AX6" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="n">
         <v>2.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ6" t="n">
         <v>13</v>
@@ -2050,19 +2050,19 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BN6" t="n">
         <v>9</v>
       </c>
       <c r="BO6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
@@ -2077,26 +2077,26 @@
         <v>3.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -2136,31 +2136,31 @@
         <v>3.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="L7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="R7" t="n">
         <v>1.17</v>
@@ -2175,7 +2175,7 @@
         <v>1.43</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
         <v>1.6</v>
@@ -2184,7 +2184,7 @@
         <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>75</v>
       </c>
       <c r="Z7" t="n">
         <v>500</v>
@@ -2196,7 +2196,7 @@
         <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -2217,7 +2217,7 @@
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -2238,55 +2238,55 @@
         <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU7" t="n">
         <v>4.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.04</v>
+        <v>2.64</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="BB7" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.04</v>
+        <v>2.64</v>
       </c>
       <c r="BF7" t="n">
         <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2298,59 +2298,59 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>16</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>16</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="I8" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -2408,88 +2408,88 @@
         <v>5.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
         <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="V8" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AB8" t="n">
         <v>22</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
         <v>10.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AG8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>330</v>
       </c>
       <c r="AK8" t="n">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="AL8" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AM8" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
         <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AP8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
         <v>10</v>
@@ -2498,94 +2498,94 @@
         <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AT8" t="n">
         <v>18.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AY8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA8" t="n">
         <v>15</v>
       </c>
-      <c r="BA8" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>9.6</v>
+        <v>40</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.6</v>
+        <v>40</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BF8" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BU8" t="n">
         <v>4.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
         <v>8.800000000000001</v>
@@ -2594,7 +2594,7 @@
         <v>23</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -2635,64 +2635,64 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.54</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.58</v>
-      </c>
       <c r="H9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S9" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
         <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z9" t="n">
         <v>65</v>
@@ -2707,13 +2707,13 @@
         <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE9" t="n">
         <v>260</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
@@ -2725,46 +2725,46 @@
         <v>240</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK9" t="n">
         <v>16.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>790</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AW9" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX9" t="n">
         <v>8.199999999999999</v>
@@ -2773,10 +2773,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB9" t="n">
         <v>12</v>
@@ -2785,80 +2785,80 @@
         <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="n">
         <v>4.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO9" t="n">
         <v>3.35</v>
       </c>
       <c r="BP9" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BT9" t="n">
         <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BV9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
         <v>60</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BZ9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.55</v>
@@ -2916,13 +2916,13 @@
         <v>2.86</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
         <v>1.59</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R10" t="n">
         <v>1.21</v>
@@ -2937,19 +2937,19 @@
         <v>1.74</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2970,7 +2970,7 @@
         <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
         <v>75</v>
@@ -2997,16 +2997,16 @@
         <v>180</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT10" t="n">
         <v>5.9</v>
@@ -3015,10 +3015,10 @@
         <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
@@ -3027,37 +3027,37 @@
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.4</v>
+        <v>3.55</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BK10" t="n">
         <v>6</v>
@@ -3084,7 +3084,7 @@
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10" t="n">
         <v>8.4</v>
@@ -3096,7 +3096,7 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
@@ -3108,11 +3108,11 @@
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -3143,97 +3143,97 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
         <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X11" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>700</v>
       </c>
       <c r="AF11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
         <v>40</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="n">
         <v>65</v>
@@ -3245,128 +3245,128 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO11" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.64</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.64</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.86</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.74</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.64</v>
+        <v>11</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.76</v>
+        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.82</v>
+        <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.64</v>
+        <v>12</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.86</v>
+        <v>36</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.38</v>
@@ -3421,22 +3421,22 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
         <v>1.9</v>
@@ -3445,172 +3445,172 @@
         <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" t="n">
         <v>9</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT12" t="n">
         <v>20</v>
       </c>
-      <c r="AC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AU12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>20</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
         <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="BC12" t="n">
         <v>50</v>
       </c>
       <c r="BD12" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE12" t="n">
         <v>50</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>48</v>
       </c>
       <c r="BF12" t="n">
         <v>65</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BH12" t="n">
         <v>3.75</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN12" t="n">
         <v>9.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BP12" t="n">
         <v>50</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR12" t="n">
         <v>55</v>
       </c>
       <c r="BS12" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BV12" t="n">
         <v>11.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BX12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="G13" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
         <v>4.5</v>
@@ -3675,97 +3675,97 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.23</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W13" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="X13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y13" t="n">
         <v>22</v>
       </c>
-      <c r="Y13" t="n">
-        <v>24</v>
-      </c>
       <c r="Z13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA13" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
       </c>
       <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG13" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL13" t="n">
         <v>29</v>
       </c>
       <c r="AM13" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP13" t="n">
         <v>19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AS13" t="n">
         <v>70</v>
@@ -3774,16 +3774,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
         <v>9.199999999999999</v>
@@ -3792,31 +3792,31 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB13" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE13" t="n">
         <v>60</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BH13" t="n">
         <v>4.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BJ13" t="n">
         <v>10</v>
@@ -3834,7 +3834,7 @@
         <v>4.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP13" t="n">
         <v>11</v>
@@ -3849,16 +3849,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX13" t="n">
         <v>46</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -3905,31 +3905,31 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="H14" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="I14" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.29</v>
@@ -3938,70 +3938,70 @@
         <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
         <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
         <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
         <v>16</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM14" t="n">
         <v>80</v>
@@ -4010,7 +4010,7 @@
         <v>21</v>
       </c>
       <c r="AO14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP14" t="n">
         <v>14.5</v>
@@ -4019,13 +4019,13 @@
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU14" t="n">
         <v>7.4</v>
@@ -4037,19 +4037,19 @@
         <v>26</v>
       </c>
       <c r="AX14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>14.5</v>
       </c>
       <c r="BA14" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB14" t="n">
         <v>34</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>32</v>
       </c>
       <c r="BC14" t="n">
         <v>24</v>
@@ -4061,64 +4061,64 @@
         <v>34</v>
       </c>
       <c r="BF14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH14" t="n">
         <v>3.7</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.4</v>
       </c>
       <c r="BK14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL14" t="n">
         <v>110</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP14" t="n">
         <v>20</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BR14" t="n">
         <v>32</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT14" t="n">
         <v>6.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -4159,34 +4159,34 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G15" t="n">
         <v>1.7</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.75</v>
-      </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P15" t="n">
         <v>3.05</v>
@@ -4195,7 +4195,7 @@
         <v>1.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="S15" t="n">
         <v>2.12</v>
@@ -4210,10 +4210,10 @@
         <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="X15" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Y15" t="n">
         <v>48</v>
@@ -4225,46 +4225,46 @@
         <v>500</v>
       </c>
       <c r="AB15" t="n">
-        <v>29</v>
+        <v>15.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
         <v>90</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AK15" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AM15" t="n">
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AO15" t="n">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="AP15" t="n">
         <v>16.5</v>
@@ -4276,7 +4276,7 @@
         <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
         <v>8.800000000000001</v>
@@ -4285,37 +4285,37 @@
         <v>10.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ15" t="n">
         <v>8.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>16.5</v>
+        <v>36</v>
       </c>
       <c r="BB15" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG15" t="n">
         <v>8.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -4413,142 +4413,142 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H16" t="n">
         <v>2.68</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.74</v>
-      </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
         <v>1.4</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
         <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T16" t="n">
         <v>1.7</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W16" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AB16" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AF16" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
         <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="AJ16" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AK16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL16" t="n">
         <v>48</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>85</v>
       </c>
       <c r="AM16" t="n">
         <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AP16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AS16" t="n">
         <v>18</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>7</v>
       </c>
       <c r="AV16" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW16" t="n">
         <v>14.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
         <v>14</v>
@@ -4566,19 +4566,19 @@
         <v>16.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF16" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.6</v>
@@ -4590,7 +4590,7 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BN16" t="n">
         <v>6</v>
@@ -4602,31 +4602,31 @@
         <v>21</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BR16" t="n">
         <v>34</v>
       </c>
       <c r="BS16" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU16" t="n">
         <v>5.1</v>
       </c>
       <c r="BV16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BX16" t="n">
         <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="G17" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="H17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>4.6</v>
       </c>
       <c r="K17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
@@ -4694,37 +4694,37 @@
         <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
         <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="U17" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="V17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="X17" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
         <v>500</v>
@@ -4733,10 +4733,10 @@
         <v>700</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
@@ -4745,7 +4745,7 @@
         <v>700</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>9.6</v>
       </c>
       <c r="AG17" t="n">
         <v>36</v>
@@ -4760,7 +4760,7 @@
         <v>180</v>
       </c>
       <c r="AK17" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="AL17" t="n">
         <v>500</v>
@@ -4772,67 +4772,67 @@
         <v>8.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AY17" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BC17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE17" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE17" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
@@ -4844,28 +4844,28 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT17" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU17" t="n">
         <v>8</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -4921,73 +4921,73 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H18" t="n">
         <v>2.72</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.76</v>
-      </c>
       <c r="I18" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
         <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
         <v>1.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T18" t="n">
         <v>1.56</v>
       </c>
       <c r="U18" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="n">
         <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA18" t="n">
         <v>120</v>
       </c>
       <c r="AB18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC18" t="n">
         <v>8</v>
@@ -4996,10 +4996,10 @@
         <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
         <v>12.5</v>
@@ -5026,34 +5026,34 @@
         <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT18" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>12</v>
-      </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="AX18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
@@ -5062,79 +5062,79 @@
         <v>12</v>
       </c>
       <c r="BA18" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="BC18" t="n">
         <v>11</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BF18" t="n">
         <v>17</v>
       </c>
       <c r="BG18" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU18" t="n">
         <v>5.1</v>
       </c>
       <c r="BV18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18" t="n">
         <v>29</v>
       </c>
       <c r="BY18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -5175,64 +5175,64 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I19" t="n">
         <v>7</v>
       </c>
       <c r="J19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K19" t="n">
         <v>5.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.48</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.52</v>
-      </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
         <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y19" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="Z19" t="n">
         <v>160</v>
@@ -5241,10 +5241,10 @@
         <v>180</v>
       </c>
       <c r="AB19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD19" t="n">
         <v>48</v>
@@ -5253,37 +5253,37 @@
         <v>210</v>
       </c>
       <c r="AF19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>95</v>
+        <v>19.5</v>
       </c>
       <c r="AI19" t="n">
         <v>170</v>
       </c>
       <c r="AJ19" t="n">
-        <v>80</v>
+        <v>14.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ19" t="n">
         <v>13</v>
@@ -5295,43 +5295,43 @@
         <v>12</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
         <v>11</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BE19" t="n">
         <v>11</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG19" t="n">
         <v>11</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -5432,19 +5432,19 @@
         <v>1.48</v>
       </c>
       <c r="G20" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I20" t="n">
         <v>7.8</v>
       </c>
       <c r="J20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.26</v>
@@ -5453,43 +5453,43 @@
         <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="T20" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="U20" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V20" t="n">
         <v>1.15</v>
       </c>
       <c r="W20" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="X20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y20" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="Z20" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AA20" t="n">
         <v>190</v>
@@ -5501,13 +5501,13 @@
         <v>12.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
         <v>190</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG20" t="n">
         <v>10.5</v>
@@ -5522,70 +5522,70 @@
         <v>15</v>
       </c>
       <c r="AK20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AO20" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AP20" t="n">
         <v>24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU20" t="n">
         <v>11</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>10</v>
       </c>
       <c r="AV20" t="n">
         <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>30</v>
+        <v>11.5</v>
       </c>
       <c r="BB20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE20" t="n">
         <v>12.5</v>
       </c>
-      <c r="BC20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>29</v>
-      </c>
       <c r="BF20" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BG20" t="n">
         <v>15</v>
@@ -5594,19 +5594,19 @@
         <v>4.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ20" t="n">
         <v>10</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN20" t="n">
         <v>4.6</v>
@@ -5615,7 +5615,7 @@
         <v>3.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ20" t="n">
         <v>5</v>
@@ -5624,35 +5624,35 @@
         <v>20</v>
       </c>
       <c r="BS20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT20" t="n">
         <v>11</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV20" t="n">
         <v>48</v>
       </c>
       <c r="BW20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX20" t="n">
         <v>46</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ20" t="n">
         <v>12</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -5683,46 +5683,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="I21" t="n">
         <v>1.21</v>
       </c>
       <c r="J21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.09</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="S21" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="T21" t="n">
         <v>1.8</v>
@@ -5731,16 +5731,16 @@
         <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="W21" t="n">
         <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Y21" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z21" t="n">
         <v>14.5</v>
@@ -5749,13 +5749,13 @@
         <v>11.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AC21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE21" t="n">
         <v>13.5</v>
@@ -5764,7 +5764,7 @@
         <v>200</v>
       </c>
       <c r="AG21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AH21" t="n">
         <v>32</v>
@@ -5785,13 +5785,13 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AO21" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AP21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>14.5</v>
@@ -5803,7 +5803,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT21" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="AU21" t="n">
         <v>18</v>
@@ -5812,25 +5812,25 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY21" t="n">
         <v>44</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
         <v>16</v>
       </c>
       <c r="BB21" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD21" t="n">
         <v>42</v>
@@ -5839,16 +5839,16 @@
         <v>20</v>
       </c>
       <c r="BF21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="BH21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BJ21" t="n">
         <v>12</v>
@@ -5860,25 +5860,25 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BO21" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT21" t="n">
         <v>4.4</v>
@@ -5896,17 +5896,17 @@
         <v>17.5</v>
       </c>
       <c r="BY21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ21" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H22" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L22" t="n">
         <v>1.35</v>
@@ -5961,7 +5961,7 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
         <v>1.24</v>
@@ -5976,10 +5976,10 @@
         <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T22" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U22" t="n">
         <v>2.08</v>
@@ -5988,46 +5988,46 @@
         <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X22" t="n">
         <v>21</v>
       </c>
       <c r="Y22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z22" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AA22" t="n">
         <v>700</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC22" t="n">
         <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE22" t="n">
         <v>700</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
         <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>700</v>
+        <v>230</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK22" t="n">
         <v>16.5</v>
@@ -6042,10 +6042,10 @@
         <v>7.8</v>
       </c>
       <c r="AO22" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP22" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AQ22" t="n">
         <v>20</v>
@@ -6054,19 +6054,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU22" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV22" t="n">
         <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX22" t="n">
         <v>9</v>
@@ -6075,10 +6075,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB22" t="n">
         <v>13</v>
@@ -6090,7 +6090,7 @@
         <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF22" t="n">
         <v>6.6</v>
@@ -6102,28 +6102,28 @@
         <v>4</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BP22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ22" t="n">
         <v>5.8</v>
@@ -6132,35 +6132,35 @@
         <v>23</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT22" t="n">
         <v>10</v>
       </c>
       <c r="BU22" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX22" t="n">
         <v>55</v>
       </c>
       <c r="BY22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ22" t="n">
         <v>16</v>
       </c>
       <c r="CA22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -6191,100 +6191,100 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="J23" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K23" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
         <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P23" t="n">
         <v>2.42</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R23" t="n">
         <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y23" t="n">
         <v>11</v>
       </c>
       <c r="Z23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AA23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>11</v>
-      </c>
       <c r="AE23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF23" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AG23" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
         <v>34</v>
       </c>
       <c r="AJ23" t="n">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="AK23" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AL23" t="n">
         <v>240</v>
@@ -6293,25 +6293,25 @@
         <v>130</v>
       </c>
       <c r="AN23" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="AO23" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AP23" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
-        <v>19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU23" t="n">
         <v>10</v>
@@ -6323,34 +6323,34 @@
         <v>12</v>
       </c>
       <c r="AX23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY23" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BA23" t="n">
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH23" t="n">
         <v>4.5</v>
@@ -6359,10 +6359,10 @@
         <v>3.75</v>
       </c>
       <c r="BJ23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6371,50 +6371,50 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BO23" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV23" t="n">
         <v>8.6</v>
       </c>
-      <c r="BT23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>9</v>
-      </c>
       <c r="BW23" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BZ23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G24" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H24" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="I24" t="n">
         <v>3.05</v>
@@ -6475,13 +6475,13 @@
         <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
         <v>3.15</v>
@@ -6496,7 +6496,7 @@
         <v>1.49</v>
       </c>
       <c r="W24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X24" t="n">
         <v>17</v>
@@ -6505,7 +6505,7 @@
         <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
         <v>48</v>
@@ -6517,7 +6517,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE24" t="n">
         <v>32</v>
@@ -6538,7 +6538,7 @@
         <v>36</v>
       </c>
       <c r="AK24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL24" t="n">
         <v>36</v>
@@ -6559,19 +6559,19 @@
         <v>12.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU24" t="n">
         <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW24" t="n">
         <v>26</v>
@@ -6583,7 +6583,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA24" t="n">
         <v>34</v>
@@ -6592,7 +6592,7 @@
         <v>32</v>
       </c>
       <c r="BC24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD24" t="n">
         <v>30</v>
@@ -6604,16 +6604,16 @@
         <v>16</v>
       </c>
       <c r="BG24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI24" t="n">
         <v>3.4</v>
       </c>
       <c r="BJ24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK24" t="n">
         <v>8.199999999999999</v>
@@ -6628,22 +6628,22 @@
         <v>5.5</v>
       </c>
       <c r="BO24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ24" t="n">
         <v>10</v>
       </c>
       <c r="BR24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS24" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BT24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU24" t="n">
         <v>5.6</v>
@@ -6658,7 +6658,7 @@
         <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H25" t="n">
         <v>2.96</v>
@@ -6711,10 +6711,10 @@
         <v>2.98</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.39</v>
@@ -6729,46 +6729,46 @@
         <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
         <v>1.87</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
         <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U25" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V25" t="n">
         <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X25" t="n">
         <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z25" t="n">
         <v>21</v>
       </c>
       <c r="AA25" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB25" t="n">
         <v>12</v>
       </c>
       <c r="AC25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
         <v>13</v>
@@ -6780,7 +6780,7 @@
         <v>17.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
         <v>16</v>
@@ -6798,55 +6798,55 @@
         <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN25" t="n">
         <v>19</v>
       </c>
       <c r="AO25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR25" t="n">
         <v>19</v>
       </c>
       <c r="AS25" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AT25" t="n">
         <v>11</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV25" t="n">
         <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA25" t="n">
         <v>36</v>
       </c>
       <c r="BB25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD25" t="n">
         <v>32</v>
@@ -6855,10 +6855,10 @@
         <v>36</v>
       </c>
       <c r="BF25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH25" t="n">
         <v>3.6</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G26" t="n">
         <v>1.72</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I26" t="n">
         <v>5.4</v>
@@ -6968,7 +6968,7 @@
         <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.3</v>
@@ -6998,7 +6998,7 @@
         <v>1.64</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V26" t="n">
         <v>1.23</v>
@@ -7010,7 +7010,7 @@
         <v>26</v>
       </c>
       <c r="Y26" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
         <v>46</v>
@@ -7019,7 +7019,7 @@
         <v>120</v>
       </c>
       <c r="AB26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC26" t="n">
         <v>12</v>
@@ -7043,7 +7043,7 @@
         <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -7055,67 +7055,67 @@
         <v>85</v>
       </c>
       <c r="AN26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
         <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC26" t="n">
         <v>14</v>
       </c>
-      <c r="BC26" t="n">
-        <v>13</v>
-      </c>
       <c r="BD26" t="n">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI26" t="n">
         <v>3.45</v>
@@ -7142,13 +7142,13 @@
         <v>11.5</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT26" t="n">
         <v>9</v>
@@ -7160,7 +7160,7 @@
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
@@ -7169,14 +7169,14 @@
         <v>8</v>
       </c>
       <c r="BZ26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA26" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G27" t="n">
         <v>2.02</v>
@@ -7222,40 +7222,40 @@
         <v>3.65</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M27" t="n">
         <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W27" t="n">
         <v>1.98</v>
@@ -7264,10 +7264,10 @@
         <v>18</v>
       </c>
       <c r="Y27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z27" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA27" t="n">
         <v>110</v>
@@ -7276,7 +7276,7 @@
         <v>11.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
         <v>22</v>
@@ -7306,13 +7306,13 @@
         <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP27" t="n">
         <v>11</v>
@@ -7327,7 +7327,7 @@
         <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU27" t="n">
         <v>6.4</v>
@@ -7342,7 +7342,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AZ27" t="n">
         <v>13.5</v>
@@ -7369,28 +7369,28 @@
         <v>1.01</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.55</v>
+        <v>2.66</v>
       </c>
       <c r="BN27" t="n">
         <v>4.8</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
@@ -7414,13 +7414,13 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>
@@ -7461,112 +7461,112 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="G28" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="H28" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="I28" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K28" t="n">
         <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P28" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="T28" t="n">
         <v>1.64</v>
       </c>
       <c r="U28" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V28" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="X28" t="n">
         <v>22</v>
       </c>
       <c r="Y28" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA28" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AB28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
         <v>17</v>
       </c>
       <c r="AE28" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI28" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL28" t="n">
         <v>34</v>
       </c>
-      <c r="AK28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>38</v>
-      </c>
       <c r="AM28" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN28" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP28" t="n">
         <v>11.5</v>
@@ -7578,19 +7578,19 @@
         <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT28" t="n">
         <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
         <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX28" t="n">
         <v>11.5</v>
@@ -7602,34 +7602,34 @@
         <v>13.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BG28" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ28" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK28" t="n">
         <v>4.8</v>
@@ -7638,53 +7638,53 @@
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU28" t="n">
         <v>5.7</v>
       </c>
-      <c r="BO28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS28" t="n">
+      <c r="BV28" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW28" t="n">
         <v>7.4</v>
       </c>
-      <c r="BT28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>25</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>7</v>
-      </c>
       <c r="BX28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY28" t="n">
         <v>7.8</v>
       </c>
       <c r="BZ28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CA28" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-17 06:58:24</t>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="I2" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="J2" t="n">
         <v>4.6</v>
       </c>
       <c r="K2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N2" t="n">
         <v>4.9</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="O2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.16</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X2" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="AB2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
         <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>22</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2" t="n">
         <v>13</v>
       </c>
       <c r="AX2" t="n">
-        <v>34</v>
+        <v>3.05</v>
       </c>
       <c r="AY2" t="n">
-        <v>17</v>
+        <v>3.05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>3.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>120</v>
       </c>
       <c r="BC2" t="n">
+        <v>60</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>960</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>590</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>910</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>690</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>950</v>
+      </c>
+      <c r="BY2" t="n">
         <v>22</v>
       </c>
-      <c r="BD2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>7</v>
-      </c>
       <c r="BZ2" t="n">
-        <v>12.5</v>
+        <v>960</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I3" t="n">
         <v>3.3</v>
       </c>
       <c r="J3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U3" t="n">
         <v>3.15</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="X3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Y3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z3" t="n">
         <v>32</v>
       </c>
-      <c r="Z3" t="n">
-        <v>38</v>
-      </c>
       <c r="AA3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>14.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AM3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AT3" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
         <v>25</v>
       </c>
       <c r="AX3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB3" t="n">
         <v>23</v>
       </c>
       <c r="BC3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>960</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>910</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU3" t="n">
         <v>5.8</v>
       </c>
-      <c r="BI3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BP3" t="n">
+      <c r="BV3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>950</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>960</v>
+      </c>
+      <c r="CA3" t="n">
         <v>13</v>
       </c>
-      <c r="BQ3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>8.4</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="H4" t="n">
         <v>10</v>
@@ -1377,218 +1377,218 @@
         <v>11.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="V4" t="n">
         <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
         <v>32</v>
       </c>
       <c r="Z4" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AA4" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AE4" t="n">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>380</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>470</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>32</v>
       </c>
-      <c r="AI4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ4" t="n">
+      <c r="BA4" t="n">
+        <v>150</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>220</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>940</v>
+      </c>
+      <c r="BM4" t="n">
         <v>12.5</v>
       </c>
-      <c r="AK4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>790</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>370</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY4" t="n">
+      <c r="BN4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BR4" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BT4" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BZ4" t="n">
-        <v>17.5</v>
+        <v>50</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H5" t="n">
         <v>7.2</v>
@@ -1643,37 +1643,37 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
         <v>20</v>
@@ -1682,7 +1682,7 @@
         <v>75</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>320</v>
       </c>
       <c r="AB5" t="n">
         <v>6.6</v>
@@ -1694,22 +1694,22 @@
         <v>32</v>
       </c>
       <c r="AE5" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
         <v>170</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK5" t="n">
         <v>22</v>
@@ -1718,25 +1718,25 @@
         <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="AN5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
         <v>16</v>
       </c>
       <c r="AR5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
         <v>5.6</v>
@@ -1745,22 +1745,22 @@
         <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX5" t="n">
         <v>7.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
         <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB5" t="n">
         <v>13.5</v>
@@ -1769,43 +1769,43 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG5" t="n">
         <v>11</v>
       </c>
-      <c r="BG5" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP5" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>12</v>
       </c>
       <c r="BQ5" t="n">
         <v>9</v>
@@ -1814,7 +1814,7 @@
         <v>34</v>
       </c>
       <c r="BS5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BT5" t="n">
         <v>11.5</v>
@@ -1826,23 +1826,23 @@
         <v>95</v>
       </c>
       <c r="BW5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
         <v>28</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="I6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
@@ -1900,13 +1900,13 @@
         <v>2.66</v>
       </c>
       <c r="O6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1915,130 +1915,130 @@
         <v>5.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AG6" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AH6" t="n">
         <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>460</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>180</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>220</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AP6" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR6" t="n">
         <v>8.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW6" t="n">
         <v>9.4</v>
       </c>
-      <c r="AW6" t="n">
-        <v>12</v>
-      </c>
       <c r="AX6" t="n">
-        <v>18.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BE6" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="n">
         <v>2.76</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ6" t="n">
         <v>13</v>
@@ -2053,50 +2053,50 @@
         <v>32</v>
       </c>
       <c r="BN6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
         <v>9</v>
       </c>
-      <c r="BO6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>9.4</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="H7" t="n">
         <v>3.7</v>
@@ -2142,31 +2142,31 @@
         <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="L7" t="n">
         <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T7" t="n">
         <v>2.06</v>
@@ -2175,25 +2175,25 @@
         <v>1.43</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>75</v>
+        <v>18.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
         <v>8.800000000000001</v>
@@ -2202,91 +2202,91 @@
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH7" t="n">
         <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AK7" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>600</v>
+        <v>130</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="AQ7" t="n">
         <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AT7" t="n">
         <v>5.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV7" t="n">
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.64</v>
+        <v>3.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.54</v>
+        <v>3.35</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -2381,220 +2381,220 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J8" t="n">
         <v>4.2</v>
       </c>
-      <c r="G8" t="n">
+      <c r="K8" t="n">
         <v>4.6</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.63</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z8" t="n">
         <v>13</v>
       </c>
-      <c r="Z8" t="n">
-        <v>15</v>
-      </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
         <v>10.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>28</v>
       </c>
       <c r="AJ8" t="n">
-        <v>330</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="n">
         <v>55</v>
       </c>
       <c r="AL8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO8" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AP8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AY8" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BC8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BD8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BE8" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BF8" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="BG8" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BU8" t="n">
         <v>4.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BW8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>22</v>
+      </c>
+      <c r="BY8" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>23</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9" t="n">
         <v>4.6</v>
@@ -2653,55 +2653,55 @@
         <v>5.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y9" t="n">
         <v>27</v>
       </c>
       <c r="Z9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA9" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
@@ -2710,52 +2710,52 @@
         <v>30</v>
       </c>
       <c r="AE9" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AJ9" t="n">
         <v>14</v>
       </c>
       <c r="AK9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>790</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AO9" t="n">
         <v>170</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AR9" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
         <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU9" t="n">
         <v>9.4</v>
@@ -2773,92 +2773,92 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
         <v>10.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
         <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BE9" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG9" t="n">
         <v>10.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT9" t="n">
         <v>11</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BY9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ9" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -2901,40 +2901,40 @@
         <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
         <v>3.35</v>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M10" t="n">
         <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
         <v>1.59</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R10" t="n">
         <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
         <v>1.22</v>
@@ -2946,52 +2946,52 @@
         <v>9.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>180</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
         <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AI10" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>240</v>
       </c>
       <c r="AN10" t="n">
-        <v>600</v>
+        <v>24</v>
       </c>
       <c r="AO10" t="n">
         <v>180</v>
@@ -3000,73 +3000,73 @@
         <v>8.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB10" t="n">
         <v>20</v>
       </c>
-      <c r="BA10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>10</v>
-      </c>
       <c r="BC10" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="BE10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BJ10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN10" t="n">
         <v>4.6</v>
@@ -3075,16 +3075,16 @@
         <v>3.95</v>
       </c>
       <c r="BP10" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT10" t="n">
         <v>8.4</v>
@@ -3093,26 +3093,26 @@
         <v>5.8</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -3143,25 +3143,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="H11" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
@@ -3170,203 +3170,203 @@
         <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AB11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT11" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF11" t="n">
         <v>23</v>
       </c>
-      <c r="AE11" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BG11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BO11" t="n">
         <v>4.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
         <v>11.5</v>
       </c>
-      <c r="BT11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>13</v>
-      </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -3397,220 +3397,220 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G12" t="n">
         <v>6.2</v>
       </c>
-      <c r="G12" t="n">
-        <v>6.4</v>
-      </c>
       <c r="H12" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="I12" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="J12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K12" t="n">
         <v>4.3</v>
       </c>
-      <c r="K12" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AB12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG12" t="n">
         <v>23</v>
       </c>
-      <c r="AC12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>25</v>
-      </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AK12" t="n">
         <v>90</v>
       </c>
       <c r="AL12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AO12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
         <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AY12" t="n">
         <v>20</v>
       </c>
-      <c r="AU12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>21</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA12" t="n">
         <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BC12" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BD12" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BE12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BF12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BG12" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>140</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>50</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BR12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV12" t="n">
         <v>11.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -3651,46 +3651,46 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G13" t="n">
         <v>1.73</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.74</v>
-      </c>
       <c r="H13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
         <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
         <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
         <v>1.75</v>
@@ -3699,19 +3699,19 @@
         <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
         <v>22</v>
       </c>
       <c r="Z13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA13" t="n">
         <v>120</v>
@@ -3723,64 +3723,64 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
         <v>11.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM13" t="n">
         <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AO13" t="n">
         <v>55</v>
       </c>
       <c r="AP13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS13" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
@@ -3789,10 +3789,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB13" t="n">
         <v>16.5</v>
@@ -3804,67 +3804,67 @@
         <v>27</v>
       </c>
       <c r="BE13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BJ13" t="n">
         <v>10</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL13" t="n">
         <v>110</v>
       </c>
       <c r="BM13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO13" t="n">
         <v>4.1</v>
       </c>
       <c r="BP13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX13" t="n">
         <v>46</v>
       </c>
       <c r="BY13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I14" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3932,16 +3932,16 @@
         <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
         <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
         <v>3.25</v>
@@ -3953,31 +3953,31 @@
         <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
         <v>32</v>
@@ -3986,40 +3986,40 @@
         <v>17.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
         <v>38</v>
       </c>
       <c r="AK14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL14" t="n">
         <v>36</v>
       </c>
       <c r="AM14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="n">
         <v>21</v>
       </c>
       <c r="AO14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ14" t="n">
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AS14" t="n">
         <v>40</v>
@@ -4031,13 +4031,13 @@
         <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
         <v>10.5</v>
@@ -4052,73 +4052,73 @@
         <v>34</v>
       </c>
       <c r="BC14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BF14" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BL14" t="n">
         <v>110</v>
       </c>
       <c r="BM14" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="BR14" t="n">
         <v>32</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BX14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="H15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J15" t="n">
         <v>4.8</v>
       </c>
-      <c r="I15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.9</v>
-      </c>
       <c r="K15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
@@ -4189,67 +4189,67 @@
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U15" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="X15" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z15" t="n">
         <v>85</v>
       </c>
-      <c r="Y15" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>55</v>
-      </c>
       <c r="AA15" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AB15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC15" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
         <v>90</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
         <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK15" t="n">
         <v>15</v>
@@ -4258,109 +4258,109 @@
         <v>38</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AS15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU15" t="n">
         <v>11</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>10.5</v>
       </c>
       <c r="AV15" t="n">
         <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
         <v>36</v>
       </c>
       <c r="BB15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BD15" t="n">
         <v>18.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="BH15" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BJ15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BR15" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4369,20 +4369,20 @@
         <v>10.5</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>10.5</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>11.5</v>
-      </c>
       <c r="CA15" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I16" t="n">
         <v>2.88</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.7</v>
-      </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
         <v>3.55</v>
@@ -4437,7 +4437,7 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
         <v>1.3</v>
@@ -4446,7 +4446,7 @@
         <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R16" t="n">
         <v>1.38</v>
@@ -4455,130 +4455,130 @@
         <v>3.35</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X16" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
         <v>16</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AI16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV16" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AW16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL16" t="n">
+      <c r="BA16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE16" t="n">
         <v>48</v>
       </c>
-      <c r="AM16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO16" t="n">
+      <c r="BF16" t="n">
         <v>22</v>
       </c>
-      <c r="AP16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7</v>
-      </c>
       <c r="BG16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.6</v>
@@ -4587,10 +4587,10 @@
         <v>7</v>
       </c>
       <c r="BL16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM16" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN16" t="n">
         <v>6</v>
@@ -4599,34 +4599,34 @@
         <v>5</v>
       </c>
       <c r="BP16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="n">
         <v>34</v>
       </c>
       <c r="BS16" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BT16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX16" t="n">
         <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
@@ -4691,142 +4691,142 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
         <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AA17" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AJ17" t="n">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO17" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AP17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AW17" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AX17" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AY17" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE17" t="n">
         <v>6.4</v>
       </c>
-      <c r="BA17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BH17" t="n">
         <v>3.85</v>
@@ -4835,7 +4835,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK17" t="n">
         <v>8.4</v>
@@ -4844,7 +4844,7 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN17" t="n">
         <v>4.1</v>
@@ -4853,7 +4853,7 @@
         <v>3.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BQ17" t="n">
         <v>6.4</v>
@@ -4862,10 +4862,10 @@
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BT17" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
         <v>8</v>
@@ -4874,13 +4874,13 @@
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>2.96</v>
+        <v>7</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.96</v>
+        <v>7</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -4921,25 +4921,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="G18" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="H18" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="I18" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
         <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -4948,139 +4948,139 @@
         <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
         <v>1.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
         <v>2.96</v>
       </c>
       <c r="T18" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U18" t="n">
         <v>2.46</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="X18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF18" t="n">
         <v>19</v>
       </c>
-      <c r="Y18" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>23</v>
-      </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
         <v>15</v>
       </c>
       <c r="AI18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>38</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>48</v>
-      </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM18" t="n">
         <v>70</v>
       </c>
       <c r="AN18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG18" t="n">
         <v>21</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>17</v>
       </c>
       <c r="BH18" t="n">
         <v>4.2</v>
@@ -5092,49 +5092,49 @@
         <v>8.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BP18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV18" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX18" t="n">
         <v>29</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G19" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="H19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J19" t="n">
         <v>4.7</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.29</v>
@@ -5199,43 +5199,43 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O19" t="n">
         <v>1.19</v>
       </c>
       <c r="P19" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S19" t="n">
         <v>2.48</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V19" t="n">
         <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="X19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y19" t="n">
         <v>46</v>
       </c>
       <c r="Z19" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AA19" t="n">
         <v>180</v>
@@ -5247,25 +5247,25 @@
         <v>12</v>
       </c>
       <c r="AD19" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="AF19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH19" t="n">
         <v>19.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -5274,13 +5274,13 @@
         <v>28</v>
       </c>
       <c r="AM19" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN19" t="n">
         <v>6</v>
       </c>
       <c r="AO19" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AP19" t="n">
         <v>22</v>
@@ -5289,13 +5289,13 @@
         <v>13</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
         <v>10.5</v>
@@ -5304,19 +5304,19 @@
         <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
         <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="BB19" t="n">
         <v>12.5</v>
@@ -5328,13 +5328,13 @@
         <v>14</v>
       </c>
       <c r="BE19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BH19" t="n">
         <v>4.4</v>
@@ -5346,7 +5346,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5385,7 +5385,7 @@
         <v>11.5</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY19" t="n">
         <v>11.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G20" t="n">
         <v>1.5</v>
@@ -5441,115 +5441,115 @@
         <v>7.8</v>
       </c>
       <c r="J20" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K20" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P20" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R20" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="S20" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="T20" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Y20" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Z20" t="n">
         <v>75</v>
       </c>
       <c r="AA20" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC20" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD20" t="n">
         <v>27</v>
       </c>
       <c r="AE20" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="AF20" t="n">
         <v>12.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK20" t="n">
         <v>14</v>
       </c>
       <c r="AL20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AP20" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS20" t="n">
         <v>13</v>
       </c>
-      <c r="AR20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>10</v>
-      </c>
       <c r="AT20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU20" t="n">
         <v>11</v>
@@ -5558,19 +5558,19 @@
         <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BB20" t="n">
         <v>13</v>
@@ -5582,77 +5582,77 @@
         <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG20" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BH20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>80</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN20" t="n">
         <v>4.8</v>
       </c>
-      <c r="BI20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BO20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ20" t="n">
         <v>5</v>
       </c>
       <c r="BR20" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT20" t="n">
         <v>11</v>
       </c>
       <c r="BU20" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX20" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BY20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
         <v>1.19</v>
@@ -5695,10 +5695,10 @@
         <v>1.21</v>
       </c>
       <c r="J21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
         <v>1.19</v>
@@ -5710,25 +5710,25 @@
         <v>10.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P21" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S21" t="n">
         <v>1.72</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V21" t="n">
         <v>5.7</v>
@@ -5743,7 +5743,7 @@
         <v>18.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA21" t="n">
         <v>11.5</v>
@@ -5752,7 +5752,7 @@
         <v>100</v>
       </c>
       <c r="AC21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD21" t="n">
         <v>13.5</v>
@@ -5761,10 +5761,10 @@
         <v>13.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AH21" t="n">
         <v>32</v>
@@ -5776,40 +5776,40 @@
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AL21" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AM21" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AN21" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AO21" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AP21" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR21" t="n">
         <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT21" t="n">
-        <v>32</v>
+        <v>13.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW21" t="n">
         <v>11.5</v>
@@ -5818,13 +5818,13 @@
         <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
         <v>13</v>
@@ -5833,16 +5833,16 @@
         <v>12</v>
       </c>
       <c r="BD21" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BF21" t="n">
         <v>12</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BH21" t="n">
         <v>6.4</v>
@@ -5851,7 +5851,7 @@
         <v>5.6</v>
       </c>
       <c r="BJ21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK21" t="n">
         <v>6.6</v>
@@ -5860,31 +5860,31 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT21" t="n">
         <v>4.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BV21" t="n">
         <v>6.4</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G22" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H22" t="n">
         <v>6.2</v>
       </c>
       <c r="I22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.35</v>
@@ -5961,52 +5961,52 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
         <v>2.92</v>
       </c>
       <c r="T22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
         <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="X22" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z22" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AA22" t="n">
         <v>700</v>
       </c>
       <c r="AB22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC22" t="n">
         <v>10</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
         <v>26</v>
@@ -6024,37 +6024,37 @@
         <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK22" t="n">
         <v>16.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
         <v>700</v>
       </c>
       <c r="AN22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO22" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AP22" t="n">
         <v>16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR22" t="n">
-        <v>9.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT22" t="n">
         <v>8.199999999999999</v>
@@ -6063,10 +6063,10 @@
         <v>8.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>9</v>
@@ -6078,89 +6078,89 @@
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BB22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC22" t="n">
         <v>13.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="n">
         <v>4</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ22" t="n">
         <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO22" t="n">
         <v>3.8</v>
       </c>
       <c r="BP22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BR22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BT22" t="n">
         <v>10</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BX22" t="n">
         <v>55</v>
       </c>
       <c r="BY22" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -6197,10 +6197,10 @@
         <v>10.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I23" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J23" t="n">
         <v>4.9</v>
@@ -6218,10 +6218,10 @@
         <v>5.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q23" t="n">
         <v>1.61</v>
@@ -6233,19 +6233,19 @@
         <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V23" t="n">
         <v>3.15</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y23" t="n">
         <v>11</v>
@@ -6257,13 +6257,13 @@
         <v>13</v>
       </c>
       <c r="AB23" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AC23" t="n">
         <v>13</v>
       </c>
       <c r="AD23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>15</v>
@@ -6272,16 +6272,16 @@
         <v>170</v>
       </c>
       <c r="AG23" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH23" t="n">
         <v>26</v>
       </c>
       <c r="AI23" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AK23" t="n">
         <v>260</v>
@@ -6290,16 +6290,16 @@
         <v>240</v>
       </c>
       <c r="AM23" t="n">
-        <v>130</v>
+        <v>790</v>
       </c>
       <c r="AN23" t="n">
         <v>180</v>
       </c>
       <c r="AO23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AP23" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AQ23" t="n">
         <v>8.6</v>
@@ -6311,7 +6311,7 @@
         <v>10</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AU23" t="n">
         <v>10</v>
@@ -6323,31 +6323,31 @@
         <v>12</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ23" t="n">
         <v>20</v>
       </c>
       <c r="BA23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF23" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BG23" t="n">
         <v>4.7</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G24" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H24" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I24" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J24" t="n">
         <v>3.7</v>
@@ -6472,7 +6472,7 @@
         <v>4.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P24" t="n">
         <v>2.14</v>
@@ -6493,16 +6493,16 @@
         <v>2.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W24" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z24" t="n">
         <v>21</v>
@@ -6517,10 +6517,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF24" t="n">
         <v>17.5</v>
@@ -6547,25 +6547,25 @@
         <v>80</v>
       </c>
       <c r="AN24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR24" t="n">
         <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
         <v>7.6</v>
@@ -6574,22 +6574,22 @@
         <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY24" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
         <v>34</v>
       </c>
       <c r="BB24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
         <v>23</v>
@@ -6598,10 +6598,10 @@
         <v>30</v>
       </c>
       <c r="BE24" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG24" t="n">
         <v>21</v>
@@ -6613,16 +6613,16 @@
         <v>3.4</v>
       </c>
       <c r="BJ24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL24" t="n">
         <v>100</v>
       </c>
       <c r="BM24" t="n">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="BN24" t="n">
         <v>5.5</v>
@@ -6640,7 +6640,7 @@
         <v>29</v>
       </c>
       <c r="BS24" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="BT24" t="n">
         <v>6.2</v>
@@ -6658,7 +6658,7 @@
         <v>32</v>
       </c>
       <c r="BY24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -6699,19 +6699,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G25" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H25" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
         <v>3.7</v>
@@ -6726,7 +6726,7 @@
         <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P25" t="n">
         <v>2.12</v>
@@ -6747,22 +6747,22 @@
         <v>2.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X25" t="n">
         <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
         <v>21</v>
       </c>
       <c r="AA25" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AB25" t="n">
         <v>12</v>
@@ -6774,7 +6774,7 @@
         <v>13</v>
       </c>
       <c r="AE25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF25" t="n">
         <v>17.5</v>
@@ -6792,31 +6792,31 @@
         <v>36</v>
       </c>
       <c r="AK25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL25" t="n">
         <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AN25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO25" t="n">
         <v>25</v>
       </c>
       <c r="AP25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>12.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT25" t="n">
         <v>11</v>
@@ -6825,25 +6825,25 @@
         <v>7.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW25" t="n">
         <v>28</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY25" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
         <v>36</v>
       </c>
       <c r="BB25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC25" t="n">
         <v>23</v>
@@ -6855,13 +6855,13 @@
         <v>36</v>
       </c>
       <c r="BF25" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG25" t="n">
         <v>22</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI25" t="n">
         <v>3.3</v>
@@ -6870,49 +6870,49 @@
         <v>9</v>
       </c>
       <c r="BK25" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="BN25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO25" t="n">
         <v>5</v>
       </c>
       <c r="BP25" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS25" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT25" t="n">
         <v>6.2</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV25" t="n">
         <v>22</v>
       </c>
       <c r="BW25" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX25" t="n">
         <v>32</v>
       </c>
       <c r="BY25" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G26" t="n">
         <v>1.72</v>
@@ -6962,10 +6962,10 @@
         <v>4.9</v>
       </c>
       <c r="I26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
         <v>4.7</v>
@@ -6995,13 +6995,13 @@
         <v>2.56</v>
       </c>
       <c r="T26" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U26" t="n">
         <v>2.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W26" t="n">
         <v>2.38</v>
@@ -7010,7 +7010,7 @@
         <v>26</v>
       </c>
       <c r="Y26" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="Z26" t="n">
         <v>46</v>
@@ -7025,7 +7025,7 @@
         <v>12</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE26" t="n">
         <v>65</v>
@@ -7061,19 +7061,19 @@
         <v>55</v>
       </c>
       <c r="AP26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>19.5</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AR26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU26" t="n">
         <v>9</v>
@@ -7082,37 +7082,37 @@
         <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX26" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
         <v>14</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH26" t="n">
         <v>4.5</v>
@@ -7142,7 +7142,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR26" t="n">
         <v>22</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G27" t="n">
         <v>2.02</v>
       </c>
       <c r="H27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J27" t="n">
         <v>3.65</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
         <v>1.39</v>
@@ -7234,25 +7234,25 @@
         <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U27" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V27" t="n">
         <v>1.28</v>
@@ -7261,22 +7261,22 @@
         <v>1.98</v>
       </c>
       <c r="X27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y27" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB27" t="n">
         <v>11.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
         <v>22</v>
@@ -7288,10 +7288,10 @@
         <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>70</v>
@@ -7306,73 +7306,73 @@
         <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN27" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>11.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.05</v>
+        <v>3.85</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.2</v>
+        <v>3.1</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="AV27" t="n">
         <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="AY27" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="AZ27" t="n">
         <v>13.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>16.5</v>
+        <v>3.7</v>
       </c>
       <c r="BC27" t="n">
         <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.05</v>
+        <v>3.85</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
@@ -7384,7 +7384,7 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="BN27" t="n">
         <v>4.8</v>
@@ -7402,7 +7402,7 @@
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>4.3</v>
+        <v>1.98</v>
       </c>
       <c r="BT27" t="n">
         <v>1000</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
         <v>2.1</v>
@@ -7476,7 +7476,7 @@
         <v>3.8</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L28" t="n">
         <v>1.34</v>
@@ -7485,13 +7485,13 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
         <v>1.71</v>
@@ -7500,43 +7500,43 @@
         <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T28" t="n">
         <v>1.64</v>
       </c>
       <c r="U28" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V28" t="n">
         <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA28" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC28" t="n">
         <v>11</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF28" t="n">
         <v>16</v>
@@ -7545,64 +7545,64 @@
         <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ28" t="n">
         <v>27</v>
       </c>
       <c r="AK28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
         <v>34</v>
       </c>
       <c r="AM28" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN28" t="n">
         <v>13.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AP28" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>18</v>
+        <v>5.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX28" t="n">
         <v>11.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB28" t="n">
         <v>17.5</v>
@@ -7611,16 +7611,16 @@
         <v>14.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BH28" t="n">
         <v>4</v>
@@ -7632,16 +7632,16 @@
         <v>9.6</v>
       </c>
       <c r="BK28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO28" t="n">
         <v>4</v>
@@ -7650,13 +7650,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ28" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR28" t="n">
         <v>26</v>
       </c>
       <c r="BS28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT28" t="n">
         <v>7.6</v>
@@ -7668,23 +7668,23 @@
         <v>30</v>
       </c>
       <c r="BW28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX28" t="n">
         <v>38</v>
       </c>
       <c r="BY28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ28" t="n">
         <v>21</v>
       </c>
       <c r="CA28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,93 +843,93 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Birmingham Legion FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S2" t="n">
+        <v>55</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.32</v>
       </c>
-      <c r="I2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB2" t="n">
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -938,13 +938,13 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.06</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -956,67 +956,67 @@
         <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>22</v>
+        <v>1.51</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="AU2" t="n">
-        <v>22</v>
+        <v>3.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>24</v>
+        <v>3.55</v>
       </c>
       <c r="AW2" t="n">
-        <v>15.5</v>
+        <v>3.85</v>
       </c>
       <c r="AX2" t="n">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="AY2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.94</v>
+        <v>3.85</v>
       </c>
       <c r="BB2" t="n">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="BC2" t="n">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BF2" t="n">
-        <v>17.5</v>
+        <v>3.85</v>
       </c>
       <c r="BG2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Utsiktens</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z3" t="n">
         <v>70</v>
       </c>
-      <c r="G3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="J3" t="n">
-        <v>18</v>
-      </c>
-      <c r="K3" t="n">
-        <v>21</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AA3" t="n">
-        <v>5.4</v>
+        <v>180</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
-        <v>8.800000000000001</v>
+        <v>120</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
         <v>24</v>
       </c>
       <c r="AI3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR3" t="n">
         <v>28</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>95</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>250</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Tulsa Roughnecks FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Monterey Bay FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="G4" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AO4" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.199999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>3.65</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.5</v>
+        <v>3.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>16.5</v>
+        <v>3.95</v>
       </c>
       <c r="BD4" t="n">
-        <v>34</v>
+        <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>18</v>
+        <v>3.85</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>17</v>
+        <v>2.96</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>17</v>
+        <v>1.37</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="BP4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>17</v>
+        <v>5.7</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>17</v>
+        <v>1.61</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>16.5</v>
+        <v>1.63</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,1006 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Forward Madison FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Fort Wayne FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>1.34</v>
       </c>
       <c r="M5" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.24</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Q5" t="n">
-        <v>3.45</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.5</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
         <v>14</v>
       </c>
       <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP5" t="n">
         <v>15</v>
       </c>
-      <c r="AH5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>460</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS5" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>55</v>
-      </c>
       <c r="AT5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE5" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY5" t="n">
+      <c r="BF5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP5" t="n">
         <v>13.5</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>100</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>95</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>270</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>55</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>90</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>180</v>
-      </c>
-      <c r="BK5" t="n">
+      <c r="BQ5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR5" t="n">
         <v>25</v>
       </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>320</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
       <c r="BS5" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="BT5" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU5" t="n">
         <v>6</v>
       </c>
       <c r="BV5" t="n">
-        <v>480</v>
+        <v>34</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Indy Eleven</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Brooklyn FC</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X6" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>6</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-17 15:42:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Tulsa Roughnecks FC</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Monterey Bay FC</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X7" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>9</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-17 15:42:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Forward Madison FC</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Fort Wayne FC</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Birmingham Legion FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="H2" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L2" t="n">
         <v>1.39</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N2" t="n">
         <v>4</v>
       </c>
-      <c r="K2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.62</v>
-      </c>
       <c r="O2" t="n">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="R2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.01</v>
-      </c>
-      <c r="S2" t="n">
-        <v>55</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3.7</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.12</v>
+        <v>980</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.5</v>
+        <v>990</v>
       </c>
       <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>960</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AG2" t="n">
         <v>970</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>46</v>
-      </c>
       <c r="AH2" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>1.92</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.4</v>
+        <v>1.92</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.85</v>
+        <v>1.67</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>1.71</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.85</v>
+        <v>1.79</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.85</v>
+        <v>1.73</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.85</v>
+        <v>1.86</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.85</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.85</v>
+        <v>1.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Tulsa Roughnecks FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Monterey Bay FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z3" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI3" t="n">
         <v>120</v>
       </c>
-      <c r="AF3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK3" t="n">
         <v>24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
         <v>15.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>14</v>
       </c>
-      <c r="AR3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="BA3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>85</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BT3" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BU3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>2.78</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="BZ3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8</v>
+        <v>2.66</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,498 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks FC</t>
+          <t>Forward Madison FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Monterey Bay FC</t>
+          <t>Fort Wayne FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH4" t="n">
         <v>3.9</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL4" t="n">
+      <c r="BI4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>85</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX4" t="n">
         <v>42</v>
       </c>
-      <c r="AM4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY4" t="n">
-        <v>1.63</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Forward Madison FC</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Fort Wayne FC</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-17.xlsx
@@ -878,7 +878,7 @@
         <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
@@ -887,13 +887,13 @@
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="Q2" t="n">
         <v>1.91</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
@@ -1010,7 +1010,7 @@
         <v>1.86</v>
       </c>
       <c r="BE2" t="n">
-        <v>85</v>
+        <v>1.92</v>
       </c>
       <c r="BF2" t="n">
         <v>1.67</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>110</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.32</v>
       </c>
       <c r="G3" t="n">
-        <v>1.95</v>
+        <v>1.35</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>17.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="K3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W3" t="n">
         <v>4</v>
       </c>
-      <c r="L3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.04</v>
-      </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>350</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI3" t="n">
         <v>110</v>
       </c>
-      <c r="AB3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AJ3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD3" t="n">
         <v>21</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.8</v>
       </c>
       <c r="BE3" t="n">
         <v>70</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>870</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BP3" t="n">
         <v>6.6</v>
       </c>
-      <c r="BH3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>85</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.7</v>
+        <v>34</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.78</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.76</v>
+        <v>70</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.66</v>
+        <v>22</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="AA4" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>950</v>
       </c>
       <c r="AC4" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>240</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>3.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>3.75</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>3.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.5</v>
+        <v>3.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>17.5</v>
+        <v>3.35</v>
       </c>
       <c r="BC4" t="n">
-        <v>15.5</v>
+        <v>3.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>13.5</v>
+        <v>3.55</v>
       </c>
       <c r="BE4" t="n">
-        <v>70</v>
+        <v>3.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>9.6</v>
+        <v>3.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>85</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
